--- a/live_rates.xlsx
+++ b/live_rates.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F837"/>
+  <dimension ref="A1:F1262"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17508,6 +17508,8506 @@
       </c>
       <c r="F837" t="inlineStr"/>
     </row>
+    <row r="838">
+      <c r="A838" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:30:56</t>
+        </is>
+      </c>
+      <c r="B838" t="n">
+        <v>154232.52</v>
+      </c>
+      <c r="C838" t="n">
+        <v>141276.99</v>
+      </c>
+      <c r="D838" t="n">
+        <v>245096.24</v>
+      </c>
+      <c r="E838" t="n">
+        <v>162977.13</v>
+      </c>
+      <c r="F838" t="inlineStr"/>
+    </row>
+    <row r="839">
+      <c r="A839" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:31:07</t>
+        </is>
+      </c>
+      <c r="B839" t="n">
+        <v>154192.28</v>
+      </c>
+      <c r="C839" t="n">
+        <v>141240.13</v>
+      </c>
+      <c r="D839" t="n">
+        <v>245023.45</v>
+      </c>
+      <c r="E839" t="n">
+        <v>162934.61</v>
+      </c>
+      <c r="F839" t="inlineStr"/>
+    </row>
+    <row r="840">
+      <c r="A840" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:31:18</t>
+        </is>
+      </c>
+      <c r="B840" t="n">
+        <v>154257.37</v>
+      </c>
+      <c r="C840" t="n">
+        <v>141299.75</v>
+      </c>
+      <c r="D840" t="n">
+        <v>245304.54</v>
+      </c>
+      <c r="E840" t="n">
+        <v>163003.39</v>
+      </c>
+      <c r="F840" t="inlineStr"/>
+    </row>
+    <row r="841">
+      <c r="A841" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:31:30</t>
+        </is>
+      </c>
+      <c r="B841" t="n">
+        <v>154420.1</v>
+      </c>
+      <c r="C841" t="n">
+        <v>141448.81</v>
+      </c>
+      <c r="D841" t="n">
+        <v>245703.99</v>
+      </c>
+      <c r="E841" t="n">
+        <v>163175.35</v>
+      </c>
+      <c r="F841" t="inlineStr"/>
+    </row>
+    <row r="842">
+      <c r="A842" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:31:41</t>
+        </is>
+      </c>
+      <c r="B842" t="n">
+        <v>154370.12</v>
+      </c>
+      <c r="C842" t="n">
+        <v>141403.03</v>
+      </c>
+      <c r="D842" t="n">
+        <v>245476.5</v>
+      </c>
+      <c r="E842" t="n">
+        <v>163122.53</v>
+      </c>
+      <c r="F842" t="inlineStr"/>
+    </row>
+    <row r="843">
+      <c r="A843" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:31:52</t>
+        </is>
+      </c>
+      <c r="B843" t="n">
+        <v>154370.12</v>
+      </c>
+      <c r="C843" t="n">
+        <v>141403.03</v>
+      </c>
+      <c r="D843" t="n">
+        <v>245520.89</v>
+      </c>
+      <c r="E843" t="n">
+        <v>163122.53</v>
+      </c>
+      <c r="F843" t="inlineStr"/>
+    </row>
+    <row r="844">
+      <c r="A844" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:32:03</t>
+        </is>
+      </c>
+      <c r="B844" t="n">
+        <v>154340.52</v>
+      </c>
+      <c r="C844" t="n">
+        <v>141375.92</v>
+      </c>
+      <c r="D844" t="n">
+        <v>245358.14</v>
+      </c>
+      <c r="E844" t="n">
+        <v>163091.26</v>
+      </c>
+      <c r="F844" t="inlineStr"/>
+    </row>
+    <row r="845">
+      <c r="A845" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:32:14</t>
+        </is>
+      </c>
+      <c r="B845" t="n">
+        <v>154168.89</v>
+      </c>
+      <c r="C845" t="n">
+        <v>141218.7</v>
+      </c>
+      <c r="D845" t="n">
+        <v>244869.87</v>
+      </c>
+      <c r="E845" t="n">
+        <v>162909.89</v>
+      </c>
+      <c r="F845" t="inlineStr"/>
+    </row>
+    <row r="846">
+      <c r="A846" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:32:26</t>
+        </is>
+      </c>
+      <c r="B846" t="n">
+        <v>154094.91</v>
+      </c>
+      <c r="C846" t="n">
+        <v>141150.93</v>
+      </c>
+      <c r="D846" t="n">
+        <v>244677.52</v>
+      </c>
+      <c r="E846" t="n">
+        <v>162831.72</v>
+      </c>
+      <c r="F846" t="inlineStr"/>
+    </row>
+    <row r="847">
+      <c r="A847" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:32:37</t>
+        </is>
+      </c>
+      <c r="B847" t="n">
+        <v>154141.4</v>
+      </c>
+      <c r="C847" t="n">
+        <v>141193.52</v>
+      </c>
+      <c r="D847" t="n">
+        <v>244746.64</v>
+      </c>
+      <c r="E847" t="n">
+        <v>162880.85</v>
+      </c>
+      <c r="F847" t="inlineStr"/>
+    </row>
+    <row r="848">
+      <c r="A848" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:32:48</t>
+        </is>
+      </c>
+      <c r="B848" t="n">
+        <v>154256.84</v>
+      </c>
+      <c r="C848" t="n">
+        <v>141299.26</v>
+      </c>
+      <c r="D848" t="n">
+        <v>245116.64</v>
+      </c>
+      <c r="E848" t="n">
+        <v>163002.83</v>
+      </c>
+      <c r="F848" t="inlineStr"/>
+    </row>
+    <row r="849">
+      <c r="A849" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:32:59</t>
+        </is>
+      </c>
+      <c r="B849" t="n">
+        <v>154319</v>
+      </c>
+      <c r="C849" t="n">
+        <v>141356.2</v>
+      </c>
+      <c r="D849" t="n">
+        <v>245368.24</v>
+      </c>
+      <c r="E849" t="n">
+        <v>163068.52</v>
+      </c>
+      <c r="F849" t="inlineStr"/>
+    </row>
+    <row r="850">
+      <c r="A850" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:33:10</t>
+        </is>
+      </c>
+      <c r="B850" t="n">
+        <v>154250.93</v>
+      </c>
+      <c r="C850" t="n">
+        <v>141293.85</v>
+      </c>
+      <c r="D850" t="n">
+        <v>245767.84</v>
+      </c>
+      <c r="E850" t="n">
+        <v>162996.58</v>
+      </c>
+      <c r="F850" t="inlineStr"/>
+    </row>
+    <row r="851">
+      <c r="A851" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:33:21</t>
+        </is>
+      </c>
+      <c r="B851" t="n">
+        <v>154197.64</v>
+      </c>
+      <c r="C851" t="n">
+        <v>141245.04</v>
+      </c>
+      <c r="D851" t="n">
+        <v>245264.65</v>
+      </c>
+      <c r="E851" t="n">
+        <v>162940.27</v>
+      </c>
+      <c r="F851" t="inlineStr"/>
+    </row>
+    <row r="852">
+      <c r="A852" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:33:32</t>
+        </is>
+      </c>
+      <c r="B852" t="n">
+        <v>154126.6</v>
+      </c>
+      <c r="C852" t="n">
+        <v>141179.97</v>
+      </c>
+      <c r="D852" t="n">
+        <v>245072.24</v>
+      </c>
+      <c r="E852" t="n">
+        <v>162865.21</v>
+      </c>
+      <c r="F852" t="inlineStr"/>
+    </row>
+    <row r="853">
+      <c r="A853" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:33:44</t>
+        </is>
+      </c>
+      <c r="B853" t="n">
+        <v>154134.97</v>
+      </c>
+      <c r="C853" t="n">
+        <v>141187.63</v>
+      </c>
+      <c r="D853" t="n">
+        <v>245144.76</v>
+      </c>
+      <c r="E853" t="n">
+        <v>162874.05</v>
+      </c>
+      <c r="F853" t="inlineStr"/>
+    </row>
+    <row r="854">
+      <c r="A854" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:33:55</t>
+        </is>
+      </c>
+      <c r="B854" t="n">
+        <v>154288.9</v>
+      </c>
+      <c r="C854" t="n">
+        <v>141328.63</v>
+      </c>
+      <c r="D854" t="n">
+        <v>245440.77</v>
+      </c>
+      <c r="E854" t="n">
+        <v>163036.71</v>
+      </c>
+      <c r="F854" t="inlineStr"/>
+    </row>
+    <row r="855">
+      <c r="A855" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:34:06</t>
+        </is>
+      </c>
+      <c r="B855" t="n">
+        <v>154374.74</v>
+      </c>
+      <c r="C855" t="n">
+        <v>141407.26</v>
+      </c>
+      <c r="D855" t="n">
+        <v>245781.18</v>
+      </c>
+      <c r="E855" t="n">
+        <v>163127.42</v>
+      </c>
+      <c r="F855" t="inlineStr"/>
+    </row>
+    <row r="856">
+      <c r="A856" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:34:17</t>
+        </is>
+      </c>
+      <c r="B856" t="n">
+        <v>154356.98</v>
+      </c>
+      <c r="C856" t="n">
+        <v>141390.99</v>
+      </c>
+      <c r="D856" t="n">
+        <v>245810.79</v>
+      </c>
+      <c r="E856" t="n">
+        <v>163108.65</v>
+      </c>
+      <c r="F856" t="inlineStr"/>
+    </row>
+    <row r="857">
+      <c r="A857" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:34:29</t>
+        </is>
+      </c>
+      <c r="B857" t="n">
+        <v>154389.54</v>
+      </c>
+      <c r="C857" t="n">
+        <v>141420.82</v>
+      </c>
+      <c r="D857" t="n">
+        <v>245766.39</v>
+      </c>
+      <c r="E857" t="n">
+        <v>163143.06</v>
+      </c>
+      <c r="F857" t="inlineStr"/>
+    </row>
+    <row r="858">
+      <c r="A858" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:34:40</t>
+        </is>
+      </c>
+      <c r="B858" t="n">
+        <v>154408.98</v>
+      </c>
+      <c r="C858" t="n">
+        <v>141438.63</v>
+      </c>
+      <c r="D858" t="n">
+        <v>245857.86</v>
+      </c>
+      <c r="E858" t="n">
+        <v>163163.6</v>
+      </c>
+      <c r="F858" t="inlineStr"/>
+    </row>
+    <row r="859">
+      <c r="A859" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:34:51</t>
+        </is>
+      </c>
+      <c r="B859" t="n">
+        <v>154403.06</v>
+      </c>
+      <c r="C859" t="n">
+        <v>141433.2</v>
+      </c>
+      <c r="D859" t="n">
+        <v>245991.06</v>
+      </c>
+      <c r="E859" t="n">
+        <v>163157.34</v>
+      </c>
+      <c r="F859" t="inlineStr"/>
+    </row>
+    <row r="860">
+      <c r="A860" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:35:02</t>
+        </is>
+      </c>
+      <c r="B860" t="n">
+        <v>154518.11</v>
+      </c>
+      <c r="C860" t="n">
+        <v>141538.59</v>
+      </c>
+      <c r="D860" t="n">
+        <v>246355.73</v>
+      </c>
+      <c r="E860" t="n">
+        <v>163278.91</v>
+      </c>
+      <c r="F860" t="inlineStr"/>
+    </row>
+    <row r="861">
+      <c r="A861" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:35:14</t>
+        </is>
+      </c>
+      <c r="B861" t="n">
+        <v>154526.98</v>
+      </c>
+      <c r="C861" t="n">
+        <v>141546.72</v>
+      </c>
+      <c r="D861" t="n">
+        <v>246444.53</v>
+      </c>
+      <c r="E861" t="n">
+        <v>163288.29</v>
+      </c>
+      <c r="F861" t="inlineStr"/>
+    </row>
+    <row r="862">
+      <c r="A862" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:35:25</t>
+        </is>
+      </c>
+      <c r="B862" t="n">
+        <v>154518.11</v>
+      </c>
+      <c r="C862" t="n">
+        <v>141538.59</v>
+      </c>
+      <c r="D862" t="n">
+        <v>246429.74</v>
+      </c>
+      <c r="E862" t="n">
+        <v>163278.91</v>
+      </c>
+      <c r="F862" t="inlineStr"/>
+    </row>
+    <row r="863">
+      <c r="A863" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:35:36</t>
+        </is>
+      </c>
+      <c r="B863" t="n">
+        <v>154626.09</v>
+      </c>
+      <c r="C863" t="n">
+        <v>141637.5</v>
+      </c>
+      <c r="D863" t="n">
+        <v>246932.76</v>
+      </c>
+      <c r="E863" t="n">
+        <v>163393.02</v>
+      </c>
+      <c r="F863" t="inlineStr"/>
+    </row>
+    <row r="864">
+      <c r="A864" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:35:47</t>
+        </is>
+      </c>
+      <c r="B864" t="n">
+        <v>154611.29</v>
+      </c>
+      <c r="C864" t="n">
+        <v>141623.94</v>
+      </c>
+      <c r="D864" t="n">
+        <v>246977.17</v>
+      </c>
+      <c r="E864" t="n">
+        <v>163377.38</v>
+      </c>
+      <c r="F864" t="inlineStr"/>
+    </row>
+    <row r="865">
+      <c r="A865" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:35:58</t>
+        </is>
+      </c>
+      <c r="B865" t="n">
+        <v>154700.11</v>
+      </c>
+      <c r="C865" t="n">
+        <v>141705.3</v>
+      </c>
+      <c r="D865" t="n">
+        <v>246947.56</v>
+      </c>
+      <c r="E865" t="n">
+        <v>163471.24</v>
+      </c>
+      <c r="F865" t="inlineStr"/>
+    </row>
+    <row r="866">
+      <c r="A866" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:36:09</t>
+        </is>
+      </c>
+      <c r="B866" t="n">
+        <v>154770.3</v>
+      </c>
+      <c r="C866" t="n">
+        <v>141769.59</v>
+      </c>
+      <c r="D866" t="n">
+        <v>247236.89</v>
+      </c>
+      <c r="E866" t="n">
+        <v>163545.4</v>
+      </c>
+      <c r="F866" t="inlineStr"/>
+    </row>
+    <row r="867">
+      <c r="A867" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:36:20</t>
+        </is>
+      </c>
+      <c r="B867" t="n">
+        <v>154826.55</v>
+      </c>
+      <c r="C867" t="n">
+        <v>141821.12</v>
+      </c>
+      <c r="D867" t="n">
+        <v>247251.69</v>
+      </c>
+      <c r="E867" t="n">
+        <v>163604.84</v>
+      </c>
+      <c r="F867" t="inlineStr"/>
+    </row>
+    <row r="868">
+      <c r="A868" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:36:31</t>
+        </is>
+      </c>
+      <c r="B868" t="n">
+        <v>154930.18</v>
+      </c>
+      <c r="C868" t="n">
+        <v>141916.05</v>
+      </c>
+      <c r="D868" t="n">
+        <v>247458.95</v>
+      </c>
+      <c r="E868" t="n">
+        <v>163714.35</v>
+      </c>
+      <c r="F868" t="inlineStr"/>
+    </row>
+    <row r="869">
+      <c r="A869" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:36:43</t>
+        </is>
+      </c>
+      <c r="B869" t="n">
+        <v>154924.26</v>
+      </c>
+      <c r="C869" t="n">
+        <v>141910.62</v>
+      </c>
+      <c r="D869" t="n">
+        <v>247592.21</v>
+      </c>
+      <c r="E869" t="n">
+        <v>163708.09</v>
+      </c>
+      <c r="F869" t="inlineStr"/>
+    </row>
+    <row r="870">
+      <c r="A870" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:36:54</t>
+        </is>
+      </c>
+      <c r="B870" t="n">
+        <v>154903.54</v>
+      </c>
+      <c r="C870" t="n">
+        <v>141891.64</v>
+      </c>
+      <c r="D870" t="n">
+        <v>247384.94</v>
+      </c>
+      <c r="E870" t="n">
+        <v>163686.2</v>
+      </c>
+      <c r="F870" t="inlineStr"/>
+    </row>
+    <row r="871">
+      <c r="A871" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:37:05</t>
+        </is>
+      </c>
+      <c r="B871" t="n">
+        <v>154947.47</v>
+      </c>
+      <c r="C871" t="n">
+        <v>141931.88</v>
+      </c>
+      <c r="D871" t="n">
+        <v>247546.41</v>
+      </c>
+      <c r="E871" t="n">
+        <v>163732.62</v>
+      </c>
+      <c r="F871" t="inlineStr"/>
+    </row>
+    <row r="872">
+      <c r="A872" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:37:16</t>
+        </is>
+      </c>
+      <c r="B872" t="n">
+        <v>154944.52</v>
+      </c>
+      <c r="C872" t="n">
+        <v>141929.18</v>
+      </c>
+      <c r="D872" t="n">
+        <v>247487.2</v>
+      </c>
+      <c r="E872" t="n">
+        <v>163729.5</v>
+      </c>
+      <c r="F872" t="inlineStr"/>
+    </row>
+    <row r="873">
+      <c r="A873" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:37:27</t>
+        </is>
+      </c>
+      <c r="B873" t="n">
+        <v>155000.78</v>
+      </c>
+      <c r="C873" t="n">
+        <v>141980.71</v>
+      </c>
+      <c r="D873" t="n">
+        <v>247635.24</v>
+      </c>
+      <c r="E873" t="n">
+        <v>163788.95</v>
+      </c>
+      <c r="F873" t="inlineStr"/>
+    </row>
+    <row r="874">
+      <c r="A874" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:37:38</t>
+        </is>
+      </c>
+      <c r="B874" t="n">
+        <v>154997.81</v>
+      </c>
+      <c r="C874" t="n">
+        <v>141978</v>
+      </c>
+      <c r="D874" t="n">
+        <v>247531.61</v>
+      </c>
+      <c r="E874" t="n">
+        <v>163785.82</v>
+      </c>
+      <c r="F874" t="inlineStr"/>
+    </row>
+    <row r="875">
+      <c r="A875" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:37:50</t>
+        </is>
+      </c>
+      <c r="B875" t="n">
+        <v>154965.24</v>
+      </c>
+      <c r="C875" t="n">
+        <v>141948.16</v>
+      </c>
+      <c r="D875" t="n">
+        <v>247546.41</v>
+      </c>
+      <c r="E875" t="n">
+        <v>163751.39</v>
+      </c>
+      <c r="F875" t="inlineStr"/>
+    </row>
+    <row r="876">
+      <c r="A876" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:38:05</t>
+        </is>
+      </c>
+      <c r="B876" t="n">
+        <v>155026.62</v>
+      </c>
+      <c r="C876" t="n">
+        <v>142004.38</v>
+      </c>
+      <c r="D876" t="n">
+        <v>247402.43</v>
+      </c>
+      <c r="E876" t="n">
+        <v>163816.26</v>
+      </c>
+      <c r="F876" t="inlineStr"/>
+    </row>
+    <row r="877">
+      <c r="A877" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:38:17</t>
+        </is>
+      </c>
+      <c r="B877" t="n">
+        <v>154985.16</v>
+      </c>
+      <c r="C877" t="n">
+        <v>141966.4</v>
+      </c>
+      <c r="D877" t="n">
+        <v>247417.22</v>
+      </c>
+      <c r="E877" t="n">
+        <v>163772.44</v>
+      </c>
+      <c r="F877" t="inlineStr"/>
+    </row>
+    <row r="878">
+      <c r="A878" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:38:30</t>
+        </is>
+      </c>
+      <c r="B878" t="n">
+        <v>155020.69</v>
+      </c>
+      <c r="C878" t="n">
+        <v>141998.95</v>
+      </c>
+      <c r="D878" t="n">
+        <v>247343.22</v>
+      </c>
+      <c r="E878" t="n">
+        <v>163809.99</v>
+      </c>
+      <c r="F878" t="inlineStr"/>
+    </row>
+    <row r="879">
+      <c r="A879" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:38:41</t>
+        </is>
+      </c>
+      <c r="B879" t="n">
+        <v>154976.28</v>
+      </c>
+      <c r="C879" t="n">
+        <v>141958.27</v>
+      </c>
+      <c r="D879" t="n">
+        <v>247476.45</v>
+      </c>
+      <c r="E879" t="n">
+        <v>163763.06</v>
+      </c>
+      <c r="F879" t="inlineStr"/>
+    </row>
+    <row r="880">
+      <c r="A880" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:38:52</t>
+        </is>
+      </c>
+      <c r="B880" t="n">
+        <v>154979.24</v>
+      </c>
+      <c r="C880" t="n">
+        <v>141960.99</v>
+      </c>
+      <c r="D880" t="n">
+        <v>247476.45</v>
+      </c>
+      <c r="E880" t="n">
+        <v>163766.19</v>
+      </c>
+      <c r="F880" t="inlineStr"/>
+    </row>
+    <row r="881">
+      <c r="A881" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:39:03</t>
+        </is>
+      </c>
+      <c r="B881" t="n">
+        <v>154952.6</v>
+      </c>
+      <c r="C881" t="n">
+        <v>141936.58</v>
+      </c>
+      <c r="D881" t="n">
+        <v>247121.13</v>
+      </c>
+      <c r="E881" t="n">
+        <v>163738.04</v>
+      </c>
+      <c r="F881" t="inlineStr"/>
+    </row>
+    <row r="882">
+      <c r="A882" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:39:15</t>
+        </is>
+      </c>
+      <c r="B882" t="n">
+        <v>154940.27</v>
+      </c>
+      <c r="C882" t="n">
+        <v>141925.29</v>
+      </c>
+      <c r="D882" t="n">
+        <v>247149.34</v>
+      </c>
+      <c r="E882" t="n">
+        <v>163725.01</v>
+      </c>
+      <c r="F882" t="inlineStr"/>
+    </row>
+    <row r="883">
+      <c r="A883" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:39:26</t>
+        </is>
+      </c>
+      <c r="B883" t="n">
+        <v>154886.98</v>
+      </c>
+      <c r="C883" t="n">
+        <v>141876.47</v>
+      </c>
+      <c r="D883" t="n">
+        <v>246942.06</v>
+      </c>
+      <c r="E883" t="n">
+        <v>163668.7</v>
+      </c>
+      <c r="F883" t="inlineStr"/>
+    </row>
+    <row r="884">
+      <c r="A884" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:39:38</t>
+        </is>
+      </c>
+      <c r="B884" t="n">
+        <v>154944.52</v>
+      </c>
+      <c r="C884" t="n">
+        <v>141929.18</v>
+      </c>
+      <c r="D884" t="n">
+        <v>247013.41</v>
+      </c>
+      <c r="E884" t="n">
+        <v>163729.5</v>
+      </c>
+      <c r="F884" t="inlineStr"/>
+    </row>
+    <row r="885">
+      <c r="A885" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:39:49</t>
+        </is>
+      </c>
+      <c r="B885" t="n">
+        <v>154974.13</v>
+      </c>
+      <c r="C885" t="n">
+        <v>141956.3</v>
+      </c>
+      <c r="D885" t="n">
+        <v>247087.44</v>
+      </c>
+      <c r="E885" t="n">
+        <v>163760.79</v>
+      </c>
+      <c r="F885" t="inlineStr"/>
+    </row>
+    <row r="886">
+      <c r="A886" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:40:00</t>
+        </is>
+      </c>
+      <c r="B886" t="n">
+        <v>155021.49</v>
+      </c>
+      <c r="C886" t="n">
+        <v>141999.69</v>
+      </c>
+      <c r="D886" t="n">
+        <v>247131.86</v>
+      </c>
+      <c r="E886" t="n">
+        <v>163810.84</v>
+      </c>
+      <c r="F886" t="inlineStr"/>
+    </row>
+    <row r="887">
+      <c r="A887" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:40:11</t>
+        </is>
+      </c>
+      <c r="B887" t="n">
+        <v>154707.37</v>
+      </c>
+      <c r="C887" t="n">
+        <v>141711.95</v>
+      </c>
+      <c r="D887" t="n">
+        <v>246092.36</v>
+      </c>
+      <c r="E887" t="n">
+        <v>163478.9</v>
+      </c>
+      <c r="F887" t="inlineStr"/>
+    </row>
+    <row r="888">
+      <c r="A888" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:40:22</t>
+        </is>
+      </c>
+      <c r="B888" t="n">
+        <v>154742.91</v>
+      </c>
+      <c r="C888" t="n">
+        <v>141744.51</v>
+      </c>
+      <c r="D888" t="n">
+        <v>246166.41</v>
+      </c>
+      <c r="E888" t="n">
+        <v>163516.46</v>
+      </c>
+      <c r="F888" t="inlineStr"/>
+    </row>
+    <row r="889">
+      <c r="A889" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:40:34</t>
+        </is>
+      </c>
+      <c r="B889" t="n">
+        <v>154604.99</v>
+      </c>
+      <c r="C889" t="n">
+        <v>141618.17</v>
+      </c>
+      <c r="D889" t="n">
+        <v>245556.6</v>
+      </c>
+      <c r="E889" t="n">
+        <v>163370.72</v>
+      </c>
+      <c r="F889" t="inlineStr"/>
+    </row>
+    <row r="890">
+      <c r="A890" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:40:45</t>
+        </is>
+      </c>
+      <c r="B890" t="n">
+        <v>154332.51</v>
+      </c>
+      <c r="C890" t="n">
+        <v>141368.58</v>
+      </c>
+      <c r="D890" t="n">
+        <v>244238.61</v>
+      </c>
+      <c r="E890" t="n">
+        <v>163082.79</v>
+      </c>
+      <c r="F890" t="inlineStr"/>
+    </row>
+    <row r="891">
+      <c r="A891" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:40:56</t>
+        </is>
+      </c>
+      <c r="B891" t="n">
+        <v>154264.39</v>
+      </c>
+      <c r="C891" t="n">
+        <v>141306.18</v>
+      </c>
+      <c r="D891" t="n">
+        <v>243927.64</v>
+      </c>
+      <c r="E891" t="n">
+        <v>163010.81</v>
+      </c>
+      <c r="F891" t="inlineStr"/>
+    </row>
+    <row r="892">
+      <c r="A892" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:41:08</t>
+        </is>
+      </c>
+      <c r="B892" t="n">
+        <v>154205.16</v>
+      </c>
+      <c r="C892" t="n">
+        <v>141251.93</v>
+      </c>
+      <c r="D892" t="n">
+        <v>244238.61</v>
+      </c>
+      <c r="E892" t="n">
+        <v>162948.22</v>
+      </c>
+      <c r="F892" t="inlineStr"/>
+    </row>
+    <row r="893">
+      <c r="A893" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:41:19</t>
+        </is>
+      </c>
+      <c r="B893" t="n">
+        <v>154181.46</v>
+      </c>
+      <c r="C893" t="n">
+        <v>141230.21</v>
+      </c>
+      <c r="D893" t="n">
+        <v>244268.24</v>
+      </c>
+      <c r="E893" t="n">
+        <v>162923.17</v>
+      </c>
+      <c r="F893" t="inlineStr"/>
+    </row>
+    <row r="894">
+      <c r="A894" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:41:30</t>
+        </is>
+      </c>
+      <c r="B894" t="n">
+        <v>154077.8</v>
+      </c>
+      <c r="C894" t="n">
+        <v>141135.26</v>
+      </c>
+      <c r="D894" t="n">
+        <v>244312.66</v>
+      </c>
+      <c r="E894" t="n">
+        <v>162813.64</v>
+      </c>
+      <c r="F894" t="inlineStr"/>
+    </row>
+    <row r="895">
+      <c r="A895" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:41:41</t>
+        </is>
+      </c>
+      <c r="B895" t="n">
+        <v>154010.98</v>
+      </c>
+      <c r="C895" t="n">
+        <v>141074.05</v>
+      </c>
+      <c r="D895" t="n">
+        <v>244339.63</v>
+      </c>
+      <c r="E895" t="n">
+        <v>162743.03</v>
+      </c>
+      <c r="F895" t="inlineStr"/>
+    </row>
+    <row r="896">
+      <c r="A896" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:41:53</t>
+        </is>
+      </c>
+      <c r="B896" t="n">
+        <v>154301.22</v>
+      </c>
+      <c r="C896" t="n">
+        <v>141339.91</v>
+      </c>
+      <c r="D896" t="n">
+        <v>245598.36</v>
+      </c>
+      <c r="E896" t="n">
+        <v>163049.72</v>
+      </c>
+      <c r="F896" t="inlineStr"/>
+    </row>
+    <row r="897">
+      <c r="A897" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:42:04</t>
+        </is>
+      </c>
+      <c r="B897" t="n">
+        <v>154272.88</v>
+      </c>
+      <c r="C897" t="n">
+        <v>141313.96</v>
+      </c>
+      <c r="D897" t="n">
+        <v>245432.78</v>
+      </c>
+      <c r="E897" t="n">
+        <v>163019.78</v>
+      </c>
+      <c r="F897" t="inlineStr"/>
+    </row>
+    <row r="898">
+      <c r="A898" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:42:15</t>
+        </is>
+      </c>
+      <c r="B898" t="n">
+        <v>154207.71</v>
+      </c>
+      <c r="C898" t="n">
+        <v>141254.27</v>
+      </c>
+      <c r="D898" t="n">
+        <v>245521.63</v>
+      </c>
+      <c r="E898" t="n">
+        <v>162950.92</v>
+      </c>
+      <c r="F898" t="inlineStr"/>
+    </row>
+    <row r="899">
+      <c r="A899" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:42:27</t>
+        </is>
+      </c>
+      <c r="B899" t="n">
+        <v>154006.33</v>
+      </c>
+      <c r="C899" t="n">
+        <v>141069.8</v>
+      </c>
+      <c r="D899" t="n">
+        <v>245018.15</v>
+      </c>
+      <c r="E899" t="n">
+        <v>162738.12</v>
+      </c>
+      <c r="F899" t="inlineStr"/>
+    </row>
+    <row r="900">
+      <c r="A900" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:42:38</t>
+        </is>
+      </c>
+      <c r="B900" t="n">
+        <v>153978</v>
+      </c>
+      <c r="C900" t="n">
+        <v>141043.85</v>
+      </c>
+      <c r="D900" t="n">
+        <v>245015.5</v>
+      </c>
+      <c r="E900" t="n">
+        <v>162708.19</v>
+      </c>
+      <c r="F900" t="inlineStr"/>
+    </row>
+    <row r="901">
+      <c r="A901" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:42:51</t>
+        </is>
+      </c>
+      <c r="B901" t="n">
+        <v>153966.16</v>
+      </c>
+      <c r="C901" t="n">
+        <v>141033</v>
+      </c>
+      <c r="D901" t="n">
+        <v>245711.46</v>
+      </c>
+      <c r="E901" t="n">
+        <v>162695.67</v>
+      </c>
+      <c r="F901" t="inlineStr"/>
+    </row>
+    <row r="902">
+      <c r="A902" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:43:03</t>
+        </is>
+      </c>
+      <c r="B902" t="n">
+        <v>153947.56</v>
+      </c>
+      <c r="C902" t="n">
+        <v>141015.97</v>
+      </c>
+      <c r="D902" t="n">
+        <v>245288.2</v>
+      </c>
+      <c r="E902" t="n">
+        <v>162676.02</v>
+      </c>
+      <c r="F902" t="inlineStr"/>
+    </row>
+    <row r="903">
+      <c r="A903" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:43:16</t>
+        </is>
+      </c>
+      <c r="B903" t="n">
+        <v>154006.81</v>
+      </c>
+      <c r="C903" t="n">
+        <v>141070.24</v>
+      </c>
+      <c r="D903" t="n">
+        <v>245495.56</v>
+      </c>
+      <c r="E903" t="n">
+        <v>162738.62</v>
+      </c>
+      <c r="F903" t="inlineStr"/>
+    </row>
+    <row r="904">
+      <c r="A904" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:43:32</t>
+        </is>
+      </c>
+      <c r="B904" t="n">
+        <v>153836.49</v>
+      </c>
+      <c r="C904" t="n">
+        <v>140914.23</v>
+      </c>
+      <c r="D904" t="n">
+        <v>244613.3</v>
+      </c>
+      <c r="E904" t="n">
+        <v>162558.65</v>
+      </c>
+      <c r="F904" t="inlineStr"/>
+    </row>
+    <row r="905">
+      <c r="A905" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:43:43</t>
+        </is>
+      </c>
+      <c r="B905" t="n">
+        <v>153700.23</v>
+      </c>
+      <c r="C905" t="n">
+        <v>140789.41</v>
+      </c>
+      <c r="D905" t="n">
+        <v>244717</v>
+      </c>
+      <c r="E905" t="n">
+        <v>162414.66</v>
+      </c>
+      <c r="F905" t="inlineStr"/>
+    </row>
+    <row r="906">
+      <c r="A906" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:43:55</t>
+        </is>
+      </c>
+      <c r="B906" t="n">
+        <v>153774.29</v>
+      </c>
+      <c r="C906" t="n">
+        <v>140857.25</v>
+      </c>
+      <c r="D906" t="n">
+        <v>244894.74</v>
+      </c>
+      <c r="E906" t="n">
+        <v>162492.92</v>
+      </c>
+      <c r="F906" t="inlineStr"/>
+    </row>
+    <row r="907">
+      <c r="A907" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:48:07</t>
+        </is>
+      </c>
+      <c r="B907" t="n">
+        <v>153134.54</v>
+      </c>
+      <c r="C907" t="n">
+        <v>140271.24</v>
+      </c>
+      <c r="D907" t="n">
+        <v>242637.31</v>
+      </c>
+      <c r="E907" t="n">
+        <v>161816.9</v>
+      </c>
+      <c r="F907" t="inlineStr"/>
+    </row>
+    <row r="908">
+      <c r="A908" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:48:20</t>
+        </is>
+      </c>
+      <c r="B908" t="n">
+        <v>153101.94</v>
+      </c>
+      <c r="C908" t="n">
+        <v>140241.38</v>
+      </c>
+      <c r="D908" t="n">
+        <v>242726.21</v>
+      </c>
+      <c r="E908" t="n">
+        <v>161782.46</v>
+      </c>
+      <c r="F908" t="inlineStr"/>
+    </row>
+    <row r="909">
+      <c r="A909" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:48:31</t>
+        </is>
+      </c>
+      <c r="B909" t="n">
+        <v>153107.87</v>
+      </c>
+      <c r="C909" t="n">
+        <v>140246.81</v>
+      </c>
+      <c r="D909" t="n">
+        <v>242592.87</v>
+      </c>
+      <c r="E909" t="n">
+        <v>161788.72</v>
+      </c>
+      <c r="F909" t="inlineStr"/>
+    </row>
+    <row r="910">
+      <c r="A910" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:48:45</t>
+        </is>
+      </c>
+      <c r="B910" t="n">
+        <v>153014.81</v>
+      </c>
+      <c r="C910" t="n">
+        <v>140161.57</v>
+      </c>
+      <c r="D910" t="n">
+        <v>242434.89</v>
+      </c>
+      <c r="E910" t="n">
+        <v>161690.38</v>
+      </c>
+      <c r="F910" t="inlineStr"/>
+    </row>
+    <row r="911">
+      <c r="A911" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:48:56</t>
+        </is>
+      </c>
+      <c r="B911" t="n">
+        <v>153109.61</v>
+      </c>
+      <c r="C911" t="n">
+        <v>140248.4</v>
+      </c>
+      <c r="D911" t="n">
+        <v>242523.78</v>
+      </c>
+      <c r="E911" t="n">
+        <v>161790.56</v>
+      </c>
+      <c r="F911" t="inlineStr"/>
+    </row>
+    <row r="912">
+      <c r="A912" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:49:08</t>
+        </is>
+      </c>
+      <c r="B912" t="n">
+        <v>152892.76</v>
+      </c>
+      <c r="C912" t="n">
+        <v>140049.77</v>
+      </c>
+      <c r="D912" t="n">
+        <v>242107.36</v>
+      </c>
+      <c r="E912" t="n">
+        <v>161561.42</v>
+      </c>
+      <c r="F912" t="inlineStr"/>
+    </row>
+    <row r="913">
+      <c r="A913" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:49:19</t>
+        </is>
+      </c>
+      <c r="B913" t="n">
+        <v>152857.21</v>
+      </c>
+      <c r="C913" t="n">
+        <v>140017.2</v>
+      </c>
+      <c r="D913" t="n">
+        <v>241766.69</v>
+      </c>
+      <c r="E913" t="n">
+        <v>161523.85</v>
+      </c>
+      <c r="F913" t="inlineStr"/>
+    </row>
+    <row r="914">
+      <c r="A914" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:49:53</t>
+        </is>
+      </c>
+      <c r="B914" t="n">
+        <v>153008.3</v>
+      </c>
+      <c r="C914" t="n">
+        <v>140155.6</v>
+      </c>
+      <c r="D914" t="n">
+        <v>242136.99</v>
+      </c>
+      <c r="E914" t="n">
+        <v>161683.5</v>
+      </c>
+      <c r="F914" t="inlineStr"/>
+    </row>
+    <row r="915">
+      <c r="A915" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:50:06</t>
+        </is>
+      </c>
+      <c r="B915" t="n">
+        <v>152963.74</v>
+      </c>
+      <c r="C915" t="n">
+        <v>140114.79</v>
+      </c>
+      <c r="D915" t="n">
+        <v>242009.67</v>
+      </c>
+      <c r="E915" t="n">
+        <v>161636.42</v>
+      </c>
+      <c r="F915" t="inlineStr"/>
+    </row>
+    <row r="916">
+      <c r="A916" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:50:20</t>
+        </is>
+      </c>
+      <c r="B916" t="n">
+        <v>152978.55</v>
+      </c>
+      <c r="C916" t="n">
+        <v>140128.35</v>
+      </c>
+      <c r="D916" t="n">
+        <v>242246.65</v>
+      </c>
+      <c r="E916" t="n">
+        <v>161652.07</v>
+      </c>
+      <c r="F916" t="inlineStr"/>
+    </row>
+    <row r="917">
+      <c r="A917" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:50:32</t>
+        </is>
+      </c>
+      <c r="B917" t="n">
+        <v>152910.43</v>
+      </c>
+      <c r="C917" t="n">
+        <v>140065.95</v>
+      </c>
+      <c r="D917" t="n">
+        <v>242054.1</v>
+      </c>
+      <c r="E917" t="n">
+        <v>161580.08</v>
+      </c>
+      <c r="F917" t="inlineStr"/>
+    </row>
+    <row r="918">
+      <c r="A918" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:50:46</t>
+        </is>
+      </c>
+      <c r="B918" t="n">
+        <v>152896.32</v>
+      </c>
+      <c r="C918" t="n">
+        <v>140053.03</v>
+      </c>
+      <c r="D918" t="n">
+        <v>241798.01</v>
+      </c>
+      <c r="E918" t="n">
+        <v>161565.17</v>
+      </c>
+      <c r="F918" t="inlineStr"/>
+    </row>
+    <row r="919">
+      <c r="A919" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:51:01</t>
+        </is>
+      </c>
+      <c r="B919" t="n">
+        <v>152822.26</v>
+      </c>
+      <c r="C919" t="n">
+        <v>139985.19</v>
+      </c>
+      <c r="D919" t="n">
+        <v>241812.81</v>
+      </c>
+      <c r="E919" t="n">
+        <v>161486.92</v>
+      </c>
+      <c r="F919" t="inlineStr"/>
+    </row>
+    <row r="920">
+      <c r="A920" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:51:15</t>
+        </is>
+      </c>
+      <c r="B920" t="n">
+        <v>153053.33</v>
+      </c>
+      <c r="C920" t="n">
+        <v>140196.85</v>
+      </c>
+      <c r="D920" t="n">
+        <v>242583.01</v>
+      </c>
+      <c r="E920" t="n">
+        <v>161731.09</v>
+      </c>
+      <c r="F920" t="inlineStr"/>
+    </row>
+    <row r="921">
+      <c r="A921" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:51:28</t>
+        </is>
+      </c>
+      <c r="B921" t="n">
+        <v>153275.5</v>
+      </c>
+      <c r="C921" t="n">
+        <v>140400.36</v>
+      </c>
+      <c r="D921" t="n">
+        <v>243205.1</v>
+      </c>
+      <c r="E921" t="n">
+        <v>161965.86</v>
+      </c>
+      <c r="F921" t="inlineStr"/>
+    </row>
+    <row r="922">
+      <c r="A922" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:51:43</t>
+        </is>
+      </c>
+      <c r="B922" t="n">
+        <v>153303.65</v>
+      </c>
+      <c r="C922" t="n">
+        <v>140426.15</v>
+      </c>
+      <c r="D922" t="n">
+        <v>243450.57</v>
+      </c>
+      <c r="E922" t="n">
+        <v>161995.6</v>
+      </c>
+      <c r="F922" t="inlineStr"/>
+    </row>
+    <row r="923">
+      <c r="A923" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:51:56</t>
+        </is>
+      </c>
+      <c r="B923" t="n">
+        <v>153247.38</v>
+      </c>
+      <c r="C923" t="n">
+        <v>140374.6</v>
+      </c>
+      <c r="D923" t="n">
+        <v>243095.11</v>
+      </c>
+      <c r="E923" t="n">
+        <v>161936.14</v>
+      </c>
+      <c r="F923" t="inlineStr"/>
+    </row>
+    <row r="924">
+      <c r="A924" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:52:07</t>
+        </is>
+      </c>
+      <c r="B924" t="n">
+        <v>153385.1</v>
+      </c>
+      <c r="C924" t="n">
+        <v>140500.75</v>
+      </c>
+      <c r="D924" t="n">
+        <v>243160.66</v>
+      </c>
+      <c r="E924" t="n">
+        <v>162081.67</v>
+      </c>
+      <c r="F924" t="inlineStr"/>
+    </row>
+    <row r="925">
+      <c r="A925" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:52:46</t>
+        </is>
+      </c>
+      <c r="B925" t="n">
+        <v>153623.01</v>
+      </c>
+      <c r="C925" t="n">
+        <v>140718.68</v>
+      </c>
+      <c r="D925" t="n">
+        <v>244071.03</v>
+      </c>
+      <c r="E925" t="n">
+        <v>162333.07</v>
+      </c>
+      <c r="F925" t="inlineStr"/>
+    </row>
+    <row r="926">
+      <c r="A926" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:53:00</t>
+        </is>
+      </c>
+      <c r="B926" t="n">
+        <v>153460.09</v>
+      </c>
+      <c r="C926" t="n">
+        <v>140569.45</v>
+      </c>
+      <c r="D926" t="n">
+        <v>243374.93</v>
+      </c>
+      <c r="E926" t="n">
+        <v>162160.91</v>
+      </c>
+      <c r="F926" t="inlineStr"/>
+    </row>
+    <row r="927">
+      <c r="A927" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:53:12</t>
+        </is>
+      </c>
+      <c r="B927" t="n">
+        <v>153443.04</v>
+      </c>
+      <c r="C927" t="n">
+        <v>140553.83</v>
+      </c>
+      <c r="D927" t="n">
+        <v>243415.1</v>
+      </c>
+      <c r="E927" t="n">
+        <v>162142.9</v>
+      </c>
+      <c r="F927" t="inlineStr"/>
+    </row>
+    <row r="928">
+      <c r="A928" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:53:26</t>
+        </is>
+      </c>
+      <c r="B928" t="n">
+        <v>153511.19</v>
+      </c>
+      <c r="C928" t="n">
+        <v>140616.25</v>
+      </c>
+      <c r="D928" t="n">
+        <v>243400.29</v>
+      </c>
+      <c r="E928" t="n">
+        <v>162214.9</v>
+      </c>
+      <c r="F928" t="inlineStr"/>
+    </row>
+    <row r="929">
+      <c r="A929" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:53:57</t>
+        </is>
+      </c>
+      <c r="B929" t="n">
+        <v>153229.77</v>
+      </c>
+      <c r="C929" t="n">
+        <v>140358.46</v>
+      </c>
+      <c r="D929" t="n">
+        <v>242955.94</v>
+      </c>
+      <c r="E929" t="n">
+        <v>161917.53</v>
+      </c>
+      <c r="F929" t="inlineStr"/>
+    </row>
+    <row r="930">
+      <c r="A930" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:54:10</t>
+        </is>
+      </c>
+      <c r="B930" t="n">
+        <v>153320.66</v>
+      </c>
+      <c r="C930" t="n">
+        <v>140441.72</v>
+      </c>
+      <c r="D930" t="n">
+        <v>243141.58</v>
+      </c>
+      <c r="E930" t="n">
+        <v>162013.57</v>
+      </c>
+      <c r="F930" t="inlineStr"/>
+    </row>
+    <row r="931">
+      <c r="A931" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:54:21</t>
+        </is>
+      </c>
+      <c r="B931" t="n">
+        <v>153299.92</v>
+      </c>
+      <c r="C931" t="n">
+        <v>140422.72</v>
+      </c>
+      <c r="D931" t="n">
+        <v>243304.52</v>
+      </c>
+      <c r="E931" t="n">
+        <v>161991.65</v>
+      </c>
+      <c r="F931" t="inlineStr"/>
+    </row>
+    <row r="932">
+      <c r="A932" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:54:32</t>
+        </is>
+      </c>
+      <c r="B932" t="n">
+        <v>153120.88</v>
+      </c>
+      <c r="C932" t="n">
+        <v>140258.73</v>
+      </c>
+      <c r="D932" t="n">
+        <v>243396.05</v>
+      </c>
+      <c r="E932" t="n">
+        <v>161802.47</v>
+      </c>
+      <c r="F932" t="inlineStr"/>
+    </row>
+    <row r="933">
+      <c r="A933" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:54:43</t>
+        </is>
+      </c>
+      <c r="B933" t="n">
+        <v>153079.39</v>
+      </c>
+      <c r="C933" t="n">
+        <v>140220.73</v>
+      </c>
+      <c r="D933" t="n">
+        <v>243188.66</v>
+      </c>
+      <c r="E933" t="n">
+        <v>161758.63</v>
+      </c>
+      <c r="F933" t="inlineStr"/>
+    </row>
+    <row r="934">
+      <c r="A934" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:54:56</t>
+        </is>
+      </c>
+      <c r="B934" t="n">
+        <v>153251.23</v>
+      </c>
+      <c r="C934" t="n">
+        <v>140378.12</v>
+      </c>
+      <c r="D934" t="n">
+        <v>243647.86</v>
+      </c>
+      <c r="E934" t="n">
+        <v>161940.2</v>
+      </c>
+      <c r="F934" t="inlineStr"/>
+    </row>
+    <row r="935">
+      <c r="A935" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:55:07</t>
+        </is>
+      </c>
+      <c r="B935" t="n">
+        <v>153402.31</v>
+      </c>
+      <c r="C935" t="n">
+        <v>140516.52</v>
+      </c>
+      <c r="D935" t="n">
+        <v>244062.6</v>
+      </c>
+      <c r="E935" t="n">
+        <v>162099.86</v>
+      </c>
+      <c r="F935" t="inlineStr"/>
+    </row>
+    <row r="936">
+      <c r="A936" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:55:19</t>
+        </is>
+      </c>
+      <c r="B936" t="n">
+        <v>153384.54</v>
+      </c>
+      <c r="C936" t="n">
+        <v>140500.24</v>
+      </c>
+      <c r="D936" t="n">
+        <v>244107.03</v>
+      </c>
+      <c r="E936" t="n">
+        <v>162081.07</v>
+      </c>
+      <c r="F936" t="inlineStr"/>
+    </row>
+    <row r="937">
+      <c r="A937" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:55:30</t>
+        </is>
+      </c>
+      <c r="B937" t="n">
+        <v>153340.1</v>
+      </c>
+      <c r="C937" t="n">
+        <v>140459.53</v>
+      </c>
+      <c r="D937" t="n">
+        <v>243840.4</v>
+      </c>
+      <c r="E937" t="n">
+        <v>162034.12</v>
+      </c>
+      <c r="F937" t="inlineStr"/>
+    </row>
+    <row r="938">
+      <c r="A938" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:55:42</t>
+        </is>
+      </c>
+      <c r="B938" t="n">
+        <v>153242.33</v>
+      </c>
+      <c r="C938" t="n">
+        <v>140369.97</v>
+      </c>
+      <c r="D938" t="n">
+        <v>243810.79</v>
+      </c>
+      <c r="E938" t="n">
+        <v>161930.8</v>
+      </c>
+      <c r="F938" t="inlineStr"/>
+    </row>
+    <row r="939">
+      <c r="A939" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:55:53</t>
+        </is>
+      </c>
+      <c r="B939" t="n">
+        <v>153292.7</v>
+      </c>
+      <c r="C939" t="n">
+        <v>140416.11</v>
+      </c>
+      <c r="D939" t="n">
+        <v>243810.79</v>
+      </c>
+      <c r="E939" t="n">
+        <v>161984.03</v>
+      </c>
+      <c r="F939" t="inlineStr"/>
+    </row>
+    <row r="940">
+      <c r="A940" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:56:04</t>
+        </is>
+      </c>
+      <c r="B940" t="n">
+        <v>153408.98</v>
+      </c>
+      <c r="C940" t="n">
+        <v>140522.63</v>
+      </c>
+      <c r="D940" t="n">
+        <v>244043.58</v>
+      </c>
+      <c r="E940" t="n">
+        <v>162106.9</v>
+      </c>
+      <c r="F940" t="inlineStr"/>
+    </row>
+    <row r="941">
+      <c r="A941" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:56:16</t>
+        </is>
+      </c>
+      <c r="B941" t="n">
+        <v>153352.68</v>
+      </c>
+      <c r="C941" t="n">
+        <v>140471.06</v>
+      </c>
+      <c r="D941" t="n">
+        <v>243791.76</v>
+      </c>
+      <c r="E941" t="n">
+        <v>162047.41</v>
+      </c>
+      <c r="F941" t="inlineStr"/>
+    </row>
+    <row r="942">
+      <c r="A942" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:56:27</t>
+        </is>
+      </c>
+      <c r="B942" t="n">
+        <v>153254.92</v>
+      </c>
+      <c r="C942" t="n">
+        <v>140381.51</v>
+      </c>
+      <c r="D942" t="n">
+        <v>243584.38</v>
+      </c>
+      <c r="E942" t="n">
+        <v>161944.11</v>
+      </c>
+      <c r="F942" t="inlineStr"/>
+    </row>
+    <row r="943">
+      <c r="A943" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:56:38</t>
+        </is>
+      </c>
+      <c r="B943" t="n">
+        <v>153355.65</v>
+      </c>
+      <c r="C943" t="n">
+        <v>140473.77</v>
+      </c>
+      <c r="D943" t="n">
+        <v>243895.44</v>
+      </c>
+      <c r="E943" t="n">
+        <v>162050.54</v>
+      </c>
+      <c r="F943" t="inlineStr"/>
+    </row>
+    <row r="944">
+      <c r="A944" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:56:50</t>
+        </is>
+      </c>
+      <c r="B944" t="n">
+        <v>153272.7</v>
+      </c>
+      <c r="C944" t="n">
+        <v>140397.79</v>
+      </c>
+      <c r="D944" t="n">
+        <v>243732.49</v>
+      </c>
+      <c r="E944" t="n">
+        <v>161962.89</v>
+      </c>
+      <c r="F944" t="inlineStr"/>
+    </row>
+    <row r="945">
+      <c r="A945" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:57:01</t>
+        </is>
+      </c>
+      <c r="B945" t="n">
+        <v>153438.61</v>
+      </c>
+      <c r="C945" t="n">
+        <v>140549.77</v>
+      </c>
+      <c r="D945" t="n">
+        <v>243954.7</v>
+      </c>
+      <c r="E945" t="n">
+        <v>162138.21</v>
+      </c>
+      <c r="F945" t="inlineStr"/>
+    </row>
+    <row r="946">
+      <c r="A946" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:57:12</t>
+        </is>
+      </c>
+      <c r="B946" t="n">
+        <v>153372.12</v>
+      </c>
+      <c r="C946" t="n">
+        <v>140488.87</v>
+      </c>
+      <c r="D946" t="n">
+        <v>244001.79</v>
+      </c>
+      <c r="E946" t="n">
+        <v>162067.96</v>
+      </c>
+      <c r="F946" t="inlineStr"/>
+    </row>
+    <row r="947">
+      <c r="A947" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:57:23</t>
+        </is>
+      </c>
+      <c r="B947" t="n">
+        <v>153381.02</v>
+      </c>
+      <c r="C947" t="n">
+        <v>140497.01</v>
+      </c>
+      <c r="D947" t="n">
+        <v>244238.8</v>
+      </c>
+      <c r="E947" t="n">
+        <v>162077.36</v>
+      </c>
+      <c r="F947" t="inlineStr"/>
+    </row>
+    <row r="948">
+      <c r="A948" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:58:02</t>
+        </is>
+      </c>
+      <c r="B948" t="n">
+        <v>153555.81</v>
+      </c>
+      <c r="C948" t="n">
+        <v>140657.12</v>
+      </c>
+      <c r="D948" t="n">
+        <v>244905.39</v>
+      </c>
+      <c r="E948" t="n">
+        <v>162262.06</v>
+      </c>
+      <c r="F948" t="inlineStr"/>
+    </row>
+    <row r="949">
+      <c r="A949" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:58:13</t>
+        </is>
+      </c>
+      <c r="B949" t="n">
+        <v>153511.37</v>
+      </c>
+      <c r="C949" t="n">
+        <v>140616.42</v>
+      </c>
+      <c r="D949" t="n">
+        <v>244683.18</v>
+      </c>
+      <c r="E949" t="n">
+        <v>162215.1</v>
+      </c>
+      <c r="F949" t="inlineStr"/>
+    </row>
+    <row r="950">
+      <c r="A950" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:58:25</t>
+        </is>
+      </c>
+      <c r="B950" t="n">
+        <v>153529.15</v>
+      </c>
+      <c r="C950" t="n">
+        <v>140632.7</v>
+      </c>
+      <c r="D950" t="n">
+        <v>244683.18</v>
+      </c>
+      <c r="E950" t="n">
+        <v>162233.89</v>
+      </c>
+      <c r="F950" t="inlineStr"/>
+    </row>
+    <row r="951">
+      <c r="A951" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:58:36</t>
+        </is>
+      </c>
+      <c r="B951" t="n">
+        <v>153469.9</v>
+      </c>
+      <c r="C951" t="n">
+        <v>140578.43</v>
+      </c>
+      <c r="D951" t="n">
+        <v>244564.69</v>
+      </c>
+      <c r="E951" t="n">
+        <v>162171.27</v>
+      </c>
+      <c r="F951" t="inlineStr"/>
+    </row>
+    <row r="952">
+      <c r="A952" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:58:47</t>
+        </is>
+      </c>
+      <c r="B952" t="n">
+        <v>153475.82</v>
+      </c>
+      <c r="C952" t="n">
+        <v>140583.85</v>
+      </c>
+      <c r="D952" t="n">
+        <v>244357.31</v>
+      </c>
+      <c r="E952" t="n">
+        <v>162177.53</v>
+      </c>
+      <c r="F952" t="inlineStr"/>
+    </row>
+    <row r="953">
+      <c r="A953" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:58:59</t>
+        </is>
+      </c>
+      <c r="B953" t="n">
+        <v>153529.15</v>
+      </c>
+      <c r="C953" t="n">
+        <v>140632.7</v>
+      </c>
+      <c r="D953" t="n">
+        <v>244342.48</v>
+      </c>
+      <c r="E953" t="n">
+        <v>162233.89</v>
+      </c>
+      <c r="F953" t="inlineStr"/>
+    </row>
+    <row r="954">
+      <c r="A954" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:59:10</t>
+        </is>
+      </c>
+      <c r="B954" t="n">
+        <v>153500.62</v>
+      </c>
+      <c r="C954" t="n">
+        <v>140606.57</v>
+      </c>
+      <c r="D954" t="n">
+        <v>244165.81</v>
+      </c>
+      <c r="E954" t="n">
+        <v>162203.73</v>
+      </c>
+      <c r="F954" t="inlineStr"/>
+    </row>
+    <row r="955">
+      <c r="A955" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:59:21</t>
+        </is>
+      </c>
+      <c r="B955" t="n">
+        <v>153613.21</v>
+      </c>
+      <c r="C955" t="n">
+        <v>140709.7</v>
+      </c>
+      <c r="D955" t="n">
+        <v>244654.66</v>
+      </c>
+      <c r="E955" t="n">
+        <v>162322.71</v>
+      </c>
+      <c r="F955" t="inlineStr"/>
+    </row>
+    <row r="956">
+      <c r="A956" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:59:33</t>
+        </is>
+      </c>
+      <c r="B956" t="n">
+        <v>153678.75</v>
+      </c>
+      <c r="C956" t="n">
+        <v>140769.74</v>
+      </c>
+      <c r="D956" t="n">
+        <v>244941.44</v>
+      </c>
+      <c r="E956" t="n">
+        <v>162391.97</v>
+      </c>
+      <c r="F956" t="inlineStr"/>
+    </row>
+    <row r="957">
+      <c r="A957" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:59:45</t>
+        </is>
+      </c>
+      <c r="B957" t="n">
+        <v>153512.84</v>
+      </c>
+      <c r="C957" t="n">
+        <v>140617.77</v>
+      </c>
+      <c r="D957" t="n">
+        <v>244734.04</v>
+      </c>
+      <c r="E957" t="n">
+        <v>162216.65</v>
+      </c>
+      <c r="F957" t="inlineStr"/>
+    </row>
+    <row r="958">
+      <c r="A958" t="inlineStr">
+        <is>
+          <t>2026-03-03 18:59:58</t>
+        </is>
+      </c>
+      <c r="B958" t="n">
+        <v>153622.46</v>
+      </c>
+      <c r="C958" t="n">
+        <v>140718.18</v>
+      </c>
+      <c r="D958" t="n">
+        <v>244956.27</v>
+      </c>
+      <c r="E958" t="n">
+        <v>162332.49</v>
+      </c>
+      <c r="F958" t="inlineStr"/>
+    </row>
+    <row r="959">
+      <c r="A959" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:00:10</t>
+        </is>
+      </c>
+      <c r="B959" t="n">
+        <v>153676.72</v>
+      </c>
+      <c r="C959" t="n">
+        <v>140767.88</v>
+      </c>
+      <c r="D959" t="n">
+        <v>244874.23</v>
+      </c>
+      <c r="E959" t="n">
+        <v>162389.82</v>
+      </c>
+      <c r="F959" t="inlineStr"/>
+    </row>
+    <row r="960">
+      <c r="A960" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:00:22</t>
+        </is>
+      </c>
+      <c r="B960" t="n">
+        <v>153756.72</v>
+      </c>
+      <c r="C960" t="n">
+        <v>140841.16</v>
+      </c>
+      <c r="D960" t="n">
+        <v>245303.82</v>
+      </c>
+      <c r="E960" t="n">
+        <v>162474.36</v>
+      </c>
+      <c r="F960" t="inlineStr"/>
+    </row>
+    <row r="961">
+      <c r="A961" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:00:33</t>
+        </is>
+      </c>
+      <c r="B961" t="n">
+        <v>153625.78</v>
+      </c>
+      <c r="C961" t="n">
+        <v>140721.22</v>
+      </c>
+      <c r="D961" t="n">
+        <v>245215.3</v>
+      </c>
+      <c r="E961" t="n">
+        <v>162336</v>
+      </c>
+      <c r="F961" t="inlineStr"/>
+    </row>
+    <row r="962">
+      <c r="A962" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:00:44</t>
+        </is>
+      </c>
+      <c r="B962" t="n">
+        <v>153756.14</v>
+      </c>
+      <c r="C962" t="n">
+        <v>140840.63</v>
+      </c>
+      <c r="D962" t="n">
+        <v>244993.1</v>
+      </c>
+      <c r="E962" t="n">
+        <v>162473.75</v>
+      </c>
+      <c r="F962" t="inlineStr"/>
+    </row>
+    <row r="963">
+      <c r="A963" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:00:56</t>
+        </is>
+      </c>
+      <c r="B963" t="n">
+        <v>153797.61</v>
+      </c>
+      <c r="C963" t="n">
+        <v>140878.61</v>
+      </c>
+      <c r="D963" t="n">
+        <v>245200.47</v>
+      </c>
+      <c r="E963" t="n">
+        <v>162517.57</v>
+      </c>
+      <c r="F963" t="inlineStr"/>
+    </row>
+    <row r="964">
+      <c r="A964" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:01:07</t>
+        </is>
+      </c>
+      <c r="B964" t="n">
+        <v>153927.26</v>
+      </c>
+      <c r="C964" t="n">
+        <v>140997.37</v>
+      </c>
+      <c r="D964" t="n">
+        <v>245617.59</v>
+      </c>
+      <c r="E964" t="n">
+        <v>162654.57</v>
+      </c>
+      <c r="F964" t="inlineStr"/>
+    </row>
+    <row r="965">
+      <c r="A965" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:01:18</t>
+        </is>
+      </c>
+      <c r="B965" t="n">
+        <v>153770.24</v>
+      </c>
+      <c r="C965" t="n">
+        <v>140853.54</v>
+      </c>
+      <c r="D965" t="n">
+        <v>245187.97</v>
+      </c>
+      <c r="E965" t="n">
+        <v>162488.64</v>
+      </c>
+      <c r="F965" t="inlineStr"/>
+    </row>
+    <row r="966">
+      <c r="A966" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:01:30</t>
+        </is>
+      </c>
+      <c r="B966" t="n">
+        <v>153666.54</v>
+      </c>
+      <c r="C966" t="n">
+        <v>140758.55</v>
+      </c>
+      <c r="D966" t="n">
+        <v>245010.21</v>
+      </c>
+      <c r="E966" t="n">
+        <v>162379.06</v>
+      </c>
+      <c r="F966" t="inlineStr"/>
+    </row>
+    <row r="967">
+      <c r="A967" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:01:41</t>
+        </is>
+      </c>
+      <c r="B967" t="n">
+        <v>153555.24</v>
+      </c>
+      <c r="C967" t="n">
+        <v>140656.6</v>
+      </c>
+      <c r="D967" t="n">
+        <v>244814.96</v>
+      </c>
+      <c r="E967" t="n">
+        <v>162261.46</v>
+      </c>
+      <c r="F967" t="inlineStr"/>
+    </row>
+    <row r="968">
+      <c r="A968" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:01:52</t>
+        </is>
+      </c>
+      <c r="B968" t="n">
+        <v>153632.28</v>
+      </c>
+      <c r="C968" t="n">
+        <v>140727.17</v>
+      </c>
+      <c r="D968" t="n">
+        <v>245066.79</v>
+      </c>
+      <c r="E968" t="n">
+        <v>162342.86</v>
+      </c>
+      <c r="F968" t="inlineStr"/>
+    </row>
+    <row r="969">
+      <c r="A969" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:02:03</t>
+        </is>
+      </c>
+      <c r="B969" t="n">
+        <v>153644.13</v>
+      </c>
+      <c r="C969" t="n">
+        <v>140738.02</v>
+      </c>
+      <c r="D969" t="n">
+        <v>245407.53</v>
+      </c>
+      <c r="E969" t="n">
+        <v>162355.38</v>
+      </c>
+      <c r="F969" t="inlineStr"/>
+    </row>
+    <row r="970">
+      <c r="A970" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:02:15</t>
+        </is>
+      </c>
+      <c r="B970" t="n">
+        <v>153673.75</v>
+      </c>
+      <c r="C970" t="n">
+        <v>140765.16</v>
+      </c>
+      <c r="D970" t="n">
+        <v>245659.37</v>
+      </c>
+      <c r="E970" t="n">
+        <v>162386.69</v>
+      </c>
+      <c r="F970" t="inlineStr"/>
+    </row>
+    <row r="971">
+      <c r="A971" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:08:58</t>
+        </is>
+      </c>
+      <c r="B971" t="n">
+        <v>153524.68</v>
+      </c>
+      <c r="C971" t="n">
+        <v>140628.61</v>
+      </c>
+      <c r="D971" t="n">
+        <v>245043.25</v>
+      </c>
+      <c r="E971" t="n">
+        <v>162229.16</v>
+      </c>
+      <c r="F971" t="inlineStr"/>
+    </row>
+    <row r="972">
+      <c r="A972" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:09:11</t>
+        </is>
+      </c>
+      <c r="B972" t="n">
+        <v>153542.08</v>
+      </c>
+      <c r="C972" t="n">
+        <v>140644.55</v>
+      </c>
+      <c r="D972" t="n">
+        <v>245363.9</v>
+      </c>
+      <c r="E972" t="n">
+        <v>162247.55</v>
+      </c>
+      <c r="F972" t="inlineStr"/>
+    </row>
+    <row r="973">
+      <c r="A973" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:09:23</t>
+        </is>
+      </c>
+      <c r="B973" t="n">
+        <v>153592.47</v>
+      </c>
+      <c r="C973" t="n">
+        <v>140690.7</v>
+      </c>
+      <c r="D973" t="n">
+        <v>245097.19</v>
+      </c>
+      <c r="E973" t="n">
+        <v>162300.79</v>
+      </c>
+      <c r="F973" t="inlineStr"/>
+    </row>
+    <row r="974">
+      <c r="A974" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:09:36</t>
+        </is>
+      </c>
+      <c r="B974" t="n">
+        <v>153709.31</v>
+      </c>
+      <c r="C974" t="n">
+        <v>140797.73</v>
+      </c>
+      <c r="D974" t="n">
+        <v>246118.59</v>
+      </c>
+      <c r="E974" t="n">
+        <v>162424.26</v>
+      </c>
+      <c r="F974" t="inlineStr"/>
+    </row>
+    <row r="975">
+      <c r="A975" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:09:48</t>
+        </is>
+      </c>
+      <c r="B975" t="n">
+        <v>153818.94</v>
+      </c>
+      <c r="C975" t="n">
+        <v>140898.15</v>
+      </c>
+      <c r="D975" t="n">
+        <v>246400.06</v>
+      </c>
+      <c r="E975" t="n">
+        <v>162540.11</v>
+      </c>
+      <c r="F975" t="inlineStr"/>
+    </row>
+    <row r="976">
+      <c r="A976" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:09:59</t>
+        </is>
+      </c>
+      <c r="B976" t="n">
+        <v>153727.09</v>
+      </c>
+      <c r="C976" t="n">
+        <v>140814.02</v>
+      </c>
+      <c r="D976" t="n">
+        <v>246311.18</v>
+      </c>
+      <c r="E976" t="n">
+        <v>162443.05</v>
+      </c>
+      <c r="F976" t="inlineStr"/>
+    </row>
+    <row r="977">
+      <c r="A977" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:10:11</t>
+        </is>
+      </c>
+      <c r="B977" t="n">
+        <v>153710.58</v>
+      </c>
+      <c r="C977" t="n">
+        <v>140798.89</v>
+      </c>
+      <c r="D977" t="n">
+        <v>246073.2</v>
+      </c>
+      <c r="E977" t="n">
+        <v>162425.6</v>
+      </c>
+      <c r="F977" t="inlineStr"/>
+    </row>
+    <row r="978">
+      <c r="A978" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:10:24</t>
+        </is>
+      </c>
+      <c r="B978" t="n">
+        <v>153802.42</v>
+      </c>
+      <c r="C978" t="n">
+        <v>140883.01</v>
+      </c>
+      <c r="D978" t="n">
+        <v>246147.26</v>
+      </c>
+      <c r="E978" t="n">
+        <v>162522.64</v>
+      </c>
+      <c r="F978" t="inlineStr"/>
+    </row>
+    <row r="979">
+      <c r="A979" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:10:42</t>
+        </is>
+      </c>
+      <c r="B979" t="n">
+        <v>153827.99</v>
+      </c>
+      <c r="C979" t="n">
+        <v>140906.44</v>
+      </c>
+      <c r="D979" t="n">
+        <v>246292.48</v>
+      </c>
+      <c r="E979" t="n">
+        <v>162549.67</v>
+      </c>
+      <c r="F979" t="inlineStr"/>
+    </row>
+    <row r="980">
+      <c r="A980" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:10:54</t>
+        </is>
+      </c>
+      <c r="B980" t="n">
+        <v>153890.21</v>
+      </c>
+      <c r="C980" t="n">
+        <v>140963.43</v>
+      </c>
+      <c r="D980" t="n">
+        <v>246307.29</v>
+      </c>
+      <c r="E980" t="n">
+        <v>162615.42</v>
+      </c>
+      <c r="F980" t="inlineStr"/>
+    </row>
+    <row r="981">
+      <c r="A981" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:11:06</t>
+        </is>
+      </c>
+      <c r="B981" t="n">
+        <v>153883</v>
+      </c>
+      <c r="C981" t="n">
+        <v>140956.83</v>
+      </c>
+      <c r="D981" t="n">
+        <v>246783.98</v>
+      </c>
+      <c r="E981" t="n">
+        <v>162607.79</v>
+      </c>
+      <c r="F981" t="inlineStr"/>
+    </row>
+    <row r="982">
+      <c r="A982" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:11:17</t>
+        </is>
+      </c>
+      <c r="B982" t="n">
+        <v>153817.81</v>
+      </c>
+      <c r="C982" t="n">
+        <v>140897.12</v>
+      </c>
+      <c r="D982" t="n">
+        <v>246517.34</v>
+      </c>
+      <c r="E982" t="n">
+        <v>162538.92</v>
+      </c>
+      <c r="F982" t="inlineStr"/>
+    </row>
+    <row r="983">
+      <c r="A983" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:11:29</t>
+        </is>
+      </c>
+      <c r="B983" t="n">
+        <v>153791.15</v>
+      </c>
+      <c r="C983" t="n">
+        <v>140872.7</v>
+      </c>
+      <c r="D983" t="n">
+        <v>246309.96</v>
+      </c>
+      <c r="E983" t="n">
+        <v>162510.74</v>
+      </c>
+      <c r="F983" t="inlineStr"/>
+    </row>
+    <row r="984">
+      <c r="A984" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:11:43</t>
+        </is>
+      </c>
+      <c r="B984" t="n">
+        <v>153788.19</v>
+      </c>
+      <c r="C984" t="n">
+        <v>140869.98</v>
+      </c>
+      <c r="D984" t="n">
+        <v>246295.15</v>
+      </c>
+      <c r="E984" t="n">
+        <v>162507.61</v>
+      </c>
+      <c r="F984" t="inlineStr"/>
+    </row>
+    <row r="985">
+      <c r="A985" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:11:55</t>
+        </is>
+      </c>
+      <c r="B985" t="n">
+        <v>153699.31</v>
+      </c>
+      <c r="C985" t="n">
+        <v>140788.57</v>
+      </c>
+      <c r="D985" t="n">
+        <v>245910</v>
+      </c>
+      <c r="E985" t="n">
+        <v>162413.69</v>
+      </c>
+      <c r="F985" t="inlineStr"/>
+    </row>
+    <row r="986">
+      <c r="A986" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:12:10</t>
+        </is>
+      </c>
+      <c r="B986" t="n">
+        <v>153602.28</v>
+      </c>
+      <c r="C986" t="n">
+        <v>140699.69</v>
+      </c>
+      <c r="D986" t="n">
+        <v>245831.79</v>
+      </c>
+      <c r="E986" t="n">
+        <v>162311.17</v>
+      </c>
+      <c r="F986" t="inlineStr"/>
+    </row>
+    <row r="987">
+      <c r="A987" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:12:22</t>
+        </is>
+      </c>
+      <c r="B987" t="n">
+        <v>153560.81</v>
+      </c>
+      <c r="C987" t="n">
+        <v>140661.7</v>
+      </c>
+      <c r="D987" t="n">
+        <v>245639.23</v>
+      </c>
+      <c r="E987" t="n">
+        <v>162267.34</v>
+      </c>
+      <c r="F987" t="inlineStr"/>
+    </row>
+    <row r="988">
+      <c r="A988" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:12:34</t>
+        </is>
+      </c>
+      <c r="B988" t="n">
+        <v>153625.98</v>
+      </c>
+      <c r="C988" t="n">
+        <v>140721.4</v>
+      </c>
+      <c r="D988" t="n">
+        <v>246231.77</v>
+      </c>
+      <c r="E988" t="n">
+        <v>162336.2</v>
+      </c>
+      <c r="F988" t="inlineStr"/>
+    </row>
+    <row r="989">
+      <c r="A989" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:12:45</t>
+        </is>
+      </c>
+      <c r="B989" t="n">
+        <v>153643.76</v>
+      </c>
+      <c r="C989" t="n">
+        <v>140737.68</v>
+      </c>
+      <c r="D989" t="n">
+        <v>245994.74</v>
+      </c>
+      <c r="E989" t="n">
+        <v>162354.99</v>
+      </c>
+      <c r="F989" t="inlineStr"/>
+    </row>
+    <row r="990">
+      <c r="A990" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:12:57</t>
+        </is>
+      </c>
+      <c r="B990" t="n">
+        <v>153661.54</v>
+      </c>
+      <c r="C990" t="n">
+        <v>140753.97</v>
+      </c>
+      <c r="D990" t="n">
+        <v>246350.28</v>
+      </c>
+      <c r="E990" t="n">
+        <v>162373.78</v>
+      </c>
+      <c r="F990" t="inlineStr"/>
+    </row>
+    <row r="991">
+      <c r="A991" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:13:10</t>
+        </is>
+      </c>
+      <c r="B991" t="n">
+        <v>153718.78</v>
+      </c>
+      <c r="C991" t="n">
+        <v>140806.4</v>
+      </c>
+      <c r="D991" t="n">
+        <v>246192.42</v>
+      </c>
+      <c r="E991" t="n">
+        <v>162434.27</v>
+      </c>
+      <c r="F991" t="inlineStr"/>
+    </row>
+    <row r="992">
+      <c r="A992" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:13:24</t>
+        </is>
+      </c>
+      <c r="B992" t="n">
+        <v>153831.37</v>
+      </c>
+      <c r="C992" t="n">
+        <v>140909.54</v>
+      </c>
+      <c r="D992" t="n">
+        <v>246310.95</v>
+      </c>
+      <c r="E992" t="n">
+        <v>162553.24</v>
+      </c>
+      <c r="F992" t="inlineStr"/>
+    </row>
+    <row r="993">
+      <c r="A993" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:13:35</t>
+        </is>
+      </c>
+      <c r="B993" t="n">
+        <v>153857.67</v>
+      </c>
+      <c r="C993" t="n">
+        <v>140933.62</v>
+      </c>
+      <c r="D993" t="n">
+        <v>246305.61</v>
+      </c>
+      <c r="E993" t="n">
+        <v>162581.03</v>
+      </c>
+      <c r="F993" t="inlineStr"/>
+    </row>
+    <row r="994">
+      <c r="A994" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:13:47</t>
+        </is>
+      </c>
+      <c r="B994" t="n">
+        <v>153905.08</v>
+      </c>
+      <c r="C994" t="n">
+        <v>140977.05</v>
+      </c>
+      <c r="D994" t="n">
+        <v>246498.21</v>
+      </c>
+      <c r="E994" t="n">
+        <v>162631.13</v>
+      </c>
+      <c r="F994" t="inlineStr"/>
+    </row>
+    <row r="995">
+      <c r="A995" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:13:59</t>
+        </is>
+      </c>
+      <c r="B995" t="n">
+        <v>153931.75</v>
+      </c>
+      <c r="C995" t="n">
+        <v>141001.48</v>
+      </c>
+      <c r="D995" t="n">
+        <v>246483.38</v>
+      </c>
+      <c r="E995" t="n">
+        <v>162659.31</v>
+      </c>
+      <c r="F995" t="inlineStr"/>
+    </row>
+    <row r="996">
+      <c r="A996" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:14:11</t>
+        </is>
+      </c>
+      <c r="B996" t="n">
+        <v>153841.93</v>
+      </c>
+      <c r="C996" t="n">
+        <v>140919.2</v>
+      </c>
+      <c r="D996" t="n">
+        <v>246298.81</v>
+      </c>
+      <c r="E996" t="n">
+        <v>162564.39</v>
+      </c>
+      <c r="F996" t="inlineStr"/>
+    </row>
+    <row r="997">
+      <c r="A997" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:14:24</t>
+        </is>
+      </c>
+      <c r="B997" t="n">
+        <v>153895.27</v>
+      </c>
+      <c r="C997" t="n">
+        <v>140968.07</v>
+      </c>
+      <c r="D997" t="n">
+        <v>246506.23</v>
+      </c>
+      <c r="E997" t="n">
+        <v>162620.76</v>
+      </c>
+      <c r="F997" t="inlineStr"/>
+    </row>
+    <row r="998">
+      <c r="A998" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:14:36</t>
+        </is>
+      </c>
+      <c r="B998" t="n">
+        <v>153943.59</v>
+      </c>
+      <c r="C998" t="n">
+        <v>141012.33</v>
+      </c>
+      <c r="D998" t="n">
+        <v>247268.6</v>
+      </c>
+      <c r="E998" t="n">
+        <v>162671.83</v>
+      </c>
+      <c r="F998" t="inlineStr"/>
+    </row>
+    <row r="999">
+      <c r="A999" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:14:48</t>
+        </is>
+      </c>
+      <c r="B999" t="n">
+        <v>153863.6</v>
+      </c>
+      <c r="C999" t="n">
+        <v>140939.06</v>
+      </c>
+      <c r="D999" t="n">
+        <v>246690.8</v>
+      </c>
+      <c r="E999" t="n">
+        <v>162587.3</v>
+      </c>
+      <c r="F999" t="inlineStr"/>
+    </row>
+    <row r="1000">
+      <c r="A1000" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:15:00</t>
+        </is>
+      </c>
+      <c r="B1000" t="n">
+        <v>153786.56</v>
+      </c>
+      <c r="C1000" t="n">
+        <v>140868.49</v>
+      </c>
+      <c r="D1000" t="n">
+        <v>246661.18</v>
+      </c>
+      <c r="E1000" t="n">
+        <v>162505.89</v>
+      </c>
+      <c r="F1000" t="inlineStr"/>
+    </row>
+    <row r="1001">
+      <c r="A1001" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:15:12</t>
+        </is>
+      </c>
+      <c r="B1001" t="n">
+        <v>153722.83</v>
+      </c>
+      <c r="C1001" t="n">
+        <v>140810.11</v>
+      </c>
+      <c r="D1001" t="n">
+        <v>246476.81</v>
+      </c>
+      <c r="E1001" t="n">
+        <v>162438.54</v>
+      </c>
+      <c r="F1001" t="inlineStr"/>
+    </row>
+    <row r="1002">
+      <c r="A1002" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:15:27</t>
+        </is>
+      </c>
+      <c r="B1002" t="n">
+        <v>153719.86</v>
+      </c>
+      <c r="C1002" t="n">
+        <v>140807.39</v>
+      </c>
+      <c r="D1002" t="n">
+        <v>246684.21</v>
+      </c>
+      <c r="E1002" t="n">
+        <v>162435.41</v>
+      </c>
+      <c r="F1002" t="inlineStr"/>
+    </row>
+    <row r="1003">
+      <c r="A1003" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:15:44</t>
+        </is>
+      </c>
+      <c r="B1003" t="n">
+        <v>153757.09</v>
+      </c>
+      <c r="C1003" t="n">
+        <v>140841.49</v>
+      </c>
+      <c r="D1003" t="n">
+        <v>246449.85</v>
+      </c>
+      <c r="E1003" t="n">
+        <v>162474.75</v>
+      </c>
+      <c r="F1003" t="inlineStr"/>
+    </row>
+    <row r="1004">
+      <c r="A1004" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:15:55</t>
+        </is>
+      </c>
+      <c r="B1004" t="n">
+        <v>153691.9</v>
+      </c>
+      <c r="C1004" t="n">
+        <v>140781.78</v>
+      </c>
+      <c r="D1004" t="n">
+        <v>246523.92</v>
+      </c>
+      <c r="E1004" t="n">
+        <v>162405.86</v>
+      </c>
+      <c r="F1004" t="inlineStr"/>
+    </row>
+    <row r="1005">
+      <c r="A1005" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:16:09</t>
+        </is>
+      </c>
+      <c r="B1005" t="n">
+        <v>153623.59</v>
+      </c>
+      <c r="C1005" t="n">
+        <v>140719.21</v>
+      </c>
+      <c r="D1005" t="n">
+        <v>245964.86</v>
+      </c>
+      <c r="E1005" t="n">
+        <v>162333.68</v>
+      </c>
+      <c r="F1005" t="inlineStr"/>
+    </row>
+    <row r="1006">
+      <c r="A1006" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:16:24</t>
+        </is>
+      </c>
+      <c r="B1006" t="n">
+        <v>153602.84</v>
+      </c>
+      <c r="C1006" t="n">
+        <v>140700.2</v>
+      </c>
+      <c r="D1006" t="n">
+        <v>246024.11</v>
+      </c>
+      <c r="E1006" t="n">
+        <v>162311.75</v>
+      </c>
+      <c r="F1006" t="inlineStr"/>
+    </row>
+    <row r="1007">
+      <c r="A1007" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:16:36</t>
+        </is>
+      </c>
+      <c r="B1007" t="n">
+        <v>153447.27</v>
+      </c>
+      <c r="C1007" t="n">
+        <v>140557.7</v>
+      </c>
+      <c r="D1007" t="n">
+        <v>245630.59</v>
+      </c>
+      <c r="E1007" t="n">
+        <v>162147.36</v>
+      </c>
+      <c r="F1007" t="inlineStr"/>
+    </row>
+    <row r="1008">
+      <c r="A1008" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:16:50</t>
+        </is>
+      </c>
+      <c r="B1008" t="n">
+        <v>153518.38</v>
+      </c>
+      <c r="C1008" t="n">
+        <v>140622.84</v>
+      </c>
+      <c r="D1008" t="n">
+        <v>245912.11</v>
+      </c>
+      <c r="E1008" t="n">
+        <v>162222.51</v>
+      </c>
+      <c r="F1008" t="inlineStr"/>
+    </row>
+    <row r="1009">
+      <c r="A1009" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:17:03</t>
+        </is>
+      </c>
+      <c r="B1009" t="n">
+        <v>153460.78</v>
+      </c>
+      <c r="C1009" t="n">
+        <v>140570.07</v>
+      </c>
+      <c r="D1009" t="n">
+        <v>245618.45</v>
+      </c>
+      <c r="E1009" t="n">
+        <v>162161.64</v>
+      </c>
+      <c r="F1009" t="inlineStr"/>
+    </row>
+    <row r="1010">
+      <c r="A1010" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:17:22</t>
+        </is>
+      </c>
+      <c r="B1010" t="n">
+        <v>153528.93</v>
+      </c>
+      <c r="C1010" t="n">
+        <v>140632.5</v>
+      </c>
+      <c r="D1010" t="n">
+        <v>245618.45</v>
+      </c>
+      <c r="E1010" t="n">
+        <v>162233.65</v>
+      </c>
+      <c r="F1010" t="inlineStr"/>
+    </row>
+    <row r="1011">
+      <c r="A1011" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:17:34</t>
+        </is>
+      </c>
+      <c r="B1011" t="n">
+        <v>153558.92</v>
+      </c>
+      <c r="C1011" t="n">
+        <v>140659.97</v>
+      </c>
+      <c r="D1011" t="n">
+        <v>245740.53</v>
+      </c>
+      <c r="E1011" t="n">
+        <v>162265.35</v>
+      </c>
+      <c r="F1011" t="inlineStr"/>
+    </row>
+    <row r="1012">
+      <c r="A1012" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:17:48</t>
+        </is>
+      </c>
+      <c r="B1012" t="n">
+        <v>153496.68</v>
+      </c>
+      <c r="C1012" t="n">
+        <v>140602.96</v>
+      </c>
+      <c r="D1012" t="n">
+        <v>245562.68</v>
+      </c>
+      <c r="E1012" t="n">
+        <v>162199.57</v>
+      </c>
+      <c r="F1012" t="inlineStr"/>
+    </row>
+    <row r="1013">
+      <c r="A1013" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:18:04</t>
+        </is>
+      </c>
+      <c r="B1013" t="n">
+        <v>153455.96</v>
+      </c>
+      <c r="C1013" t="n">
+        <v>140565.66</v>
+      </c>
+      <c r="D1013" t="n">
+        <v>245456.62</v>
+      </c>
+      <c r="E1013" t="n">
+        <v>162156.54</v>
+      </c>
+      <c r="F1013" t="inlineStr"/>
+    </row>
+    <row r="1014">
+      <c r="A1014" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:18:19</t>
+        </is>
+      </c>
+      <c r="B1014" t="n">
+        <v>153583.39</v>
+      </c>
+      <c r="C1014" t="n">
+        <v>140682.38</v>
+      </c>
+      <c r="D1014" t="n">
+        <v>245841.89</v>
+      </c>
+      <c r="E1014" t="n">
+        <v>162291.2</v>
+      </c>
+      <c r="F1014" t="inlineStr"/>
+    </row>
+    <row r="1015">
+      <c r="A1015" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:18:36</t>
+        </is>
+      </c>
+      <c r="B1015" t="n">
+        <v>153617.83</v>
+      </c>
+      <c r="C1015" t="n">
+        <v>140713.93</v>
+      </c>
+      <c r="D1015" t="n">
+        <v>245868.55</v>
+      </c>
+      <c r="E1015" t="n">
+        <v>162327.59</v>
+      </c>
+      <c r="F1015" t="inlineStr"/>
+    </row>
+    <row r="1016">
+      <c r="A1016" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:18:48</t>
+        </is>
+      </c>
+      <c r="B1016" t="n">
+        <v>153389.6</v>
+      </c>
+      <c r="C1016" t="n">
+        <v>140504.87</v>
+      </c>
+      <c r="D1016" t="n">
+        <v>244949.73</v>
+      </c>
+      <c r="E1016" t="n">
+        <v>162086.42</v>
+      </c>
+      <c r="F1016" t="inlineStr"/>
+    </row>
+    <row r="1017">
+      <c r="A1017" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:19:00</t>
+        </is>
+      </c>
+      <c r="B1017" t="n">
+        <v>153448.88</v>
+      </c>
+      <c r="C1017" t="n">
+        <v>140559.17</v>
+      </c>
+      <c r="D1017" t="n">
+        <v>245305.41</v>
+      </c>
+      <c r="E1017" t="n">
+        <v>162149.06</v>
+      </c>
+      <c r="F1017" t="inlineStr"/>
+    </row>
+    <row r="1018">
+      <c r="A1018" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:19:14</t>
+        </is>
+      </c>
+      <c r="B1018" t="n">
+        <v>153460.01</v>
+      </c>
+      <c r="C1018" t="n">
+        <v>140569.37</v>
+      </c>
+      <c r="D1018" t="n">
+        <v>245531.87</v>
+      </c>
+      <c r="E1018" t="n">
+        <v>162160.82</v>
+      </c>
+      <c r="F1018" t="inlineStr"/>
+    </row>
+    <row r="1019">
+      <c r="A1019" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:19:26</t>
+        </is>
+      </c>
+      <c r="B1019" t="n">
+        <v>153344.43</v>
+      </c>
+      <c r="C1019" t="n">
+        <v>140463.49</v>
+      </c>
+      <c r="D1019" t="n">
+        <v>245220.67</v>
+      </c>
+      <c r="E1019" t="n">
+        <v>162038.69</v>
+      </c>
+      <c r="F1019" t="inlineStr"/>
+    </row>
+    <row r="1020">
+      <c r="A1020" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:19:38</t>
+        </is>
+      </c>
+      <c r="B1020" t="n">
+        <v>153425.34</v>
+      </c>
+      <c r="C1020" t="n">
+        <v>140537.61</v>
+      </c>
+      <c r="D1020" t="n">
+        <v>245373.82</v>
+      </c>
+      <c r="E1020" t="n">
+        <v>162124.18</v>
+      </c>
+      <c r="F1020" t="inlineStr"/>
+    </row>
+    <row r="1021">
+      <c r="A1021" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:19:50</t>
+        </is>
+      </c>
+      <c r="B1021" t="n">
+        <v>153185.23</v>
+      </c>
+      <c r="C1021" t="n">
+        <v>140317.68</v>
+      </c>
+      <c r="D1021" t="n">
+        <v>245359.01</v>
+      </c>
+      <c r="E1021" t="n">
+        <v>161870.47</v>
+      </c>
+      <c r="F1021" t="inlineStr"/>
+    </row>
+    <row r="1022">
+      <c r="A1022" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:20:01</t>
+        </is>
+      </c>
+      <c r="B1022" t="n">
+        <v>153155.59</v>
+      </c>
+      <c r="C1022" t="n">
+        <v>140290.52</v>
+      </c>
+      <c r="D1022" t="n">
+        <v>245270.09</v>
+      </c>
+      <c r="E1022" t="n">
+        <v>161839.15</v>
+      </c>
+      <c r="F1022" t="inlineStr"/>
+    </row>
+    <row r="1023">
+      <c r="A1023" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:20:13</t>
+        </is>
+      </c>
+      <c r="B1023" t="n">
+        <v>153011.19</v>
+      </c>
+      <c r="C1023" t="n">
+        <v>140158.25</v>
+      </c>
+      <c r="D1023" t="n">
+        <v>244882.5</v>
+      </c>
+      <c r="E1023" t="n">
+        <v>161686.55</v>
+      </c>
+      <c r="F1023" t="inlineStr"/>
+    </row>
+    <row r="1024">
+      <c r="A1024" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:20:24</t>
+        </is>
+      </c>
+      <c r="B1024" t="n">
+        <v>153043.78</v>
+      </c>
+      <c r="C1024" t="n">
+        <v>140188.1</v>
+      </c>
+      <c r="D1024" t="n">
+        <v>244512.03</v>
+      </c>
+      <c r="E1024" t="n">
+        <v>161720.99</v>
+      </c>
+      <c r="F1024" t="inlineStr"/>
+    </row>
+    <row r="1025">
+      <c r="A1025" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:20:36</t>
+        </is>
+      </c>
+      <c r="B1025" t="n">
+        <v>153162.33</v>
+      </c>
+      <c r="C1025" t="n">
+        <v>140296.69</v>
+      </c>
+      <c r="D1025" t="n">
+        <v>244852.86</v>
+      </c>
+      <c r="E1025" t="n">
+        <v>161846.26</v>
+      </c>
+      <c r="F1025" t="inlineStr"/>
+    </row>
+    <row r="1026">
+      <c r="A1026" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:20:48</t>
+        </is>
+      </c>
+      <c r="B1026" t="n">
+        <v>153046.74</v>
+      </c>
+      <c r="C1026" t="n">
+        <v>140190.82</v>
+      </c>
+      <c r="D1026" t="n">
+        <v>244867.69</v>
+      </c>
+      <c r="E1026" t="n">
+        <v>161724.13</v>
+      </c>
+      <c r="F1026" t="inlineStr"/>
+    </row>
+    <row r="1027">
+      <c r="A1027" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:21:00</t>
+        </is>
+      </c>
+      <c r="B1027" t="n">
+        <v>152996.37</v>
+      </c>
+      <c r="C1027" t="n">
+        <v>140144.67</v>
+      </c>
+      <c r="D1027" t="n">
+        <v>244704.68</v>
+      </c>
+      <c r="E1027" t="n">
+        <v>161670.89</v>
+      </c>
+      <c r="F1027" t="inlineStr"/>
+    </row>
+    <row r="1028">
+      <c r="A1028" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:21:11</t>
+        </is>
+      </c>
+      <c r="B1028" t="n">
+        <v>153098.44</v>
+      </c>
+      <c r="C1028" t="n">
+        <v>140238.17</v>
+      </c>
+      <c r="D1028" t="n">
+        <v>245013.21</v>
+      </c>
+      <c r="E1028" t="n">
+        <v>161778.75</v>
+      </c>
+      <c r="F1028" t="inlineStr"/>
+    </row>
+    <row r="1029">
+      <c r="A1029" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:21:23</t>
+        </is>
+      </c>
+      <c r="B1029" t="n">
+        <v>153110.29</v>
+      </c>
+      <c r="C1029" t="n">
+        <v>140249.03</v>
+      </c>
+      <c r="D1029" t="n">
+        <v>244924.3</v>
+      </c>
+      <c r="E1029" t="n">
+        <v>161791.28</v>
+      </c>
+      <c r="F1029" t="inlineStr"/>
+    </row>
+    <row r="1030">
+      <c r="A1030" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:21:35</t>
+        </is>
+      </c>
+      <c r="B1030" t="n">
+        <v>153042.12</v>
+      </c>
+      <c r="C1030" t="n">
+        <v>140186.58</v>
+      </c>
+      <c r="D1030" t="n">
+        <v>245042.85</v>
+      </c>
+      <c r="E1030" t="n">
+        <v>161719.24</v>
+      </c>
+      <c r="F1030" t="inlineStr"/>
+    </row>
+    <row r="1031">
+      <c r="A1031" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:21:47</t>
+        </is>
+      </c>
+      <c r="B1031" t="n">
+        <v>153080.66</v>
+      </c>
+      <c r="C1031" t="n">
+        <v>140221.88</v>
+      </c>
+      <c r="D1031" t="n">
+        <v>245013.21</v>
+      </c>
+      <c r="E1031" t="n">
+        <v>161759.96</v>
+      </c>
+      <c r="F1031" t="inlineStr"/>
+    </row>
+    <row r="1032">
+      <c r="A1032" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:21:59</t>
+        </is>
+      </c>
+      <c r="B1032" t="n">
+        <v>153160.67</v>
+      </c>
+      <c r="C1032" t="n">
+        <v>140295.17</v>
+      </c>
+      <c r="D1032" t="n">
+        <v>245354.06</v>
+      </c>
+      <c r="E1032" t="n">
+        <v>161844.51</v>
+      </c>
+      <c r="F1032" t="inlineStr"/>
+    </row>
+    <row r="1033">
+      <c r="A1033" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:22:11</t>
+        </is>
+      </c>
+      <c r="B1033" t="n">
+        <v>153175.49</v>
+      </c>
+      <c r="C1033" t="n">
+        <v>140308.75</v>
+      </c>
+      <c r="D1033" t="n">
+        <v>245368.87</v>
+      </c>
+      <c r="E1033" t="n">
+        <v>161860.17</v>
+      </c>
+      <c r="F1033" t="inlineStr"/>
+    </row>
+    <row r="1034">
+      <c r="A1034" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:22:23</t>
+        </is>
+      </c>
+      <c r="B1034" t="n">
+        <v>153136.96</v>
+      </c>
+      <c r="C1034" t="n">
+        <v>140273.46</v>
+      </c>
+      <c r="D1034" t="n">
+        <v>245161.41</v>
+      </c>
+      <c r="E1034" t="n">
+        <v>161819.46</v>
+      </c>
+      <c r="F1034" t="inlineStr"/>
+    </row>
+    <row r="1035">
+      <c r="A1035" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:22:34</t>
+        </is>
+      </c>
+      <c r="B1035" t="n">
+        <v>153145.85</v>
+      </c>
+      <c r="C1035" t="n">
+        <v>140281.6</v>
+      </c>
+      <c r="D1035" t="n">
+        <v>245161.41</v>
+      </c>
+      <c r="E1035" t="n">
+        <v>161828.85</v>
+      </c>
+      <c r="F1035" t="inlineStr"/>
+    </row>
+    <row r="1036">
+      <c r="A1036" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:22:46</t>
+        </is>
+      </c>
+      <c r="B1036" t="n">
+        <v>153151.78</v>
+      </c>
+      <c r="C1036" t="n">
+        <v>140287.03</v>
+      </c>
+      <c r="D1036" t="n">
+        <v>245354.06</v>
+      </c>
+      <c r="E1036" t="n">
+        <v>161835.12</v>
+      </c>
+      <c r="F1036" t="inlineStr"/>
+    </row>
+    <row r="1037">
+      <c r="A1037" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:22:58</t>
+        </is>
+      </c>
+      <c r="B1037" t="n">
+        <v>153080.66</v>
+      </c>
+      <c r="C1037" t="n">
+        <v>140221.88</v>
+      </c>
+      <c r="D1037" t="n">
+        <v>245176.22</v>
+      </c>
+      <c r="E1037" t="n">
+        <v>161759.96</v>
+      </c>
+      <c r="F1037" t="inlineStr"/>
+    </row>
+    <row r="1038">
+      <c r="A1038" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:23:10</t>
+        </is>
+      </c>
+      <c r="B1038" t="n">
+        <v>153071.76</v>
+      </c>
+      <c r="C1038" t="n">
+        <v>140213.73</v>
+      </c>
+      <c r="D1038" t="n">
+        <v>245339.22</v>
+      </c>
+      <c r="E1038" t="n">
+        <v>161750.56</v>
+      </c>
+      <c r="F1038" t="inlineStr"/>
+    </row>
+    <row r="1039">
+      <c r="A1039" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:23:22</t>
+        </is>
+      </c>
+      <c r="B1039" t="n">
+        <v>153045.08</v>
+      </c>
+      <c r="C1039" t="n">
+        <v>140189.3</v>
+      </c>
+      <c r="D1039" t="n">
+        <v>245279.96</v>
+      </c>
+      <c r="E1039" t="n">
+        <v>161722.37</v>
+      </c>
+      <c r="F1039" t="inlineStr"/>
+    </row>
+    <row r="1040">
+      <c r="A1040" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:23:33</t>
+        </is>
+      </c>
+      <c r="B1040" t="n">
+        <v>152956.17</v>
+      </c>
+      <c r="C1040" t="n">
+        <v>140107.85</v>
+      </c>
+      <c r="D1040" t="n">
+        <v>244672.38</v>
+      </c>
+      <c r="E1040" t="n">
+        <v>161628.42</v>
+      </c>
+      <c r="F1040" t="inlineStr"/>
+    </row>
+    <row r="1041">
+      <c r="A1041" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:23:45</t>
+        </is>
+      </c>
+      <c r="B1041" t="n">
+        <v>152920.62</v>
+      </c>
+      <c r="C1041" t="n">
+        <v>140075.28</v>
+      </c>
+      <c r="D1041" t="n">
+        <v>244509.38</v>
+      </c>
+      <c r="E1041" t="n">
+        <v>161590.85</v>
+      </c>
+      <c r="F1041" t="inlineStr"/>
+    </row>
+    <row r="1042">
+      <c r="A1042" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:23:57</t>
+        </is>
+      </c>
+      <c r="B1042" t="n">
+        <v>152932.47</v>
+      </c>
+      <c r="C1042" t="n">
+        <v>140086.14</v>
+      </c>
+      <c r="D1042" t="n">
+        <v>244450.11</v>
+      </c>
+      <c r="E1042" t="n">
+        <v>161603.37</v>
+      </c>
+      <c r="F1042" t="inlineStr"/>
+    </row>
+    <row r="1043">
+      <c r="A1043" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:24:10</t>
+        </is>
+      </c>
+      <c r="B1043" t="n">
+        <v>152896.9</v>
+      </c>
+      <c r="C1043" t="n">
+        <v>140053.56</v>
+      </c>
+      <c r="D1043" t="n">
+        <v>244094.45</v>
+      </c>
+      <c r="E1043" t="n">
+        <v>161565.78</v>
+      </c>
+      <c r="F1043" t="inlineStr"/>
+    </row>
+    <row r="1044">
+      <c r="A1044" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:24:22</t>
+        </is>
+      </c>
+      <c r="B1044" t="n">
+        <v>153056.94</v>
+      </c>
+      <c r="C1044" t="n">
+        <v>140200.15</v>
+      </c>
+      <c r="D1044" t="n">
+        <v>244509.38</v>
+      </c>
+      <c r="E1044" t="n">
+        <v>161734.9</v>
+      </c>
+      <c r="F1044" t="inlineStr"/>
+    </row>
+    <row r="1045">
+      <c r="A1045" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:24:33</t>
+        </is>
+      </c>
+      <c r="B1045" t="n">
+        <v>153033.23</v>
+      </c>
+      <c r="C1045" t="n">
+        <v>140178.44</v>
+      </c>
+      <c r="D1045" t="n">
+        <v>244657.57</v>
+      </c>
+      <c r="E1045" t="n">
+        <v>161709.85</v>
+      </c>
+      <c r="F1045" t="inlineStr"/>
+    </row>
+    <row r="1046">
+      <c r="A1046" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:24:45</t>
+        </is>
+      </c>
+      <c r="B1046" t="n">
+        <v>153154.75</v>
+      </c>
+      <c r="C1046" t="n">
+        <v>140289.75</v>
+      </c>
+      <c r="D1046" t="n">
+        <v>245205.86</v>
+      </c>
+      <c r="E1046" t="n">
+        <v>161838.26</v>
+      </c>
+      <c r="F1046" t="inlineStr"/>
+    </row>
+    <row r="1047">
+      <c r="A1047" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:24:57</t>
+        </is>
+      </c>
+      <c r="B1047" t="n">
+        <v>153145.85</v>
+      </c>
+      <c r="C1047" t="n">
+        <v>140281.6</v>
+      </c>
+      <c r="D1047" t="n">
+        <v>244983.59</v>
+      </c>
+      <c r="E1047" t="n">
+        <v>161828.85</v>
+      </c>
+      <c r="F1047" t="inlineStr"/>
+    </row>
+    <row r="1048">
+      <c r="A1048" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:25:09</t>
+        </is>
+      </c>
+      <c r="B1048" t="n">
+        <v>153077.69</v>
+      </c>
+      <c r="C1048" t="n">
+        <v>140219.16</v>
+      </c>
+      <c r="D1048" t="n">
+        <v>244657.57</v>
+      </c>
+      <c r="E1048" t="n">
+        <v>161756.83</v>
+      </c>
+      <c r="F1048" t="inlineStr"/>
+    </row>
+    <row r="1049">
+      <c r="A1049" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:25:20</t>
+        </is>
+      </c>
+      <c r="B1049" t="n">
+        <v>152953.21</v>
+      </c>
+      <c r="C1049" t="n">
+        <v>140105.14</v>
+      </c>
+      <c r="D1049" t="n">
+        <v>244020.35</v>
+      </c>
+      <c r="E1049" t="n">
+        <v>161625.28</v>
+      </c>
+      <c r="F1049" t="inlineStr"/>
+    </row>
+    <row r="1050">
+      <c r="A1050" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:25:32</t>
+        </is>
+      </c>
+      <c r="B1050" t="n">
+        <v>153036.2</v>
+      </c>
+      <c r="C1050" t="n">
+        <v>140181.16</v>
+      </c>
+      <c r="D1050" t="n">
+        <v>244168.55</v>
+      </c>
+      <c r="E1050" t="n">
+        <v>161712.98</v>
+      </c>
+      <c r="F1050" t="inlineStr"/>
+    </row>
+    <row r="1051">
+      <c r="A1051" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:25:44</t>
+        </is>
+      </c>
+      <c r="B1051" t="n">
+        <v>152888.01</v>
+      </c>
+      <c r="C1051" t="n">
+        <v>140045.42</v>
+      </c>
+      <c r="D1051" t="n">
+        <v>243886.99</v>
+      </c>
+      <c r="E1051" t="n">
+        <v>161556.39</v>
+      </c>
+      <c r="F1051" t="inlineStr"/>
+    </row>
+    <row r="1052">
+      <c r="A1052" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:25:55</t>
+        </is>
+      </c>
+      <c r="B1052" t="n">
+        <v>152606.46</v>
+      </c>
+      <c r="C1052" t="n">
+        <v>139787.51</v>
+      </c>
+      <c r="D1052" t="n">
+        <v>243146.05</v>
+      </c>
+      <c r="E1052" t="n">
+        <v>161258.87</v>
+      </c>
+      <c r="F1052" t="inlineStr"/>
+    </row>
+    <row r="1053">
+      <c r="A1053" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:26:07</t>
+        </is>
+      </c>
+      <c r="B1053" t="n">
+        <v>152588.67</v>
+      </c>
+      <c r="C1053" t="n">
+        <v>139771.22</v>
+      </c>
+      <c r="D1053" t="n">
+        <v>243175.7</v>
+      </c>
+      <c r="E1053" t="n">
+        <v>161240.08</v>
+      </c>
+      <c r="F1053" t="inlineStr"/>
+    </row>
+    <row r="1054">
+      <c r="A1054" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:26:19</t>
+        </is>
+      </c>
+      <c r="B1054" t="n">
+        <v>152745.74</v>
+      </c>
+      <c r="C1054" t="n">
+        <v>139915.1</v>
+      </c>
+      <c r="D1054" t="n">
+        <v>243753.63</v>
+      </c>
+      <c r="E1054" t="n">
+        <v>161406.06</v>
+      </c>
+      <c r="F1054" t="inlineStr"/>
+    </row>
+    <row r="1055">
+      <c r="A1055" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:26:31</t>
+        </is>
+      </c>
+      <c r="B1055" t="n">
+        <v>152562</v>
+      </c>
+      <c r="C1055" t="n">
+        <v>139746.79</v>
+      </c>
+      <c r="D1055" t="n">
+        <v>243264.61</v>
+      </c>
+      <c r="E1055" t="n">
+        <v>161211.9</v>
+      </c>
+      <c r="F1055" t="inlineStr"/>
+    </row>
+    <row r="1056">
+      <c r="A1056" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:26:42</t>
+        </is>
+      </c>
+      <c r="B1056" t="n">
+        <v>152579.78</v>
+      </c>
+      <c r="C1056" t="n">
+        <v>139763.08</v>
+      </c>
+      <c r="D1056" t="n">
+        <v>243249.77</v>
+      </c>
+      <c r="E1056" t="n">
+        <v>161230.69</v>
+      </c>
+      <c r="F1056" t="inlineStr"/>
+    </row>
+    <row r="1057">
+      <c r="A1057" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:26:54</t>
+        </is>
+      </c>
+      <c r="B1057" t="n">
+        <v>152659.8</v>
+      </c>
+      <c r="C1057" t="n">
+        <v>139836.37</v>
+      </c>
+      <c r="D1057" t="n">
+        <v>243457.24</v>
+      </c>
+      <c r="E1057" t="n">
+        <v>161315.24</v>
+      </c>
+      <c r="F1057" t="inlineStr"/>
+    </row>
+    <row r="1058">
+      <c r="A1058" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:27:06</t>
+        </is>
+      </c>
+      <c r="B1058" t="n">
+        <v>152562</v>
+      </c>
+      <c r="C1058" t="n">
+        <v>139746.79</v>
+      </c>
+      <c r="D1058" t="n">
+        <v>243457.24</v>
+      </c>
+      <c r="E1058" t="n">
+        <v>161211.9</v>
+      </c>
+      <c r="F1058" t="inlineStr"/>
+    </row>
+    <row r="1059">
+      <c r="A1059" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:27:17</t>
+        </is>
+      </c>
+      <c r="B1059" t="n">
+        <v>152419.73</v>
+      </c>
+      <c r="C1059" t="n">
+        <v>139616.47</v>
+      </c>
+      <c r="D1059" t="n">
+        <v>243027.5</v>
+      </c>
+      <c r="E1059" t="n">
+        <v>161061.56</v>
+      </c>
+      <c r="F1059" t="inlineStr"/>
+    </row>
+    <row r="1060">
+      <c r="A1060" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:27:29</t>
+        </is>
+      </c>
+      <c r="B1060" t="n">
+        <v>152390.09</v>
+      </c>
+      <c r="C1060" t="n">
+        <v>139589.32</v>
+      </c>
+      <c r="D1060" t="n">
+        <v>242953.4</v>
+      </c>
+      <c r="E1060" t="n">
+        <v>161030.25</v>
+      </c>
+      <c r="F1060" t="inlineStr"/>
+    </row>
+    <row r="1061">
+      <c r="A1061" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:27:41</t>
+        </is>
+      </c>
+      <c r="B1061" t="n">
+        <v>152339.72</v>
+      </c>
+      <c r="C1061" t="n">
+        <v>139543.18</v>
+      </c>
+      <c r="D1061" t="n">
+        <v>242834.85</v>
+      </c>
+      <c r="E1061" t="n">
+        <v>160977.01</v>
+      </c>
+      <c r="F1061" t="inlineStr"/>
+    </row>
+    <row r="1062">
+      <c r="A1062" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:27:52</t>
+        </is>
+      </c>
+      <c r="B1062" t="n">
+        <v>152461.23</v>
+      </c>
+      <c r="C1062" t="n">
+        <v>139654.49</v>
+      </c>
+      <c r="D1062" t="n">
+        <v>242983.05</v>
+      </c>
+      <c r="E1062" t="n">
+        <v>161105.42</v>
+      </c>
+      <c r="F1062" t="inlineStr"/>
+    </row>
+    <row r="1063">
+      <c r="A1063" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:28:04</t>
+        </is>
+      </c>
+      <c r="B1063" t="n">
+        <v>152390.09</v>
+      </c>
+      <c r="C1063" t="n">
+        <v>139589.32</v>
+      </c>
+      <c r="D1063" t="n">
+        <v>242597.77</v>
+      </c>
+      <c r="E1063" t="n">
+        <v>161030.25</v>
+      </c>
+      <c r="F1063" t="inlineStr"/>
+    </row>
+    <row r="1064">
+      <c r="A1064" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:28:16</t>
+        </is>
+      </c>
+      <c r="B1064" t="n">
+        <v>152461.23</v>
+      </c>
+      <c r="C1064" t="n">
+        <v>139654.49</v>
+      </c>
+      <c r="D1064" t="n">
+        <v>242745.94</v>
+      </c>
+      <c r="E1064" t="n">
+        <v>161105.42</v>
+      </c>
+      <c r="F1064" t="inlineStr"/>
+    </row>
+    <row r="1065">
+      <c r="A1065" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:28:27</t>
+        </is>
+      </c>
+      <c r="B1065" t="n">
+        <v>152630.16</v>
+      </c>
+      <c r="C1065" t="n">
+        <v>139809.23</v>
+      </c>
+      <c r="D1065" t="n">
+        <v>243249.77</v>
+      </c>
+      <c r="E1065" t="n">
+        <v>161283.92</v>
+      </c>
+      <c r="F1065" t="inlineStr"/>
+    </row>
+    <row r="1066">
+      <c r="A1066" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:28:39</t>
+        </is>
+      </c>
+      <c r="B1066" t="n">
+        <v>152610.72</v>
+      </c>
+      <c r="C1066" t="n">
+        <v>139791.42</v>
+      </c>
+      <c r="D1066" t="n">
+        <v>243098.96</v>
+      </c>
+      <c r="E1066" t="n">
+        <v>161263.38</v>
+      </c>
+      <c r="F1066" t="inlineStr"/>
+    </row>
+    <row r="1067">
+      <c r="A1067" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:29:27</t>
+        </is>
+      </c>
+      <c r="B1067" t="n">
+        <v>152895.35</v>
+      </c>
+      <c r="C1067" t="n">
+        <v>140052.14</v>
+      </c>
+      <c r="D1067" t="n">
+        <v>244086</v>
+      </c>
+      <c r="E1067" t="n">
+        <v>161564.15</v>
+      </c>
+      <c r="F1067" t="inlineStr"/>
+    </row>
+    <row r="1068">
+      <c r="A1068" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:29:40</t>
+        </is>
+      </c>
+      <c r="B1068" t="n">
+        <v>152951.66</v>
+      </c>
+      <c r="C1068" t="n">
+        <v>140103.72</v>
+      </c>
+      <c r="D1068" t="n">
+        <v>244071.19</v>
+      </c>
+      <c r="E1068" t="n">
+        <v>161623.66</v>
+      </c>
+      <c r="F1068" t="inlineStr"/>
+    </row>
+    <row r="1069">
+      <c r="A1069" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:29:52</t>
+        </is>
+      </c>
+      <c r="B1069" t="n">
+        <v>152901.28</v>
+      </c>
+      <c r="C1069" t="n">
+        <v>140057.58</v>
+      </c>
+      <c r="D1069" t="n">
+        <v>243937.81</v>
+      </c>
+      <c r="E1069" t="n">
+        <v>161570.42</v>
+      </c>
+      <c r="F1069" t="inlineStr"/>
+    </row>
+    <row r="1070">
+      <c r="A1070" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:30:03</t>
+        </is>
+      </c>
+      <c r="B1070" t="n">
+        <v>152888.12</v>
+      </c>
+      <c r="C1070" t="n">
+        <v>140045.52</v>
+      </c>
+      <c r="D1070" t="n">
+        <v>243866.35</v>
+      </c>
+      <c r="E1070" t="n">
+        <v>161556.51</v>
+      </c>
+      <c r="F1070" t="inlineStr"/>
+    </row>
+    <row r="1071">
+      <c r="A1071" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:30:14</t>
+        </is>
+      </c>
+      <c r="B1071" t="n">
+        <v>152888.12</v>
+      </c>
+      <c r="C1071" t="n">
+        <v>140045.52</v>
+      </c>
+      <c r="D1071" t="n">
+        <v>243821.89</v>
+      </c>
+      <c r="E1071" t="n">
+        <v>161556.51</v>
+      </c>
+      <c r="F1071" t="inlineStr"/>
+    </row>
+    <row r="1072">
+      <c r="A1072" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:30:26</t>
+        </is>
+      </c>
+      <c r="B1072" t="n">
+        <v>152911.83</v>
+      </c>
+      <c r="C1072" t="n">
+        <v>140067.24</v>
+      </c>
+      <c r="D1072" t="n">
+        <v>244059</v>
+      </c>
+      <c r="E1072" t="n">
+        <v>161581.56</v>
+      </c>
+      <c r="F1072" t="inlineStr"/>
+    </row>
+    <row r="1073">
+      <c r="A1073" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:30:37</t>
+        </is>
+      </c>
+      <c r="B1073" t="n">
+        <v>152989.13</v>
+      </c>
+      <c r="C1073" t="n">
+        <v>140138.04</v>
+      </c>
+      <c r="D1073" t="n">
+        <v>244366.48</v>
+      </c>
+      <c r="E1073" t="n">
+        <v>161663.24</v>
+      </c>
+      <c r="F1073" t="inlineStr"/>
+    </row>
+    <row r="1074">
+      <c r="A1074" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:30:51</t>
+        </is>
+      </c>
+      <c r="B1074" t="n">
+        <v>152897.25</v>
+      </c>
+      <c r="C1074" t="n">
+        <v>140053.88</v>
+      </c>
+      <c r="D1074" t="n">
+        <v>243773.72</v>
+      </c>
+      <c r="E1074" t="n">
+        <v>161566.15</v>
+      </c>
+      <c r="F1074" t="inlineStr"/>
+    </row>
+    <row r="1075">
+      <c r="A1075" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:31:01</t>
+        </is>
+      </c>
+      <c r="B1075" t="n">
+        <v>152912.06</v>
+      </c>
+      <c r="C1075" t="n">
+        <v>140067.45</v>
+      </c>
+      <c r="D1075" t="n">
+        <v>243847.82</v>
+      </c>
+      <c r="E1075" t="n">
+        <v>161581.81</v>
+      </c>
+      <c r="F1075" t="inlineStr"/>
+    </row>
+    <row r="1076">
+      <c r="A1076" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:31:12</t>
+        </is>
+      </c>
+      <c r="B1076" t="n">
+        <v>152815.23</v>
+      </c>
+      <c r="C1076" t="n">
+        <v>139978.75</v>
+      </c>
+      <c r="D1076" t="n">
+        <v>243617.6</v>
+      </c>
+      <c r="E1076" t="n">
+        <v>161479.48</v>
+      </c>
+      <c r="F1076" t="inlineStr"/>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:31:24</t>
+        </is>
+      </c>
+      <c r="B1077" t="n">
+        <v>152827.08</v>
+      </c>
+      <c r="C1077" t="n">
+        <v>139989.6</v>
+      </c>
+      <c r="D1077" t="n">
+        <v>243662.05</v>
+      </c>
+      <c r="E1077" t="n">
+        <v>161492.01</v>
+      </c>
+      <c r="F1077" t="inlineStr"/>
+    </row>
+    <row r="1078">
+      <c r="A1078" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:31:35</t>
+        </is>
+      </c>
+      <c r="B1078" t="n">
+        <v>152740.43</v>
+      </c>
+      <c r="C1078" t="n">
+        <v>139910.23</v>
+      </c>
+      <c r="D1078" t="n">
+        <v>243310.68</v>
+      </c>
+      <c r="E1078" t="n">
+        <v>161400.44</v>
+      </c>
+      <c r="F1078" t="inlineStr"/>
+    </row>
+    <row r="1079">
+      <c r="A1079" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:31:47</t>
+        </is>
+      </c>
+      <c r="B1079" t="n">
+        <v>152580.4</v>
+      </c>
+      <c r="C1079" t="n">
+        <v>139763.64</v>
+      </c>
+      <c r="D1079" t="n">
+        <v>243058.78</v>
+      </c>
+      <c r="E1079" t="n">
+        <v>161231.34</v>
+      </c>
+      <c r="F1079" t="inlineStr"/>
+    </row>
+    <row r="1080">
+      <c r="A1080" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:31:58</t>
+        </is>
+      </c>
+      <c r="B1080" t="n">
+        <v>152535.94</v>
+      </c>
+      <c r="C1080" t="n">
+        <v>139722.92</v>
+      </c>
+      <c r="D1080" t="n">
+        <v>243058.78</v>
+      </c>
+      <c r="E1080" t="n">
+        <v>161184.37</v>
+      </c>
+      <c r="F1080" t="inlineStr"/>
+    </row>
+    <row r="1081">
+      <c r="A1081" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:32:10</t>
+        </is>
+      </c>
+      <c r="B1081" t="n">
+        <v>152510.65</v>
+      </c>
+      <c r="C1081" t="n">
+        <v>139699.76</v>
+      </c>
+      <c r="D1081" t="n">
+        <v>243316.98</v>
+      </c>
+      <c r="E1081" t="n">
+        <v>161157.64</v>
+      </c>
+      <c r="F1081" t="inlineStr"/>
+    </row>
+    <row r="1082">
+      <c r="A1082" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:32:21</t>
+        </is>
+      </c>
+      <c r="B1082" t="n">
+        <v>152478.05</v>
+      </c>
+      <c r="C1082" t="n">
+        <v>139669.89</v>
+      </c>
+      <c r="D1082" t="n">
+        <v>243316.98</v>
+      </c>
+      <c r="E1082" t="n">
+        <v>161123.18</v>
+      </c>
+      <c r="F1082" t="inlineStr"/>
+    </row>
+    <row r="1083">
+      <c r="A1083" t="inlineStr">
+        <is>
+          <t>2026-03-03 19:32:32</t>
+        </is>
+      </c>
+      <c r="B1083" t="n">
+        <v>152510.93</v>
+      </c>
+      <c r="C1083" t="n">
+        <v>139700.01</v>
+      </c>
+      <c r="D1083" t="n">
+        <v>243254.06</v>
+      </c>
+      <c r="E1083" t="n">
+        <v>161157.93</v>
+      </c>
+      <c r="F1083" t="inlineStr"/>
+    </row>
+    <row r="1084">
+      <c r="A1084" t="inlineStr">
+        <is>
+          <t>2026-03-03 21:17:39</t>
+        </is>
+      </c>
+      <c r="B1084" t="n">
+        <v>150281.99</v>
+      </c>
+      <c r="C1084" t="n">
+        <v>137658.3</v>
+      </c>
+      <c r="D1084" t="n">
+        <v>241692.91</v>
+      </c>
+      <c r="E1084" t="n">
+        <v>158802.61</v>
+      </c>
+      <c r="F1084" t="inlineStr"/>
+    </row>
+    <row r="1085">
+      <c r="A1085" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:16:55</t>
+        </is>
+      </c>
+      <c r="B1085" t="n">
+        <v>153208.86</v>
+      </c>
+      <c r="C1085" t="n">
+        <v>140339.32</v>
+      </c>
+      <c r="D1085" t="n">
+        <v>251581.37</v>
+      </c>
+      <c r="E1085" t="n">
+        <v>161895.44</v>
+      </c>
+      <c r="F1085" t="inlineStr"/>
+    </row>
+    <row r="1086">
+      <c r="A1086" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:17:06</t>
+        </is>
+      </c>
+      <c r="B1086" t="n">
+        <v>153219.99</v>
+      </c>
+      <c r="C1086" t="n">
+        <v>140349.51</v>
+      </c>
+      <c r="D1086" t="n">
+        <v>251570.45</v>
+      </c>
+      <c r="E1086" t="n">
+        <v>161907.2</v>
+      </c>
+      <c r="F1086" t="inlineStr"/>
+    </row>
+    <row r="1087">
+      <c r="A1087" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:17:17</t>
+        </is>
+      </c>
+      <c r="B1087" t="n">
+        <v>153222.95</v>
+      </c>
+      <c r="C1087" t="n">
+        <v>140352.23</v>
+      </c>
+      <c r="D1087" t="n">
+        <v>251570.45</v>
+      </c>
+      <c r="E1087" t="n">
+        <v>161910.33</v>
+      </c>
+      <c r="F1087" t="inlineStr"/>
+    </row>
+    <row r="1088">
+      <c r="A1088" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:17:28</t>
+        </is>
+      </c>
+      <c r="B1088" t="n">
+        <v>153214.06</v>
+      </c>
+      <c r="C1088" t="n">
+        <v>140344.08</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>251274.26</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>161900.93</v>
+      </c>
+      <c r="F1088" t="inlineStr"/>
+    </row>
+    <row r="1089">
+      <c r="A1089" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:17:39</t>
+        </is>
+      </c>
+      <c r="B1089" t="n">
+        <v>153227.37</v>
+      </c>
+      <c r="C1089" t="n">
+        <v>140356.27</v>
+      </c>
+      <c r="D1089" t="n">
+        <v>251370.15</v>
+      </c>
+      <c r="E1089" t="n">
+        <v>161914.99</v>
+      </c>
+      <c r="F1089" t="inlineStr"/>
+    </row>
+    <row r="1090">
+      <c r="A1090" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:17:50</t>
+        </is>
+      </c>
+      <c r="B1090" t="n">
+        <v>153227.37</v>
+      </c>
+      <c r="C1090" t="n">
+        <v>140356.27</v>
+      </c>
+      <c r="D1090" t="n">
+        <v>251370.15</v>
+      </c>
+      <c r="E1090" t="n">
+        <v>161914.99</v>
+      </c>
+      <c r="F1090" t="inlineStr"/>
+    </row>
+    <row r="1091">
+      <c r="A1091" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:18:00</t>
+        </is>
+      </c>
+      <c r="B1091" t="n">
+        <v>153230.34</v>
+      </c>
+      <c r="C1091" t="n">
+        <v>140358.99</v>
+      </c>
+      <c r="D1091" t="n">
+        <v>251370.15</v>
+      </c>
+      <c r="E1091" t="n">
+        <v>161918.13</v>
+      </c>
+      <c r="F1091" t="inlineStr"/>
+    </row>
+    <row r="1092">
+      <c r="A1092" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:18:11</t>
+        </is>
+      </c>
+      <c r="B1092" t="n">
+        <v>153233.66</v>
+      </c>
+      <c r="C1092" t="n">
+        <v>140362.03</v>
+      </c>
+      <c r="D1092" t="n">
+        <v>251375.61</v>
+      </c>
+      <c r="E1092" t="n">
+        <v>161921.64</v>
+      </c>
+      <c r="F1092" t="inlineStr"/>
+    </row>
+    <row r="1093">
+      <c r="A1093" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:18:22</t>
+        </is>
+      </c>
+      <c r="B1093" t="n">
+        <v>153227.01</v>
+      </c>
+      <c r="C1093" t="n">
+        <v>140355.94</v>
+      </c>
+      <c r="D1093" t="n">
+        <v>251364.7</v>
+      </c>
+      <c r="E1093" t="n">
+        <v>161914.61</v>
+      </c>
+      <c r="F1093" t="inlineStr"/>
+    </row>
+    <row r="1094">
+      <c r="A1094" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:18:33</t>
+        </is>
+      </c>
+      <c r="B1094" t="n">
+        <v>153250.33</v>
+      </c>
+      <c r="C1094" t="n">
+        <v>140377.3</v>
+      </c>
+      <c r="D1094" t="n">
+        <v>251507.34</v>
+      </c>
+      <c r="E1094" t="n">
+        <v>161939.26</v>
+      </c>
+      <c r="F1094" t="inlineStr"/>
+    </row>
+    <row r="1095">
+      <c r="A1095" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:18:44</t>
+        </is>
+      </c>
+      <c r="B1095" t="n">
+        <v>153250.33</v>
+      </c>
+      <c r="C1095" t="n">
+        <v>140377.3</v>
+      </c>
+      <c r="D1095" t="n">
+        <v>251507.34</v>
+      </c>
+      <c r="E1095" t="n">
+        <v>161939.26</v>
+      </c>
+      <c r="F1095" t="inlineStr"/>
+    </row>
+    <row r="1096">
+      <c r="A1096" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:18:54</t>
+        </is>
+      </c>
+      <c r="B1096" t="n">
+        <v>153241.45</v>
+      </c>
+      <c r="C1096" t="n">
+        <v>140369.17</v>
+      </c>
+      <c r="D1096" t="n">
+        <v>251507.34</v>
+      </c>
+      <c r="E1096" t="n">
+        <v>161929.87</v>
+      </c>
+      <c r="F1096" t="inlineStr"/>
+    </row>
+    <row r="1097">
+      <c r="A1097" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:19:05</t>
+        </is>
+      </c>
+      <c r="B1097" t="n">
+        <v>153247.75</v>
+      </c>
+      <c r="C1097" t="n">
+        <v>140374.94</v>
+      </c>
+      <c r="D1097" t="n">
+        <v>251512.81</v>
+      </c>
+      <c r="E1097" t="n">
+        <v>161936.53</v>
+      </c>
+      <c r="F1097" t="inlineStr"/>
+    </row>
+    <row r="1098">
+      <c r="A1098" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:19:17</t>
+        </is>
+      </c>
+      <c r="B1098" t="n">
+        <v>153247.75</v>
+      </c>
+      <c r="C1098" t="n">
+        <v>140374.94</v>
+      </c>
+      <c r="D1098" t="n">
+        <v>251512.81</v>
+      </c>
+      <c r="E1098" t="n">
+        <v>161936.53</v>
+      </c>
+      <c r="F1098" t="inlineStr"/>
+    </row>
+    <row r="1099">
+      <c r="A1099" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:19:28</t>
+        </is>
+      </c>
+      <c r="B1099" t="n">
+        <v>153200.35</v>
+      </c>
+      <c r="C1099" t="n">
+        <v>140331.53</v>
+      </c>
+      <c r="D1099" t="n">
+        <v>251186.98</v>
+      </c>
+      <c r="E1099" t="n">
+        <v>161886.45</v>
+      </c>
+      <c r="F1099" t="inlineStr"/>
+    </row>
+    <row r="1100">
+      <c r="A1100" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:19:39</t>
+        </is>
+      </c>
+      <c r="B1100" t="n">
+        <v>153190.89</v>
+      </c>
+      <c r="C1100" t="n">
+        <v>140322.85</v>
+      </c>
+      <c r="D1100" t="n">
+        <v>251452.39</v>
+      </c>
+      <c r="E1100" t="n">
+        <v>161876.44</v>
+      </c>
+      <c r="F1100" t="inlineStr"/>
+    </row>
+    <row r="1101">
+      <c r="A1101" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:19:50</t>
+        </is>
+      </c>
+      <c r="B1101" t="n">
+        <v>153190.89</v>
+      </c>
+      <c r="C1101" t="n">
+        <v>140322.85</v>
+      </c>
+      <c r="D1101" t="n">
+        <v>251452.39</v>
+      </c>
+      <c r="E1101" t="n">
+        <v>161876.44</v>
+      </c>
+      <c r="F1101" t="inlineStr"/>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:20:01</t>
+        </is>
+      </c>
+      <c r="B1102" t="n">
+        <v>153250.13</v>
+      </c>
+      <c r="C1102" t="n">
+        <v>140377.12</v>
+      </c>
+      <c r="D1102" t="n">
+        <v>251630.12</v>
+      </c>
+      <c r="E1102" t="n">
+        <v>161939.05</v>
+      </c>
+      <c r="F1102" t="inlineStr"/>
+    </row>
+    <row r="1103">
+      <c r="A1103" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:20:12</t>
+        </is>
+      </c>
+      <c r="B1103" t="n">
+        <v>153233.3</v>
+      </c>
+      <c r="C1103" t="n">
+        <v>140361.7</v>
+      </c>
+      <c r="D1103" t="n">
+        <v>251621.93</v>
+      </c>
+      <c r="E1103" t="n">
+        <v>161921.26</v>
+      </c>
+      <c r="F1103" t="inlineStr"/>
+    </row>
+    <row r="1104">
+      <c r="A1104" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:20:23</t>
+        </is>
+      </c>
+      <c r="B1104" t="n">
+        <v>153223.74</v>
+      </c>
+      <c r="C1104" t="n">
+        <v>140352.95</v>
+      </c>
+      <c r="D1104" t="n">
+        <v>251304.47</v>
+      </c>
+      <c r="E1104" t="n">
+        <v>161911.16</v>
+      </c>
+      <c r="F1104" t="inlineStr"/>
+    </row>
+    <row r="1105">
+      <c r="A1105" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:20:34</t>
+        </is>
+      </c>
+      <c r="B1105" t="n">
+        <v>153224.97</v>
+      </c>
+      <c r="C1105" t="n">
+        <v>140354.07</v>
+      </c>
+      <c r="D1105" t="n">
+        <v>251345.38</v>
+      </c>
+      <c r="E1105" t="n">
+        <v>161912.46</v>
+      </c>
+      <c r="F1105" t="inlineStr"/>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:20:45</t>
+        </is>
+      </c>
+      <c r="B1106" t="n">
+        <v>153204.24</v>
+      </c>
+      <c r="C1106" t="n">
+        <v>140335.08</v>
+      </c>
+      <c r="D1106" t="n">
+        <v>251345.38</v>
+      </c>
+      <c r="E1106" t="n">
+        <v>161890.55</v>
+      </c>
+      <c r="F1106" t="inlineStr"/>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:20:56</t>
+        </is>
+      </c>
+      <c r="B1107" t="n">
+        <v>153177.56</v>
+      </c>
+      <c r="C1107" t="n">
+        <v>140310.65</v>
+      </c>
+      <c r="D1107" t="n">
+        <v>251152.78</v>
+      </c>
+      <c r="E1107" t="n">
+        <v>161862.36</v>
+      </c>
+      <c r="F1107" t="inlineStr"/>
+    </row>
+    <row r="1108">
+      <c r="A1108" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:21:07</t>
+        </is>
+      </c>
+      <c r="B1108" t="n">
+        <v>153151.23</v>
+      </c>
+      <c r="C1108" t="n">
+        <v>140286.53</v>
+      </c>
+      <c r="D1108" t="n">
+        <v>250887.16</v>
+      </c>
+      <c r="E1108" t="n">
+        <v>161834.54</v>
+      </c>
+      <c r="F1108" t="inlineStr"/>
+    </row>
+    <row r="1109">
+      <c r="A1109" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:21:18</t>
+        </is>
+      </c>
+      <c r="B1109" t="n">
+        <v>153124.57</v>
+      </c>
+      <c r="C1109" t="n">
+        <v>140262.11</v>
+      </c>
+      <c r="D1109" t="n">
+        <v>250990.86</v>
+      </c>
+      <c r="E1109" t="n">
+        <v>161806.37</v>
+      </c>
+      <c r="F1109" t="inlineStr"/>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:21:29</t>
+        </is>
+      </c>
+      <c r="B1110" t="n">
+        <v>153149.14</v>
+      </c>
+      <c r="C1110" t="n">
+        <v>140284.61</v>
+      </c>
+      <c r="D1110" t="n">
+        <v>250981.83</v>
+      </c>
+      <c r="E1110" t="n">
+        <v>161832.33</v>
+      </c>
+      <c r="F1110" t="inlineStr"/>
+    </row>
+    <row r="1111">
+      <c r="A1111" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:21:41</t>
+        </is>
+      </c>
+      <c r="B1111" t="n">
+        <v>153135.47</v>
+      </c>
+      <c r="C1111" t="n">
+        <v>140272.09</v>
+      </c>
+      <c r="D1111" t="n">
+        <v>251073.1</v>
+      </c>
+      <c r="E1111" t="n">
+        <v>161817.88</v>
+      </c>
+      <c r="F1111" t="inlineStr"/>
+    </row>
+    <row r="1112">
+      <c r="A1112" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:21:52</t>
+        </is>
+      </c>
+      <c r="B1112" t="n">
+        <v>153127.81</v>
+      </c>
+      <c r="C1112" t="n">
+        <v>140265.08</v>
+      </c>
+      <c r="D1112" t="n">
+        <v>251202.86</v>
+      </c>
+      <c r="E1112" t="n">
+        <v>161809.79</v>
+      </c>
+      <c r="F1112" t="inlineStr"/>
+    </row>
+    <row r="1113">
+      <c r="A1113" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:22:03</t>
+        </is>
+      </c>
+      <c r="B1113" t="n">
+        <v>153140.85</v>
+      </c>
+      <c r="C1113" t="n">
+        <v>140277.02</v>
+      </c>
+      <c r="D1113" t="n">
+        <v>251209.68</v>
+      </c>
+      <c r="E1113" t="n">
+        <v>161823.57</v>
+      </c>
+      <c r="F1113" t="inlineStr"/>
+    </row>
+    <row r="1114">
+      <c r="A1114" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:22:14</t>
+        </is>
+      </c>
+      <c r="B1114" t="n">
+        <v>153069.74</v>
+      </c>
+      <c r="C1114" t="n">
+        <v>140211.88</v>
+      </c>
+      <c r="D1114" t="n">
+        <v>250972.61</v>
+      </c>
+      <c r="E1114" t="n">
+        <v>161748.43</v>
+      </c>
+      <c r="F1114" t="inlineStr"/>
+    </row>
+    <row r="1115">
+      <c r="A1115" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:22:25</t>
+        </is>
+      </c>
+      <c r="B1115" t="n">
+        <v>153012.24</v>
+      </c>
+      <c r="C1115" t="n">
+        <v>140159.21</v>
+      </c>
+      <c r="D1115" t="n">
+        <v>251128.77</v>
+      </c>
+      <c r="E1115" t="n">
+        <v>161687.66</v>
+      </c>
+      <c r="F1115" t="inlineStr"/>
+    </row>
+    <row r="1116">
+      <c r="A1116" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:22:36</t>
+        </is>
+      </c>
+      <c r="B1116" t="n">
+        <v>153052.17</v>
+      </c>
+      <c r="C1116" t="n">
+        <v>140195.78</v>
+      </c>
+      <c r="D1116" t="n">
+        <v>251082.46</v>
+      </c>
+      <c r="E1116" t="n">
+        <v>161729.86</v>
+      </c>
+      <c r="F1116" t="inlineStr"/>
+    </row>
+    <row r="1117">
+      <c r="A1117" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:22:47</t>
+        </is>
+      </c>
+      <c r="B1117" t="n">
+        <v>153054.4</v>
+      </c>
+      <c r="C1117" t="n">
+        <v>140197.83</v>
+      </c>
+      <c r="D1117" t="n">
+        <v>251071.54</v>
+      </c>
+      <c r="E1117" t="n">
+        <v>161732.21</v>
+      </c>
+      <c r="F1117" t="inlineStr"/>
+    </row>
+    <row r="1118">
+      <c r="A1118" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:22:58</t>
+        </is>
+      </c>
+      <c r="B1118" t="n">
+        <v>152996.23</v>
+      </c>
+      <c r="C1118" t="n">
+        <v>140144.55</v>
+      </c>
+      <c r="D1118" t="n">
+        <v>250692.32</v>
+      </c>
+      <c r="E1118" t="n">
+        <v>161670.75</v>
+      </c>
+      <c r="F1118" t="inlineStr"/>
+    </row>
+    <row r="1119">
+      <c r="A1119" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:23:09</t>
+        </is>
+      </c>
+      <c r="B1119" t="n">
+        <v>152978.67</v>
+      </c>
+      <c r="C1119" t="n">
+        <v>140128.46</v>
+      </c>
+      <c r="D1119" t="n">
+        <v>250905.88</v>
+      </c>
+      <c r="E1119" t="n">
+        <v>161652.2</v>
+      </c>
+      <c r="F1119" t="inlineStr"/>
+    </row>
+    <row r="1120">
+      <c r="A1120" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:23:20</t>
+        </is>
+      </c>
+      <c r="B1120" t="n">
+        <v>153117.92</v>
+      </c>
+      <c r="C1120" t="n">
+        <v>140256.01</v>
+      </c>
+      <c r="D1120" t="n">
+        <v>250905.88</v>
+      </c>
+      <c r="E1120" t="n">
+        <v>161799.33</v>
+      </c>
+      <c r="F1120" t="inlineStr"/>
+    </row>
+    <row r="1121">
+      <c r="A1121" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:23:31</t>
+        </is>
+      </c>
+      <c r="B1121" t="n">
+        <v>153171.23</v>
+      </c>
+      <c r="C1121" t="n">
+        <v>140304.85</v>
+      </c>
+      <c r="D1121" t="n">
+        <v>251172.52</v>
+      </c>
+      <c r="E1121" t="n">
+        <v>161855.67</v>
+      </c>
+      <c r="F1121" t="inlineStr"/>
+    </row>
+    <row r="1122">
+      <c r="A1122" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:23:42</t>
+        </is>
+      </c>
+      <c r="B1122" t="n">
+        <v>153101.8</v>
+      </c>
+      <c r="C1122" t="n">
+        <v>140241.25</v>
+      </c>
+      <c r="D1122" t="n">
+        <v>251175.24</v>
+      </c>
+      <c r="E1122" t="n">
+        <v>161782.3</v>
+      </c>
+      <c r="F1122" t="inlineStr"/>
+    </row>
+    <row r="1123">
+      <c r="A1123" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:23:53</t>
+        </is>
+      </c>
+      <c r="B1123" t="n">
+        <v>153125.49</v>
+      </c>
+      <c r="C1123" t="n">
+        <v>140262.95</v>
+      </c>
+      <c r="D1123" t="n">
+        <v>251175.24</v>
+      </c>
+      <c r="E1123" t="n">
+        <v>161807.34</v>
+      </c>
+      <c r="F1123" t="inlineStr"/>
+    </row>
+    <row r="1124">
+      <c r="A1124" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:24:03</t>
+        </is>
+      </c>
+      <c r="B1124" t="n">
+        <v>153220.87</v>
+      </c>
+      <c r="C1124" t="n">
+        <v>140350.32</v>
+      </c>
+      <c r="D1124" t="n">
+        <v>251506</v>
+      </c>
+      <c r="E1124" t="n">
+        <v>161908.12</v>
+      </c>
+      <c r="F1124" t="inlineStr"/>
+    </row>
+    <row r="1125">
+      <c r="A1125" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:24:15</t>
+        </is>
+      </c>
+      <c r="B1125" t="n">
+        <v>153229.75</v>
+      </c>
+      <c r="C1125" t="n">
+        <v>140358.45</v>
+      </c>
+      <c r="D1125" t="n">
+        <v>251417.11</v>
+      </c>
+      <c r="E1125" t="n">
+        <v>161917.51</v>
+      </c>
+      <c r="F1125" t="inlineStr"/>
+    </row>
+    <row r="1126">
+      <c r="A1126" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:24:26</t>
+        </is>
+      </c>
+      <c r="B1126" t="n">
+        <v>153253.45</v>
+      </c>
+      <c r="C1126" t="n">
+        <v>140380.16</v>
+      </c>
+      <c r="D1126" t="n">
+        <v>251491.19</v>
+      </c>
+      <c r="E1126" t="n">
+        <v>161942.56</v>
+      </c>
+      <c r="F1126" t="inlineStr"/>
+    </row>
+    <row r="1127">
+      <c r="A1127" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:24:36</t>
+        </is>
+      </c>
+      <c r="B1127" t="n">
+        <v>153202.73</v>
+      </c>
+      <c r="C1127" t="n">
+        <v>140333.7</v>
+      </c>
+      <c r="D1127" t="n">
+        <v>251407.96</v>
+      </c>
+      <c r="E1127" t="n">
+        <v>161888.96</v>
+      </c>
+      <c r="F1127" t="inlineStr"/>
+    </row>
+    <row r="1128">
+      <c r="A1128" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:24:47</t>
+        </is>
+      </c>
+      <c r="B1128" t="n">
+        <v>153257.6</v>
+      </c>
+      <c r="C1128" t="n">
+        <v>140383.96</v>
+      </c>
+      <c r="D1128" t="n">
+        <v>251275.74</v>
+      </c>
+      <c r="E1128" t="n">
+        <v>161946.94</v>
+      </c>
+      <c r="F1128" t="inlineStr"/>
+    </row>
+    <row r="1129">
+      <c r="A1129" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:24:58</t>
+        </is>
+      </c>
+      <c r="B1129" t="n">
+        <v>153204.27</v>
+      </c>
+      <c r="C1129" t="n">
+        <v>140335.11</v>
+      </c>
+      <c r="D1129" t="n">
+        <v>251349.82</v>
+      </c>
+      <c r="E1129" t="n">
+        <v>161890.58</v>
+      </c>
+      <c r="F1129" t="inlineStr"/>
+    </row>
+    <row r="1130">
+      <c r="A1130" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:25:09</t>
+        </is>
+      </c>
+      <c r="B1130" t="n">
+        <v>153154.4</v>
+      </c>
+      <c r="C1130" t="n">
+        <v>140289.43</v>
+      </c>
+      <c r="D1130" t="n">
+        <v>251268.02</v>
+      </c>
+      <c r="E1130" t="n">
+        <v>161837.89</v>
+      </c>
+      <c r="F1130" t="inlineStr"/>
+    </row>
+    <row r="1131">
+      <c r="A1131" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:25:20</t>
+        </is>
+      </c>
+      <c r="B1131" t="n">
+        <v>153204.77</v>
+      </c>
+      <c r="C1131" t="n">
+        <v>140335.57</v>
+      </c>
+      <c r="D1131" t="n">
+        <v>251268.02</v>
+      </c>
+      <c r="E1131" t="n">
+        <v>161891.11</v>
+      </c>
+      <c r="F1131" t="inlineStr"/>
+    </row>
+    <row r="1132">
+      <c r="A1132" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:25:30</t>
+        </is>
+      </c>
+      <c r="B1132" t="n">
+        <v>153204.77</v>
+      </c>
+      <c r="C1132" t="n">
+        <v>140335.57</v>
+      </c>
+      <c r="D1132" t="n">
+        <v>251268.02</v>
+      </c>
+      <c r="E1132" t="n">
+        <v>161891.11</v>
+      </c>
+      <c r="F1132" t="inlineStr"/>
+    </row>
+    <row r="1133">
+      <c r="A1133" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:25:41</t>
+        </is>
+      </c>
+      <c r="B1133" t="n">
+        <v>153214.75</v>
+      </c>
+      <c r="C1133" t="n">
+        <v>140344.71</v>
+      </c>
+      <c r="D1133" t="n">
+        <v>251284.39</v>
+      </c>
+      <c r="E1133" t="n">
+        <v>161901.66</v>
+      </c>
+      <c r="F1133" t="inlineStr"/>
+    </row>
+    <row r="1134">
+      <c r="A1134" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:25:52</t>
+        </is>
+      </c>
+      <c r="B1134" t="n">
+        <v>153247.33</v>
+      </c>
+      <c r="C1134" t="n">
+        <v>140374.55</v>
+      </c>
+      <c r="D1134" t="n">
+        <v>251402.89</v>
+      </c>
+      <c r="E1134" t="n">
+        <v>161936.08</v>
+      </c>
+      <c r="F1134" t="inlineStr"/>
+    </row>
+    <row r="1135">
+      <c r="A1135" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:26:03</t>
+        </is>
+      </c>
+      <c r="B1135" t="n">
+        <v>153232.14</v>
+      </c>
+      <c r="C1135" t="n">
+        <v>140360.64</v>
+      </c>
+      <c r="D1135" t="n">
+        <v>251397.42</v>
+      </c>
+      <c r="E1135" t="n">
+        <v>161920.04</v>
+      </c>
+      <c r="F1135" t="inlineStr"/>
+    </row>
+    <row r="1136">
+      <c r="A1136" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:26:14</t>
+        </is>
+      </c>
+      <c r="B1136" t="n">
+        <v>153232.14</v>
+      </c>
+      <c r="C1136" t="n">
+        <v>140360.64</v>
+      </c>
+      <c r="D1136" t="n">
+        <v>251219.68</v>
+      </c>
+      <c r="E1136" t="n">
+        <v>161920.04</v>
+      </c>
+      <c r="F1136" t="inlineStr"/>
+    </row>
+    <row r="1137">
+      <c r="A1137" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:26:25</t>
+        </is>
+      </c>
+      <c r="B1137" t="n">
+        <v>153220.3</v>
+      </c>
+      <c r="C1137" t="n">
+        <v>140349.79</v>
+      </c>
+      <c r="D1137" t="n">
+        <v>251219.68</v>
+      </c>
+      <c r="E1137" t="n">
+        <v>161907.52</v>
+      </c>
+      <c r="F1137" t="inlineStr"/>
+    </row>
+    <row r="1138">
+      <c r="A1138" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:26:36</t>
+        </is>
+      </c>
+      <c r="B1138" t="n">
+        <v>153226.39</v>
+      </c>
+      <c r="C1138" t="n">
+        <v>140355.37</v>
+      </c>
+      <c r="D1138" t="n">
+        <v>251318.27</v>
+      </c>
+      <c r="E1138" t="n">
+        <v>161913.95</v>
+      </c>
+      <c r="F1138" t="inlineStr"/>
+    </row>
+    <row r="1139">
+      <c r="A1139" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:26:47</t>
+        </is>
+      </c>
+      <c r="B1139" t="n">
+        <v>153261.93</v>
+      </c>
+      <c r="C1139" t="n">
+        <v>140387.93</v>
+      </c>
+      <c r="D1139" t="n">
+        <v>251303.47</v>
+      </c>
+      <c r="E1139" t="n">
+        <v>161951.51</v>
+      </c>
+      <c r="F1139" t="inlineStr"/>
+    </row>
+    <row r="1140">
+      <c r="A1140" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:26:58</t>
+        </is>
+      </c>
+      <c r="B1140" t="n">
+        <v>153205.64</v>
+      </c>
+      <c r="C1140" t="n">
+        <v>140336.37</v>
+      </c>
+      <c r="D1140" t="n">
+        <v>251303.47</v>
+      </c>
+      <c r="E1140" t="n">
+        <v>161892.03</v>
+      </c>
+      <c r="F1140" t="inlineStr"/>
+    </row>
+    <row r="1141">
+      <c r="A1141" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:27:09</t>
+        </is>
+      </c>
+      <c r="B1141" t="n">
+        <v>153146.03</v>
+      </c>
+      <c r="C1141" t="n">
+        <v>140281.76</v>
+      </c>
+      <c r="D1141" t="n">
+        <v>250986.92</v>
+      </c>
+      <c r="E1141" t="n">
+        <v>161829.04</v>
+      </c>
+      <c r="F1141" t="inlineStr"/>
+    </row>
+    <row r="1142">
+      <c r="A1142" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:27:19</t>
+        </is>
+      </c>
+      <c r="B1142" t="n">
+        <v>153175.66</v>
+      </c>
+      <c r="C1142" t="n">
+        <v>140308.9</v>
+      </c>
+      <c r="D1142" t="n">
+        <v>250986.92</v>
+      </c>
+      <c r="E1142" t="n">
+        <v>161860.35</v>
+      </c>
+      <c r="F1142" t="inlineStr"/>
+    </row>
+    <row r="1143">
+      <c r="A1143" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:27:30</t>
+        </is>
+      </c>
+      <c r="B1143" t="n">
+        <v>153173.45</v>
+      </c>
+      <c r="C1143" t="n">
+        <v>140306.88</v>
+      </c>
+      <c r="D1143" t="n">
+        <v>250957.8</v>
+      </c>
+      <c r="E1143" t="n">
+        <v>161858.02</v>
+      </c>
+      <c r="F1143" t="inlineStr"/>
+    </row>
+    <row r="1144">
+      <c r="A1144" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:27:41</t>
+        </is>
+      </c>
+      <c r="B1144" t="n">
+        <v>153079.54</v>
+      </c>
+      <c r="C1144" t="n">
+        <v>140220.86</v>
+      </c>
+      <c r="D1144" t="n">
+        <v>250708.2</v>
+      </c>
+      <c r="E1144" t="n">
+        <v>161758.78</v>
+      </c>
+      <c r="F1144" t="inlineStr"/>
+    </row>
+    <row r="1145">
+      <c r="A1145" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:27:52</t>
+        </is>
+      </c>
+      <c r="B1145" t="n">
+        <v>153109.43</v>
+      </c>
+      <c r="C1145" t="n">
+        <v>140248.24</v>
+      </c>
+      <c r="D1145" t="n">
+        <v>250742.33</v>
+      </c>
+      <c r="E1145" t="n">
+        <v>161790.37</v>
+      </c>
+      <c r="F1145" t="inlineStr"/>
+    </row>
+    <row r="1146">
+      <c r="A1146" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:28:03</t>
+        </is>
+      </c>
+      <c r="B1146" t="n">
+        <v>152993.62</v>
+      </c>
+      <c r="C1146" t="n">
+        <v>140142.16</v>
+      </c>
+      <c r="D1146" t="n">
+        <v>250693.37</v>
+      </c>
+      <c r="E1146" t="n">
+        <v>161667.99</v>
+      </c>
+      <c r="F1146" t="inlineStr"/>
+    </row>
+    <row r="1147">
+      <c r="A1147" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:28:14</t>
+        </is>
+      </c>
+      <c r="B1147" t="n">
+        <v>153089.89</v>
+      </c>
+      <c r="C1147" t="n">
+        <v>140230.34</v>
+      </c>
+      <c r="D1147" t="n">
+        <v>250867.68</v>
+      </c>
+      <c r="E1147" t="n">
+        <v>161769.72</v>
+      </c>
+      <c r="F1147" t="inlineStr"/>
+    </row>
+    <row r="1148">
+      <c r="A1148" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:28:24</t>
+        </is>
+      </c>
+      <c r="B1148" t="n">
+        <v>153037.14</v>
+      </c>
+      <c r="C1148" t="n">
+        <v>140182.02</v>
+      </c>
+      <c r="D1148" t="n">
+        <v>250868.91</v>
+      </c>
+      <c r="E1148" t="n">
+        <v>161713.98</v>
+      </c>
+      <c r="F1148" t="inlineStr"/>
+    </row>
+    <row r="1149">
+      <c r="A1149" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:28:35</t>
+        </is>
+      </c>
+      <c r="B1149" t="n">
+        <v>153066.77</v>
+      </c>
+      <c r="C1149" t="n">
+        <v>140209.16</v>
+      </c>
+      <c r="D1149" t="n">
+        <v>250957.8</v>
+      </c>
+      <c r="E1149" t="n">
+        <v>161745.29</v>
+      </c>
+      <c r="F1149" t="inlineStr"/>
+    </row>
+    <row r="1150">
+      <c r="A1150" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:28:46</t>
+        </is>
+      </c>
+      <c r="B1150" t="n">
+        <v>153048.99</v>
+      </c>
+      <c r="C1150" t="n">
+        <v>140192.88</v>
+      </c>
+      <c r="D1150" t="n">
+        <v>250957.8</v>
+      </c>
+      <c r="E1150" t="n">
+        <v>161726.5</v>
+      </c>
+      <c r="F1150" t="inlineStr"/>
+    </row>
+    <row r="1151">
+      <c r="A1151" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:28:57</t>
+        </is>
+      </c>
+      <c r="B1151" t="n">
+        <v>153071.5</v>
+      </c>
+      <c r="C1151" t="n">
+        <v>140213.5</v>
+      </c>
+      <c r="D1151" t="n">
+        <v>250950.99</v>
+      </c>
+      <c r="E1151" t="n">
+        <v>161750.29</v>
+      </c>
+      <c r="F1151" t="inlineStr"/>
+    </row>
+    <row r="1152">
+      <c r="A1152" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:29:08</t>
+        </is>
+      </c>
+      <c r="B1152" t="n">
+        <v>153079.8</v>
+      </c>
+      <c r="C1152" t="n">
+        <v>140221.1</v>
+      </c>
+      <c r="D1152" t="n">
+        <v>250964.6</v>
+      </c>
+      <c r="E1152" t="n">
+        <v>161759.06</v>
+      </c>
+      <c r="F1152" t="inlineStr"/>
+    </row>
+    <row r="1153">
+      <c r="A1153" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:29:19</t>
+        </is>
+      </c>
+      <c r="B1153" t="n">
+        <v>153083.96</v>
+      </c>
+      <c r="C1153" t="n">
+        <v>140224.9</v>
+      </c>
+      <c r="D1153" t="n">
+        <v>250971.41</v>
+      </c>
+      <c r="E1153" t="n">
+        <v>161763.45</v>
+      </c>
+      <c r="F1153" t="inlineStr"/>
+    </row>
+    <row r="1154">
+      <c r="A1154" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:29:30</t>
+        </is>
+      </c>
+      <c r="B1154" t="n">
+        <v>153075.66</v>
+      </c>
+      <c r="C1154" t="n">
+        <v>140217.3</v>
+      </c>
+      <c r="D1154" t="n">
+        <v>250957.8</v>
+      </c>
+      <c r="E1154" t="n">
+        <v>161754.68</v>
+      </c>
+      <c r="F1154" t="inlineStr"/>
+    </row>
+    <row r="1155">
+      <c r="A1155" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:29:41</t>
+        </is>
+      </c>
+      <c r="B1155" t="n">
+        <v>153029.76</v>
+      </c>
+      <c r="C1155" t="n">
+        <v>140175.26</v>
+      </c>
+      <c r="D1155" t="n">
+        <v>250901.99</v>
+      </c>
+      <c r="E1155" t="n">
+        <v>161706.18</v>
+      </c>
+      <c r="F1155" t="inlineStr"/>
+    </row>
+    <row r="1156">
+      <c r="A1156" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:29:52</t>
+        </is>
+      </c>
+      <c r="B1156" t="n">
+        <v>153029.76</v>
+      </c>
+      <c r="C1156" t="n">
+        <v>140175.26</v>
+      </c>
+      <c r="D1156" t="n">
+        <v>250901.99</v>
+      </c>
+      <c r="E1156" t="n">
+        <v>161706.18</v>
+      </c>
+      <c r="F1156" t="inlineStr"/>
+    </row>
+    <row r="1157">
+      <c r="A1157" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:30:02</t>
+        </is>
+      </c>
+      <c r="B1157" t="n">
+        <v>153014.01</v>
+      </c>
+      <c r="C1157" t="n">
+        <v>140160.83</v>
+      </c>
+      <c r="D1157" t="n">
+        <v>250954.59</v>
+      </c>
+      <c r="E1157" t="n">
+        <v>161689.54</v>
+      </c>
+      <c r="F1157" t="inlineStr"/>
+    </row>
+    <row r="1158">
+      <c r="A1158" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:30:13</t>
+        </is>
+      </c>
+      <c r="B1158" t="n">
+        <v>153014.01</v>
+      </c>
+      <c r="C1158" t="n">
+        <v>140160.83</v>
+      </c>
+      <c r="D1158" t="n">
+        <v>250954.59</v>
+      </c>
+      <c r="E1158" t="n">
+        <v>161689.54</v>
+      </c>
+      <c r="F1158" t="inlineStr"/>
+    </row>
+    <row r="1159">
+      <c r="A1159" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:30:24</t>
+        </is>
+      </c>
+      <c r="B1159" t="n">
+        <v>152982.22</v>
+      </c>
+      <c r="C1159" t="n">
+        <v>140131.72</v>
+      </c>
+      <c r="D1159" t="n">
+        <v>250729.35</v>
+      </c>
+      <c r="E1159" t="n">
+        <v>161655.95</v>
+      </c>
+      <c r="F1159" t="inlineStr"/>
+    </row>
+    <row r="1160">
+      <c r="A1160" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:30:35</t>
+        </is>
+      </c>
+      <c r="B1160" t="n">
+        <v>153044.25</v>
+      </c>
+      <c r="C1160" t="n">
+        <v>140188.53</v>
+      </c>
+      <c r="D1160" t="n">
+        <v>250816.42</v>
+      </c>
+      <c r="E1160" t="n">
+        <v>161721.49</v>
+      </c>
+      <c r="F1160" t="inlineStr"/>
+    </row>
+    <row r="1161">
+      <c r="A1161" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:30:46</t>
+        </is>
+      </c>
+      <c r="B1161" t="n">
+        <v>153044.25</v>
+      </c>
+      <c r="C1161" t="n">
+        <v>140188.53</v>
+      </c>
+      <c r="D1161" t="n">
+        <v>250816.42</v>
+      </c>
+      <c r="E1161" t="n">
+        <v>161721.49</v>
+      </c>
+      <c r="F1161" t="inlineStr"/>
+    </row>
+    <row r="1162">
+      <c r="A1162" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:30:57</t>
+        </is>
+      </c>
+      <c r="B1162" t="n">
+        <v>153076.85</v>
+      </c>
+      <c r="C1162" t="n">
+        <v>140218.39</v>
+      </c>
+      <c r="D1162" t="n">
+        <v>250816.42</v>
+      </c>
+      <c r="E1162" t="n">
+        <v>161755.94</v>
+      </c>
+      <c r="F1162" t="inlineStr"/>
+    </row>
+    <row r="1163">
+      <c r="A1163" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:31:08</t>
+        </is>
+      </c>
+      <c r="B1163" t="n">
+        <v>153020.39</v>
+      </c>
+      <c r="C1163" t="n">
+        <v>140166.67</v>
+      </c>
+      <c r="D1163" t="n">
+        <v>250723.91</v>
+      </c>
+      <c r="E1163" t="n">
+        <v>161696.28</v>
+      </c>
+      <c r="F1163" t="inlineStr"/>
+    </row>
+    <row r="1164">
+      <c r="A1164" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:31:19</t>
+        </is>
+      </c>
+      <c r="B1164" t="n">
+        <v>153002.61</v>
+      </c>
+      <c r="C1164" t="n">
+        <v>140150.39</v>
+      </c>
+      <c r="D1164" t="n">
+        <v>250723.91</v>
+      </c>
+      <c r="E1164" t="n">
+        <v>161677.49</v>
+      </c>
+      <c r="F1164" t="inlineStr"/>
+    </row>
+    <row r="1165">
+      <c r="A1165" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:31:30</t>
+        </is>
+      </c>
+      <c r="B1165" t="n">
+        <v>153023.34</v>
+      </c>
+      <c r="C1165" t="n">
+        <v>140169.38</v>
+      </c>
+      <c r="D1165" t="n">
+        <v>250901.64</v>
+      </c>
+      <c r="E1165" t="n">
+        <v>161699.39</v>
+      </c>
+      <c r="F1165" t="inlineStr"/>
+    </row>
+    <row r="1166">
+      <c r="A1166" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:31:41</t>
+        </is>
+      </c>
+      <c r="B1166" t="n">
+        <v>153032.94</v>
+      </c>
+      <c r="C1166" t="n">
+        <v>140178.18</v>
+      </c>
+      <c r="D1166" t="n">
+        <v>250912.52</v>
+      </c>
+      <c r="E1166" t="n">
+        <v>161709.54</v>
+      </c>
+      <c r="F1166" t="inlineStr"/>
+    </row>
+    <row r="1167">
+      <c r="A1167" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:31:52</t>
+        </is>
+      </c>
+      <c r="B1167" t="n">
+        <v>153041.84</v>
+      </c>
+      <c r="C1167" t="n">
+        <v>140186.32</v>
+      </c>
+      <c r="D1167" t="n">
+        <v>250986.59</v>
+      </c>
+      <c r="E1167" t="n">
+        <v>161718.94</v>
+      </c>
+      <c r="F1167" t="inlineStr"/>
+    </row>
+    <row r="1168">
+      <c r="A1168" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:32:03</t>
+        </is>
+      </c>
+      <c r="B1168" t="n">
+        <v>153025</v>
+      </c>
+      <c r="C1168" t="n">
+        <v>140170.9</v>
+      </c>
+      <c r="D1168" t="n">
+        <v>250889.56</v>
+      </c>
+      <c r="E1168" t="n">
+        <v>161701.15</v>
+      </c>
+      <c r="F1168" t="inlineStr"/>
+    </row>
+    <row r="1169">
+      <c r="A1169" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:32:13</t>
+        </is>
+      </c>
+      <c r="B1169" t="n">
+        <v>153054.62</v>
+      </c>
+      <c r="C1169" t="n">
+        <v>140198.03</v>
+      </c>
+      <c r="D1169" t="n">
+        <v>250978.42</v>
+      </c>
+      <c r="E1169" t="n">
+        <v>161732.45</v>
+      </c>
+      <c r="F1169" t="inlineStr"/>
+    </row>
+    <row r="1170">
+      <c r="A1170" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:32:25</t>
+        </is>
+      </c>
+      <c r="B1170" t="n">
+        <v>153055.35</v>
+      </c>
+      <c r="C1170" t="n">
+        <v>140198.7</v>
+      </c>
+      <c r="D1170" t="n">
+        <v>250915.24</v>
+      </c>
+      <c r="E1170" t="n">
+        <v>161733.22</v>
+      </c>
+      <c r="F1170" t="inlineStr"/>
+    </row>
+    <row r="1171">
+      <c r="A1171" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:32:35</t>
+        </is>
+      </c>
+      <c r="B1171" t="n">
+        <v>153096.96</v>
+      </c>
+      <c r="C1171" t="n">
+        <v>140236.82</v>
+      </c>
+      <c r="D1171" t="n">
+        <v>250939.76</v>
+      </c>
+      <c r="E1171" t="n">
+        <v>161777.19</v>
+      </c>
+      <c r="F1171" t="inlineStr"/>
+    </row>
+    <row r="1172">
+      <c r="A1172" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:32:46</t>
+        </is>
+      </c>
+      <c r="B1172" t="n">
+        <v>153068.99</v>
+      </c>
+      <c r="C1172" t="n">
+        <v>140211.2</v>
+      </c>
+      <c r="D1172" t="n">
+        <v>250942.48</v>
+      </c>
+      <c r="E1172" t="n">
+        <v>161747.64</v>
+      </c>
+      <c r="F1172" t="inlineStr"/>
+    </row>
+    <row r="1173">
+      <c r="A1173" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:32:57</t>
+        </is>
+      </c>
+      <c r="B1173" t="n">
+        <v>153028.83</v>
+      </c>
+      <c r="C1173" t="n">
+        <v>140174.4</v>
+      </c>
+      <c r="D1173" t="n">
+        <v>250924.96</v>
+      </c>
+      <c r="E1173" t="n">
+        <v>161705.19</v>
+      </c>
+      <c r="F1173" t="inlineStr"/>
+    </row>
+    <row r="1174">
+      <c r="A1174" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:33:08</t>
+        </is>
+      </c>
+      <c r="B1174" t="n">
+        <v>153073.62</v>
+      </c>
+      <c r="C1174" t="n">
+        <v>140215.44</v>
+      </c>
+      <c r="D1174" t="n">
+        <v>250974.84</v>
+      </c>
+      <c r="E1174" t="n">
+        <v>161752.53</v>
+      </c>
+      <c r="F1174" t="inlineStr"/>
+    </row>
+    <row r="1175">
+      <c r="A1175" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:33:19</t>
+        </is>
+      </c>
+      <c r="B1175" t="n">
+        <v>153067.69</v>
+      </c>
+      <c r="C1175" t="n">
+        <v>140210</v>
+      </c>
+      <c r="D1175" t="n">
+        <v>250974.84</v>
+      </c>
+      <c r="E1175" t="n">
+        <v>161746.26</v>
+      </c>
+      <c r="F1175" t="inlineStr"/>
+    </row>
+    <row r="1176">
+      <c r="A1176" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:33:30</t>
+        </is>
+      </c>
+      <c r="B1176" t="n">
+        <v>153038.06</v>
+      </c>
+      <c r="C1176" t="n">
+        <v>140182.86</v>
+      </c>
+      <c r="D1176" t="n">
+        <v>250974.84</v>
+      </c>
+      <c r="E1176" t="n">
+        <v>161714.95</v>
+      </c>
+      <c r="F1176" t="inlineStr"/>
+    </row>
+    <row r="1177">
+      <c r="A1177" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:33:41</t>
+        </is>
+      </c>
+      <c r="B1177" t="n">
+        <v>153047.17</v>
+      </c>
+      <c r="C1177" t="n">
+        <v>140191.21</v>
+      </c>
+      <c r="D1177" t="n">
+        <v>250955.76</v>
+      </c>
+      <c r="E1177" t="n">
+        <v>161724.58</v>
+      </c>
+      <c r="F1177" t="inlineStr"/>
+    </row>
+    <row r="1178">
+      <c r="A1178" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:33:52</t>
+        </is>
+      </c>
+      <c r="B1178" t="n">
+        <v>153047.17</v>
+      </c>
+      <c r="C1178" t="n">
+        <v>140191.21</v>
+      </c>
+      <c r="D1178" t="n">
+        <v>250955.76</v>
+      </c>
+      <c r="E1178" t="n">
+        <v>161724.58</v>
+      </c>
+      <c r="F1178" t="inlineStr"/>
+    </row>
+    <row r="1179">
+      <c r="A1179" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:34:03</t>
+        </is>
+      </c>
+      <c r="B1179" t="n">
+        <v>153061.4</v>
+      </c>
+      <c r="C1179" t="n">
+        <v>140204.25</v>
+      </c>
+      <c r="D1179" t="n">
+        <v>250969.39</v>
+      </c>
+      <c r="E1179" t="n">
+        <v>161739.62</v>
+      </c>
+      <c r="F1179" t="inlineStr"/>
+    </row>
+    <row r="1180">
+      <c r="A1180" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:34:14</t>
+        </is>
+      </c>
+      <c r="B1180" t="n">
+        <v>153061.4</v>
+      </c>
+      <c r="C1180" t="n">
+        <v>140204.25</v>
+      </c>
+      <c r="D1180" t="n">
+        <v>250969.39</v>
+      </c>
+      <c r="E1180" t="n">
+        <v>161739.62</v>
+      </c>
+      <c r="F1180" t="inlineStr"/>
+    </row>
+    <row r="1181">
+      <c r="A1181" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:34:25</t>
+        </is>
+      </c>
+      <c r="B1181" t="n">
+        <v>153061.4</v>
+      </c>
+      <c r="C1181" t="n">
+        <v>140204.25</v>
+      </c>
+      <c r="D1181" t="n">
+        <v>250924.96</v>
+      </c>
+      <c r="E1181" t="n">
+        <v>161739.62</v>
+      </c>
+      <c r="F1181" t="inlineStr"/>
+    </row>
+    <row r="1182">
+      <c r="A1182" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:34:36</t>
+        </is>
+      </c>
+      <c r="B1182" t="n">
+        <v>153086.42</v>
+      </c>
+      <c r="C1182" t="n">
+        <v>140227.16</v>
+      </c>
+      <c r="D1182" t="n">
+        <v>250922.23</v>
+      </c>
+      <c r="E1182" t="n">
+        <v>161766.05</v>
+      </c>
+      <c r="F1182" t="inlineStr"/>
+    </row>
+    <row r="1183">
+      <c r="A1183" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:34:47</t>
+        </is>
+      </c>
+      <c r="B1183" t="n">
+        <v>153125.46</v>
+      </c>
+      <c r="C1183" t="n">
+        <v>140262.92</v>
+      </c>
+      <c r="D1183" t="n">
+        <v>250986.22</v>
+      </c>
+      <c r="E1183" t="n">
+        <v>161807.3</v>
+      </c>
+      <c r="F1183" t="inlineStr"/>
+    </row>
+    <row r="1184">
+      <c r="A1184" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:34:57</t>
+        </is>
+      </c>
+      <c r="B1184" t="n">
+        <v>153082.77</v>
+      </c>
+      <c r="C1184" t="n">
+        <v>140223.81</v>
+      </c>
+      <c r="D1184" t="n">
+        <v>250979.41</v>
+      </c>
+      <c r="E1184" t="n">
+        <v>161762.19</v>
+      </c>
+      <c r="F1184" t="inlineStr"/>
+    </row>
+    <row r="1185">
+      <c r="A1185" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:35:08</t>
+        </is>
+      </c>
+      <c r="B1185" t="n">
+        <v>153051.22</v>
+      </c>
+      <c r="C1185" t="n">
+        <v>140194.91</v>
+      </c>
+      <c r="D1185" t="n">
+        <v>250927.68</v>
+      </c>
+      <c r="E1185" t="n">
+        <v>161728.85</v>
+      </c>
+      <c r="F1185" t="inlineStr"/>
+    </row>
+    <row r="1186">
+      <c r="A1186" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:35:19</t>
+        </is>
+      </c>
+      <c r="B1186" t="n">
+        <v>153071.96</v>
+      </c>
+      <c r="C1186" t="n">
+        <v>140213.92</v>
+      </c>
+      <c r="D1186" t="n">
+        <v>250927.68</v>
+      </c>
+      <c r="E1186" t="n">
+        <v>161750.77</v>
+      </c>
+      <c r="F1186" t="inlineStr"/>
+    </row>
+    <row r="1187">
+      <c r="A1187" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:35:30</t>
+        </is>
+      </c>
+      <c r="B1187" t="n">
+        <v>153131.21</v>
+      </c>
+      <c r="C1187" t="n">
+        <v>140268.19</v>
+      </c>
+      <c r="D1187" t="n">
+        <v>250957.31</v>
+      </c>
+      <c r="E1187" t="n">
+        <v>161813.39</v>
+      </c>
+      <c r="F1187" t="inlineStr"/>
+    </row>
+    <row r="1188">
+      <c r="A1188" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:35:41</t>
+        </is>
+      </c>
+      <c r="B1188" t="n">
+        <v>153083.1</v>
+      </c>
+      <c r="C1188" t="n">
+        <v>140224.12</v>
+      </c>
+      <c r="D1188" t="n">
+        <v>251050.1</v>
+      </c>
+      <c r="E1188" t="n">
+        <v>161762.54</v>
+      </c>
+      <c r="F1188" t="inlineStr"/>
+    </row>
+    <row r="1189">
+      <c r="A1189" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:35:52</t>
+        </is>
+      </c>
+      <c r="B1189" t="n">
+        <v>153065.32</v>
+      </c>
+      <c r="C1189" t="n">
+        <v>140207.83</v>
+      </c>
+      <c r="D1189" t="n">
+        <v>251050.1</v>
+      </c>
+      <c r="E1189" t="n">
+        <v>161743.76</v>
+      </c>
+      <c r="F1189" t="inlineStr"/>
+    </row>
+    <row r="1190">
+      <c r="A1190" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:36:03</t>
+        </is>
+      </c>
+      <c r="B1190" t="n">
+        <v>153075.51</v>
+      </c>
+      <c r="C1190" t="n">
+        <v>140217.16</v>
+      </c>
+      <c r="D1190" t="n">
+        <v>251047.38</v>
+      </c>
+      <c r="E1190" t="n">
+        <v>161754.52</v>
+      </c>
+      <c r="F1190" t="inlineStr"/>
+    </row>
+    <row r="1191">
+      <c r="A1191" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:36:15</t>
+        </is>
+      </c>
+      <c r="B1191" t="n">
+        <v>153069.58</v>
+      </c>
+      <c r="C1191" t="n">
+        <v>140211.73</v>
+      </c>
+      <c r="D1191" t="n">
+        <v>251032.57</v>
+      </c>
+      <c r="E1191" t="n">
+        <v>161748.25</v>
+      </c>
+      <c r="F1191" t="inlineStr"/>
+    </row>
+    <row r="1192">
+      <c r="A1192" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:36:26</t>
+        </is>
+      </c>
+      <c r="B1192" t="n">
+        <v>153094</v>
+      </c>
+      <c r="C1192" t="n">
+        <v>140234.1</v>
+      </c>
+      <c r="D1192" t="n">
+        <v>251028.66</v>
+      </c>
+      <c r="E1192" t="n">
+        <v>161774.06</v>
+      </c>
+      <c r="F1192" t="inlineStr"/>
+    </row>
+    <row r="1193">
+      <c r="A1193" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:36:37</t>
+        </is>
+      </c>
+      <c r="B1193" t="n">
+        <v>153047.54</v>
+      </c>
+      <c r="C1193" t="n">
+        <v>140191.55</v>
+      </c>
+      <c r="D1193" t="n">
+        <v>251020.49</v>
+      </c>
+      <c r="E1193" t="n">
+        <v>161724.97</v>
+      </c>
+      <c r="F1193" t="inlineStr"/>
+    </row>
+    <row r="1194">
+      <c r="A1194" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:36:48</t>
+        </is>
+      </c>
+      <c r="B1194" t="n">
+        <v>153023.85</v>
+      </c>
+      <c r="C1194" t="n">
+        <v>140169.84</v>
+      </c>
+      <c r="D1194" t="n">
+        <v>251035.3</v>
+      </c>
+      <c r="E1194" t="n">
+        <v>161699.93</v>
+      </c>
+      <c r="F1194" t="inlineStr"/>
+    </row>
+    <row r="1195">
+      <c r="A1195" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:36:59</t>
+        </is>
+      </c>
+      <c r="B1195" t="n">
+        <v>153050.51</v>
+      </c>
+      <c r="C1195" t="n">
+        <v>140194.26</v>
+      </c>
+      <c r="D1195" t="n">
+        <v>251050.1</v>
+      </c>
+      <c r="E1195" t="n">
+        <v>161728.1</v>
+      </c>
+      <c r="F1195" t="inlineStr"/>
+    </row>
+    <row r="1196">
+      <c r="A1196" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:37:09</t>
+        </is>
+      </c>
+      <c r="B1196" t="n">
+        <v>153051.43</v>
+      </c>
+      <c r="C1196" t="n">
+        <v>140195.11</v>
+      </c>
+      <c r="D1196" t="n">
+        <v>250908.61</v>
+      </c>
+      <c r="E1196" t="n">
+        <v>161729.08</v>
+      </c>
+      <c r="F1196" t="inlineStr"/>
+    </row>
+    <row r="1197">
+      <c r="A1197" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:37:20</t>
+        </is>
+      </c>
+      <c r="B1197" t="n">
+        <v>153078.62</v>
+      </c>
+      <c r="C1197" t="n">
+        <v>140220.02</v>
+      </c>
+      <c r="D1197" t="n">
+        <v>251061.51</v>
+      </c>
+      <c r="E1197" t="n">
+        <v>161757.81</v>
+      </c>
+      <c r="F1197" t="inlineStr"/>
+    </row>
+    <row r="1198">
+      <c r="A1198" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:37:31</t>
+        </is>
+      </c>
+      <c r="B1198" t="n">
+        <v>153003.67</v>
+      </c>
+      <c r="C1198" t="n">
+        <v>140151.36</v>
+      </c>
+      <c r="D1198" t="n">
+        <v>250977.23</v>
+      </c>
+      <c r="E1198" t="n">
+        <v>161678.61</v>
+      </c>
+      <c r="F1198" t="inlineStr"/>
+    </row>
+    <row r="1199">
+      <c r="A1199" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:37:42</t>
+        </is>
+      </c>
+      <c r="B1199" t="n">
+        <v>153047.22</v>
+      </c>
+      <c r="C1199" t="n">
+        <v>140191.25</v>
+      </c>
+      <c r="D1199" t="n">
+        <v>251053.49</v>
+      </c>
+      <c r="E1199" t="n">
+        <v>161724.63</v>
+      </c>
+      <c r="F1199" t="inlineStr"/>
+    </row>
+    <row r="1200">
+      <c r="A1200" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:37:53</t>
+        </is>
+      </c>
+      <c r="B1200" t="n">
+        <v>153059.07</v>
+      </c>
+      <c r="C1200" t="n">
+        <v>140202.1</v>
+      </c>
+      <c r="D1200" t="n">
+        <v>251053.49</v>
+      </c>
+      <c r="E1200" t="n">
+        <v>161737.15</v>
+      </c>
+      <c r="F1200" t="inlineStr"/>
+    </row>
+    <row r="1201">
+      <c r="A1201" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:38:04</t>
+        </is>
+      </c>
+      <c r="B1201" t="n">
+        <v>153015.89</v>
+      </c>
+      <c r="C1201" t="n">
+        <v>140162.55</v>
+      </c>
+      <c r="D1201" t="n">
+        <v>250982.67</v>
+      </c>
+      <c r="E1201" t="n">
+        <v>161691.52</v>
+      </c>
+      <c r="F1201" t="inlineStr"/>
+    </row>
+    <row r="1202">
+      <c r="A1202" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:38:15</t>
+        </is>
+      </c>
+      <c r="B1202" t="n">
+        <v>153020.15</v>
+      </c>
+      <c r="C1202" t="n">
+        <v>140166.45</v>
+      </c>
+      <c r="D1202" t="n">
+        <v>250979.95</v>
+      </c>
+      <c r="E1202" t="n">
+        <v>161696.02</v>
+      </c>
+      <c r="F1202" t="inlineStr"/>
+    </row>
+    <row r="1203">
+      <c r="A1203" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:38:26</t>
+        </is>
+      </c>
+      <c r="B1203" t="n">
+        <v>153002.38</v>
+      </c>
+      <c r="C1203" t="n">
+        <v>140150.18</v>
+      </c>
+      <c r="D1203" t="n">
+        <v>250979.95</v>
+      </c>
+      <c r="E1203" t="n">
+        <v>161677.25</v>
+      </c>
+      <c r="F1203" t="inlineStr"/>
+    </row>
+    <row r="1204">
+      <c r="A1204" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:38:37</t>
+        </is>
+      </c>
+      <c r="B1204" t="n">
+        <v>153009.03</v>
+      </c>
+      <c r="C1204" t="n">
+        <v>140156.27</v>
+      </c>
+      <c r="D1204" t="n">
+        <v>250990.86</v>
+      </c>
+      <c r="E1204" t="n">
+        <v>161684.28</v>
+      </c>
+      <c r="F1204" t="inlineStr"/>
+    </row>
+    <row r="1205">
+      <c r="A1205" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:38:48</t>
+        </is>
+      </c>
+      <c r="B1205" t="n">
+        <v>153009.03</v>
+      </c>
+      <c r="C1205" t="n">
+        <v>140156.27</v>
+      </c>
+      <c r="D1205" t="n">
+        <v>250990.86</v>
+      </c>
+      <c r="E1205" t="n">
+        <v>161684.28</v>
+      </c>
+      <c r="F1205" t="inlineStr"/>
+    </row>
+    <row r="1206">
+      <c r="A1206" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:38:59</t>
+        </is>
+      </c>
+      <c r="B1206" t="n">
+        <v>153050.51</v>
+      </c>
+      <c r="C1206" t="n">
+        <v>140194.26</v>
+      </c>
+      <c r="D1206" t="n">
+        <v>250946.42</v>
+      </c>
+      <c r="E1206" t="n">
+        <v>161728.1</v>
+      </c>
+      <c r="F1206" t="inlineStr"/>
+    </row>
+    <row r="1207">
+      <c r="A1207" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:39:10</t>
+        </is>
+      </c>
+      <c r="B1207" t="n">
+        <v>153035.69</v>
+      </c>
+      <c r="C1207" t="n">
+        <v>140180.7</v>
+      </c>
+      <c r="D1207" t="n">
+        <v>251094.54</v>
+      </c>
+      <c r="E1207" t="n">
+        <v>161712.45</v>
+      </c>
+      <c r="F1207" t="inlineStr"/>
+    </row>
+    <row r="1208">
+      <c r="A1208" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:39:21</t>
+        </is>
+      </c>
+      <c r="B1208" t="n">
+        <v>153014.95</v>
+      </c>
+      <c r="C1208" t="n">
+        <v>140161.69</v>
+      </c>
+      <c r="D1208" t="n">
+        <v>251198.24</v>
+      </c>
+      <c r="E1208" t="n">
+        <v>161690.53</v>
+      </c>
+      <c r="F1208" t="inlineStr"/>
+    </row>
+    <row r="1209">
+      <c r="A1209" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:39:32</t>
+        </is>
+      </c>
+      <c r="B1209" t="n">
+        <v>153003.32</v>
+      </c>
+      <c r="C1209" t="n">
+        <v>140151.04</v>
+      </c>
+      <c r="D1209" t="n">
+        <v>251193.95</v>
+      </c>
+      <c r="E1209" t="n">
+        <v>161678.24</v>
+      </c>
+      <c r="F1209" t="inlineStr"/>
+    </row>
+    <row r="1210">
+      <c r="A1210" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:39:43</t>
+        </is>
+      </c>
+      <c r="B1210" t="n">
+        <v>153000.35</v>
+      </c>
+      <c r="C1210" t="n">
+        <v>140148.32</v>
+      </c>
+      <c r="D1210" t="n">
+        <v>251193.95</v>
+      </c>
+      <c r="E1210" t="n">
+        <v>161675.11</v>
+      </c>
+      <c r="F1210" t="inlineStr"/>
+    </row>
+    <row r="1211">
+      <c r="A1211" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:39:54</t>
+        </is>
+      </c>
+      <c r="B1211" t="n">
+        <v>153006.28</v>
+      </c>
+      <c r="C1211" t="n">
+        <v>140153.76</v>
+      </c>
+      <c r="D1211" t="n">
+        <v>251193.95</v>
+      </c>
+      <c r="E1211" t="n">
+        <v>161681.37</v>
+      </c>
+      <c r="F1211" t="inlineStr"/>
+    </row>
+    <row r="1212">
+      <c r="A1212" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:40:05</t>
+        </is>
+      </c>
+      <c r="B1212" t="n">
+        <v>152995.38</v>
+      </c>
+      <c r="C1212" t="n">
+        <v>140143.76</v>
+      </c>
+      <c r="D1212" t="n">
+        <v>251052.48</v>
+      </c>
+      <c r="E1212" t="n">
+        <v>161669.85</v>
+      </c>
+      <c r="F1212" t="inlineStr"/>
+    </row>
+    <row r="1213">
+      <c r="A1213" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:40:16</t>
+        </is>
+      </c>
+      <c r="B1213" t="n">
+        <v>152986.49</v>
+      </c>
+      <c r="C1213" t="n">
+        <v>140135.63</v>
+      </c>
+      <c r="D1213" t="n">
+        <v>251170.97</v>
+      </c>
+      <c r="E1213" t="n">
+        <v>161660.46</v>
+      </c>
+      <c r="F1213" t="inlineStr"/>
+    </row>
+    <row r="1214">
+      <c r="A1214" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:40:27</t>
+        </is>
+      </c>
+      <c r="B1214" t="n">
+        <v>153042.77</v>
+      </c>
+      <c r="C1214" t="n">
+        <v>140187.18</v>
+      </c>
+      <c r="D1214" t="n">
+        <v>251289.47</v>
+      </c>
+      <c r="E1214" t="n">
+        <v>161719.93</v>
+      </c>
+      <c r="F1214" t="inlineStr"/>
+    </row>
+    <row r="1215">
+      <c r="A1215" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:40:38</t>
+        </is>
+      </c>
+      <c r="B1215" t="n">
+        <v>153141.4</v>
+      </c>
+      <c r="C1215" t="n">
+        <v>140277.52</v>
+      </c>
+      <c r="D1215" t="n">
+        <v>251739.7</v>
+      </c>
+      <c r="E1215" t="n">
+        <v>161824.15</v>
+      </c>
+      <c r="F1215" t="inlineStr"/>
+    </row>
+    <row r="1216">
+      <c r="A1216" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:40:49</t>
+        </is>
+      </c>
+      <c r="B1216" t="n">
+        <v>153046.59</v>
+      </c>
+      <c r="C1216" t="n">
+        <v>140190.68</v>
+      </c>
+      <c r="D1216" t="n">
+        <v>251798.94</v>
+      </c>
+      <c r="E1216" t="n">
+        <v>161723.96</v>
+      </c>
+      <c r="F1216" t="inlineStr"/>
+    </row>
+    <row r="1217">
+      <c r="A1217" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:41:00</t>
+        </is>
+      </c>
+      <c r="B1217" t="n">
+        <v>153051.96</v>
+      </c>
+      <c r="C1217" t="n">
+        <v>140195.59</v>
+      </c>
+      <c r="D1217" t="n">
+        <v>251565.25</v>
+      </c>
+      <c r="E1217" t="n">
+        <v>161729.64</v>
+      </c>
+      <c r="F1217" t="inlineStr"/>
+    </row>
+    <row r="1218">
+      <c r="A1218" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:41:11</t>
+        </is>
+      </c>
+      <c r="B1218" t="n">
+        <v>153023.34</v>
+      </c>
+      <c r="C1218" t="n">
+        <v>140169.38</v>
+      </c>
+      <c r="D1218" t="n">
+        <v>251479.27</v>
+      </c>
+      <c r="E1218" t="n">
+        <v>161699.39</v>
+      </c>
+      <c r="F1218" t="inlineStr"/>
+    </row>
+    <row r="1219">
+      <c r="A1219" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:41:22</t>
+        </is>
+      </c>
+      <c r="B1219" t="n">
+        <v>153064.82</v>
+      </c>
+      <c r="C1219" t="n">
+        <v>140207.38</v>
+      </c>
+      <c r="D1219" t="n">
+        <v>251790.32</v>
+      </c>
+      <c r="E1219" t="n">
+        <v>161743.23</v>
+      </c>
+      <c r="F1219" t="inlineStr"/>
+    </row>
+    <row r="1220">
+      <c r="A1220" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:41:33</t>
+        </is>
+      </c>
+      <c r="B1220" t="n">
+        <v>153084.97</v>
+      </c>
+      <c r="C1220" t="n">
+        <v>140225.83</v>
+      </c>
+      <c r="D1220" t="n">
+        <v>251626.24</v>
+      </c>
+      <c r="E1220" t="n">
+        <v>161764.52</v>
+      </c>
+      <c r="F1220" t="inlineStr"/>
+    </row>
+    <row r="1221">
+      <c r="A1221" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:41:43</t>
+        </is>
+      </c>
+      <c r="B1221" t="n">
+        <v>153034.6</v>
+      </c>
+      <c r="C1221" t="n">
+        <v>140179.7</v>
+      </c>
+      <c r="D1221" t="n">
+        <v>251626.24</v>
+      </c>
+      <c r="E1221" t="n">
+        <v>161711.3</v>
+      </c>
+      <c r="F1221" t="inlineStr"/>
+    </row>
+    <row r="1222">
+      <c r="A1222" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:41:54</t>
+        </is>
+      </c>
+      <c r="B1222" t="n">
+        <v>153034.6</v>
+      </c>
+      <c r="C1222" t="n">
+        <v>140179.7</v>
+      </c>
+      <c r="D1222" t="n">
+        <v>251626.24</v>
+      </c>
+      <c r="E1222" t="n">
+        <v>161711.3</v>
+      </c>
+      <c r="F1222" t="inlineStr"/>
+    </row>
+    <row r="1223">
+      <c r="A1223" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:42:05</t>
+        </is>
+      </c>
+      <c r="B1223" t="n">
+        <v>153083.66</v>
+      </c>
+      <c r="C1223" t="n">
+        <v>140224.64</v>
+      </c>
+      <c r="D1223" t="n">
+        <v>251762.27</v>
+      </c>
+      <c r="E1223" t="n">
+        <v>161763.14</v>
+      </c>
+      <c r="F1223" t="inlineStr"/>
+    </row>
+    <row r="1224">
+      <c r="A1224" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:42:16</t>
+        </is>
+      </c>
+      <c r="B1224" t="n">
+        <v>153070.3</v>
+      </c>
+      <c r="C1224" t="n">
+        <v>140212.39</v>
+      </c>
+      <c r="D1224" t="n">
+        <v>251680.43</v>
+      </c>
+      <c r="E1224" t="n">
+        <v>161749.02</v>
+      </c>
+      <c r="F1224" t="inlineStr"/>
+    </row>
+    <row r="1225">
+      <c r="A1225" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:42:27</t>
+        </is>
+      </c>
+      <c r="B1225" t="n">
+        <v>153076.22</v>
+      </c>
+      <c r="C1225" t="n">
+        <v>140217.81</v>
+      </c>
+      <c r="D1225" t="n">
+        <v>251176.78</v>
+      </c>
+      <c r="E1225" t="n">
+        <v>161755.27</v>
+      </c>
+      <c r="F1225" t="inlineStr"/>
+    </row>
+    <row r="1226">
+      <c r="A1226" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:42:38</t>
+        </is>
+      </c>
+      <c r="B1226" t="n">
+        <v>153067.69</v>
+      </c>
+      <c r="C1226" t="n">
+        <v>140210</v>
+      </c>
+      <c r="D1226" t="n">
+        <v>250945.2</v>
+      </c>
+      <c r="E1226" t="n">
+        <v>161746.26</v>
+      </c>
+      <c r="F1226" t="inlineStr"/>
+    </row>
+    <row r="1227">
+      <c r="A1227" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:42:49</t>
+        </is>
+      </c>
+      <c r="B1227" t="n">
+        <v>153067.69</v>
+      </c>
+      <c r="C1227" t="n">
+        <v>140210</v>
+      </c>
+      <c r="D1227" t="n">
+        <v>250900.76</v>
+      </c>
+      <c r="E1227" t="n">
+        <v>161746.26</v>
+      </c>
+      <c r="F1227" t="inlineStr"/>
+    </row>
+    <row r="1228">
+      <c r="A1228" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:43:00</t>
+        </is>
+      </c>
+      <c r="B1228" t="n">
+        <v>153026.21</v>
+      </c>
+      <c r="C1228" t="n">
+        <v>140172.01</v>
+      </c>
+      <c r="D1228" t="n">
+        <v>250811.89</v>
+      </c>
+      <c r="E1228" t="n">
+        <v>161702.43</v>
+      </c>
+      <c r="F1228" t="inlineStr"/>
+    </row>
+    <row r="1229">
+      <c r="A1229" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:43:11</t>
+        </is>
+      </c>
+      <c r="B1229" t="n">
+        <v>152969.44</v>
+      </c>
+      <c r="C1229" t="n">
+        <v>140120.01</v>
+      </c>
+      <c r="D1229" t="n">
+        <v>250470.9</v>
+      </c>
+      <c r="E1229" t="n">
+        <v>161642.44</v>
+      </c>
+      <c r="F1229" t="inlineStr"/>
+    </row>
+    <row r="1230">
+      <c r="A1230" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:43:22</t>
+        </is>
+      </c>
+      <c r="B1230" t="n">
+        <v>152933.88</v>
+      </c>
+      <c r="C1230" t="n">
+        <v>140087.44</v>
+      </c>
+      <c r="D1230" t="n">
+        <v>250515.34</v>
+      </c>
+      <c r="E1230" t="n">
+        <v>161604.87</v>
+      </c>
+      <c r="F1230" t="inlineStr"/>
+    </row>
+    <row r="1231">
+      <c r="A1231" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:43:33</t>
+        </is>
+      </c>
+      <c r="B1231" t="n">
+        <v>152963.51</v>
+      </c>
+      <c r="C1231" t="n">
+        <v>140114.57</v>
+      </c>
+      <c r="D1231" t="n">
+        <v>250456.08</v>
+      </c>
+      <c r="E1231" t="n">
+        <v>161636.17</v>
+      </c>
+      <c r="F1231" t="inlineStr"/>
+    </row>
+    <row r="1232">
+      <c r="A1232" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:43:44</t>
+        </is>
+      </c>
+      <c r="B1232" t="n">
+        <v>152978.32</v>
+      </c>
+      <c r="C1232" t="n">
+        <v>140128.14</v>
+      </c>
+      <c r="D1232" t="n">
+        <v>250426.47</v>
+      </c>
+      <c r="E1232" t="n">
+        <v>161651.82</v>
+      </c>
+      <c r="F1232" t="inlineStr"/>
+    </row>
+    <row r="1233">
+      <c r="A1233" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:43:55</t>
+        </is>
+      </c>
+      <c r="B1233" t="n">
+        <v>153007.94</v>
+      </c>
+      <c r="C1233" t="n">
+        <v>140155.28</v>
+      </c>
+      <c r="D1233" t="n">
+        <v>250426.47</v>
+      </c>
+      <c r="E1233" t="n">
+        <v>161683.13</v>
+      </c>
+      <c r="F1233" t="inlineStr"/>
+    </row>
+    <row r="1234">
+      <c r="A1234" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:44:06</t>
+        </is>
+      </c>
+      <c r="B1234" t="n">
+        <v>152998.83</v>
+      </c>
+      <c r="C1234" t="n">
+        <v>140146.93</v>
+      </c>
+      <c r="D1234" t="n">
+        <v>250830.64</v>
+      </c>
+      <c r="E1234" t="n">
+        <v>161673.5</v>
+      </c>
+      <c r="F1234" t="inlineStr"/>
+    </row>
+    <row r="1235">
+      <c r="A1235" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:44:17</t>
+        </is>
+      </c>
+      <c r="B1235" t="n">
+        <v>152997.17</v>
+      </c>
+      <c r="C1235" t="n">
+        <v>140145.41</v>
+      </c>
+      <c r="D1235" t="n">
+        <v>250827.92</v>
+      </c>
+      <c r="E1235" t="n">
+        <v>161671.74</v>
+      </c>
+      <c r="F1235" t="inlineStr"/>
+    </row>
+    <row r="1236">
+      <c r="A1236" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:44:28</t>
+        </is>
+      </c>
+      <c r="B1236" t="n">
+        <v>152973.48</v>
+      </c>
+      <c r="C1236" t="n">
+        <v>140123.7</v>
+      </c>
+      <c r="D1236" t="n">
+        <v>250635.34</v>
+      </c>
+      <c r="E1236" t="n">
+        <v>161646.7</v>
+      </c>
+      <c r="F1236" t="inlineStr"/>
+    </row>
+    <row r="1237">
+      <c r="A1237" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:44:40</t>
+        </is>
+      </c>
+      <c r="B1237" t="n">
+        <v>152969.57</v>
+      </c>
+      <c r="C1237" t="n">
+        <v>140120.13</v>
+      </c>
+      <c r="D1237" t="n">
+        <v>250599.06</v>
+      </c>
+      <c r="E1237" t="n">
+        <v>161642.58</v>
+      </c>
+      <c r="F1237" t="inlineStr"/>
+    </row>
+    <row r="1238">
+      <c r="A1238" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:44:50</t>
+        </is>
+      </c>
+      <c r="B1238" t="n">
+        <v>152954.76</v>
+      </c>
+      <c r="C1238" t="n">
+        <v>140106.56</v>
+      </c>
+      <c r="D1238" t="n">
+        <v>250362.04</v>
+      </c>
+      <c r="E1238" t="n">
+        <v>161626.93</v>
+      </c>
+      <c r="F1238" t="inlineStr"/>
+    </row>
+    <row r="1239">
+      <c r="A1239" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:45:01</t>
+        </is>
+      </c>
+      <c r="B1239" t="n">
+        <v>152947.17</v>
+      </c>
+      <c r="C1239" t="n">
+        <v>140099.61</v>
+      </c>
+      <c r="D1239" t="n">
+        <v>250522.27</v>
+      </c>
+      <c r="E1239" t="n">
+        <v>161618.91</v>
+      </c>
+      <c r="F1239" t="inlineStr"/>
+    </row>
+    <row r="1240">
+      <c r="A1240" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:45:12</t>
+        </is>
+      </c>
+      <c r="B1240" t="n">
+        <v>152948.83</v>
+      </c>
+      <c r="C1240" t="n">
+        <v>140101.13</v>
+      </c>
+      <c r="D1240" t="n">
+        <v>250258.35</v>
+      </c>
+      <c r="E1240" t="n">
+        <v>161620.66</v>
+      </c>
+      <c r="F1240" t="inlineStr"/>
+    </row>
+    <row r="1241">
+      <c r="A1241" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:45:24</t>
+        </is>
+      </c>
+      <c r="B1241" t="n">
+        <v>152928.08</v>
+      </c>
+      <c r="C1241" t="n">
+        <v>140082.12</v>
+      </c>
+      <c r="D1241" t="n">
+        <v>250332.43</v>
+      </c>
+      <c r="E1241" t="n">
+        <v>161598.74</v>
+      </c>
+      <c r="F1241" t="inlineStr"/>
+    </row>
+    <row r="1242">
+      <c r="A1242" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:45:35</t>
+        </is>
+      </c>
+      <c r="B1242" t="n">
+        <v>152887.91</v>
+      </c>
+      <c r="C1242" t="n">
+        <v>140045.33</v>
+      </c>
+      <c r="D1242" t="n">
+        <v>250329.71</v>
+      </c>
+      <c r="E1242" t="n">
+        <v>161556.29</v>
+      </c>
+      <c r="F1242" t="inlineStr"/>
+    </row>
+    <row r="1243">
+      <c r="A1243" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:45:46</t>
+        </is>
+      </c>
+      <c r="B1243" t="n">
+        <v>152896.8</v>
+      </c>
+      <c r="C1243" t="n">
+        <v>140053.47</v>
+      </c>
+      <c r="D1243" t="n">
+        <v>250329.71</v>
+      </c>
+      <c r="E1243" t="n">
+        <v>161565.68</v>
+      </c>
+      <c r="F1243" t="inlineStr"/>
+    </row>
+    <row r="1244">
+      <c r="A1244" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:45:57</t>
+        </is>
+      </c>
+      <c r="B1244" t="n">
+        <v>152896.8</v>
+      </c>
+      <c r="C1244" t="n">
+        <v>140053.47</v>
+      </c>
+      <c r="D1244" t="n">
+        <v>250329.71</v>
+      </c>
+      <c r="E1244" t="n">
+        <v>161565.68</v>
+      </c>
+      <c r="F1244" t="inlineStr"/>
+    </row>
+    <row r="1245">
+      <c r="A1245" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:46:08</t>
+        </is>
+      </c>
+      <c r="B1245" t="n">
+        <v>152991.61</v>
+      </c>
+      <c r="C1245" t="n">
+        <v>140140.31</v>
+      </c>
+      <c r="D1245" t="n">
+        <v>250477.83</v>
+      </c>
+      <c r="E1245" t="n">
+        <v>161665.86</v>
+      </c>
+      <c r="F1245" t="inlineStr"/>
+    </row>
+    <row r="1246">
+      <c r="A1246" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:46:19</t>
+        </is>
+      </c>
+      <c r="B1246" t="n">
+        <v>152970.86</v>
+      </c>
+      <c r="C1246" t="n">
+        <v>140121.31</v>
+      </c>
+      <c r="D1246" t="n">
+        <v>250670.41</v>
+      </c>
+      <c r="E1246" t="n">
+        <v>161643.94</v>
+      </c>
+      <c r="F1246" t="inlineStr"/>
+    </row>
+    <row r="1247">
+      <c r="A1247" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:46:30</t>
+        </is>
+      </c>
+      <c r="B1247" t="n">
+        <v>153041.98</v>
+      </c>
+      <c r="C1247" t="n">
+        <v>140186.45</v>
+      </c>
+      <c r="D1247" t="n">
+        <v>250877.8</v>
+      </c>
+      <c r="E1247" t="n">
+        <v>161719.09</v>
+      </c>
+      <c r="F1247" t="inlineStr"/>
+    </row>
+    <row r="1248">
+      <c r="A1248" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:46:41</t>
+        </is>
+      </c>
+      <c r="B1248" t="n">
+        <v>153023.25</v>
+      </c>
+      <c r="C1248" t="n">
+        <v>140169.29</v>
+      </c>
+      <c r="D1248" t="n">
+        <v>250974.84</v>
+      </c>
+      <c r="E1248" t="n">
+        <v>161699.3</v>
+      </c>
+      <c r="F1248" t="inlineStr"/>
+    </row>
+    <row r="1249">
+      <c r="A1249" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:46:52</t>
+        </is>
+      </c>
+      <c r="B1249" t="n">
+        <v>153082.5</v>
+      </c>
+      <c r="C1249" t="n">
+        <v>140223.57</v>
+      </c>
+      <c r="D1249" t="n">
+        <v>250974.84</v>
+      </c>
+      <c r="E1249" t="n">
+        <v>161761.91</v>
+      </c>
+      <c r="F1249" t="inlineStr"/>
+    </row>
+    <row r="1250">
+      <c r="A1250" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:47:03</t>
+        </is>
+      </c>
+      <c r="B1250" t="n">
+        <v>153045.88</v>
+      </c>
+      <c r="C1250" t="n">
+        <v>140190.03</v>
+      </c>
+      <c r="D1250" t="n">
+        <v>250973.31</v>
+      </c>
+      <c r="E1250" t="n">
+        <v>161723.21</v>
+      </c>
+      <c r="F1250" t="inlineStr"/>
+    </row>
+    <row r="1251">
+      <c r="A1251" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:47:14</t>
+        </is>
+      </c>
+      <c r="B1251" t="n">
+        <v>153048.85</v>
+      </c>
+      <c r="C1251" t="n">
+        <v>140192.74</v>
+      </c>
+      <c r="D1251" t="n">
+        <v>250810.39</v>
+      </c>
+      <c r="E1251" t="n">
+        <v>161726.35</v>
+      </c>
+      <c r="F1251" t="inlineStr"/>
+    </row>
+    <row r="1252">
+      <c r="A1252" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:47:25</t>
+        </is>
+      </c>
+      <c r="B1252" t="n">
+        <v>153078.04</v>
+      </c>
+      <c r="C1252" t="n">
+        <v>140219.48</v>
+      </c>
+      <c r="D1252" t="n">
+        <v>250882.51</v>
+      </c>
+      <c r="E1252" t="n">
+        <v>161757.2</v>
+      </c>
+      <c r="F1252" t="inlineStr"/>
+    </row>
+    <row r="1253">
+      <c r="A1253" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:47:36</t>
+        </is>
+      </c>
+      <c r="B1253" t="n">
+        <v>153035.69</v>
+      </c>
+      <c r="C1253" t="n">
+        <v>140180.7</v>
+      </c>
+      <c r="D1253" t="n">
+        <v>250813.11</v>
+      </c>
+      <c r="E1253" t="n">
+        <v>161712.45</v>
+      </c>
+      <c r="F1253" t="inlineStr"/>
+    </row>
+    <row r="1254">
+      <c r="A1254" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:47:47</t>
+        </is>
+      </c>
+      <c r="B1254" t="n">
+        <v>153041.61</v>
+      </c>
+      <c r="C1254" t="n">
+        <v>140186.11</v>
+      </c>
+      <c r="D1254" t="n">
+        <v>250901.99</v>
+      </c>
+      <c r="E1254" t="n">
+        <v>161718.7</v>
+      </c>
+      <c r="F1254" t="inlineStr"/>
+    </row>
+    <row r="1255">
+      <c r="A1255" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:47:58</t>
+        </is>
+      </c>
+      <c r="B1255" t="n">
+        <v>153081.44</v>
+      </c>
+      <c r="C1255" t="n">
+        <v>140222.6</v>
+      </c>
+      <c r="D1255" t="n">
+        <v>251225.15</v>
+      </c>
+      <c r="E1255" t="n">
+        <v>161760.79</v>
+      </c>
+      <c r="F1255" t="inlineStr"/>
+    </row>
+    <row r="1256">
+      <c r="A1256" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:48:09</t>
+        </is>
+      </c>
+      <c r="B1256" t="n">
+        <v>153001.56</v>
+      </c>
+      <c r="C1256" t="n">
+        <v>140149.43</v>
+      </c>
+      <c r="D1256" t="n">
+        <v>251279.28</v>
+      </c>
+      <c r="E1256" t="n">
+        <v>161676.39</v>
+      </c>
+      <c r="F1256" t="inlineStr"/>
+    </row>
+    <row r="1257">
+      <c r="A1257" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:48:20</t>
+        </is>
+      </c>
+      <c r="B1257" t="n">
+        <v>153012.35</v>
+      </c>
+      <c r="C1257" t="n">
+        <v>140159.31</v>
+      </c>
+      <c r="D1257" t="n">
+        <v>251262.93</v>
+      </c>
+      <c r="E1257" t="n">
+        <v>161687.79</v>
+      </c>
+      <c r="F1257" t="inlineStr"/>
+    </row>
+    <row r="1258">
+      <c r="A1258" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:48:31</t>
+        </is>
+      </c>
+      <c r="B1258" t="n">
+        <v>153022.31</v>
+      </c>
+      <c r="C1258" t="n">
+        <v>140168.44</v>
+      </c>
+      <c r="D1258" t="n">
+        <v>251279.28</v>
+      </c>
+      <c r="E1258" t="n">
+        <v>161698.31</v>
+      </c>
+      <c r="F1258" t="inlineStr"/>
+    </row>
+    <row r="1259">
+      <c r="A1259" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:48:42</t>
+        </is>
+      </c>
+      <c r="B1259" t="n">
+        <v>153022.31</v>
+      </c>
+      <c r="C1259" t="n">
+        <v>140168.44</v>
+      </c>
+      <c r="D1259" t="n">
+        <v>251279.28</v>
+      </c>
+      <c r="E1259" t="n">
+        <v>161698.31</v>
+      </c>
+      <c r="F1259" t="inlineStr"/>
+    </row>
+    <row r="1260">
+      <c r="A1260" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:48:53</t>
+        </is>
+      </c>
+      <c r="B1260" t="n">
+        <v>153167.49</v>
+      </c>
+      <c r="C1260" t="n">
+        <v>140301.42</v>
+      </c>
+      <c r="D1260" t="n">
+        <v>251279.28</v>
+      </c>
+      <c r="E1260" t="n">
+        <v>161851.72</v>
+      </c>
+      <c r="F1260" t="inlineStr"/>
+    </row>
+    <row r="1261">
+      <c r="A1261" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:49:04</t>
+        </is>
+      </c>
+      <c r="B1261" t="n">
+        <v>153158.59</v>
+      </c>
+      <c r="C1261" t="n">
+        <v>140293.27</v>
+      </c>
+      <c r="D1261" t="n">
+        <v>251279.28</v>
+      </c>
+      <c r="E1261" t="n">
+        <v>161842.31</v>
+      </c>
+      <c r="F1261" t="inlineStr"/>
+    </row>
+    <row r="1262">
+      <c r="A1262" t="inlineStr">
+        <is>
+          <t>2026-03-04 10:49:15</t>
+        </is>
+      </c>
+      <c r="B1262" t="n">
+        <v>153126.59</v>
+      </c>
+      <c r="C1262" t="n">
+        <v>140263.95</v>
+      </c>
+      <c r="D1262" t="n">
+        <v>251265.66</v>
+      </c>
+      <c r="E1262" t="n">
+        <v>161808.5</v>
+      </c>
+      <c r="F1262" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
